--- a/.codex-tmp/rmr-plant-xlsx/output/CPAC_Safety_Database_Complete.xlsx
+++ b/.codex-tmp/rmr-plant-xlsx/output/CPAC_Safety_Database_Complete.xlsx
@@ -2,62 +2,70 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Complete Index" sheetId="1" r:id="R1c3b838079144774"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database Setup" sheetId="2" r:id="Ra097970235ce4a95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="3" r:id="R387ac6e6996d4cbe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table Summary" sheetId="4" r:id="R4fd0f01886894c26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Dictionary" sheetId="5" r:id="R24281a3f5a934f41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="6" r:id="Raad399d26568496f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Source Mapping" sheetId="7" r:id="Rd67f0d41232b4cba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enums &amp; Status" sheetId="8" r:id="Rc20764bc8b524916"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indexes &amp; Constraints" sheetId="9" r:id="R61c7ba7dc93943bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MySQL DDL Examples" sheetId="10" r:id="R21c7e6c95ca54e05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Flow" sheetId="11" r:id="R721c5deb2f77427a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Privacy &amp; Audit" sheetId="12" r:id="R26787e24719e4fc5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SSO DB Integration" sheetId="13" r:id="Rc750218dfad94d11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Location Source Mapping" sheetId="14" r:id="R82fdc741bd354e91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="organizations" sheetId="15" r:id="R30df3fa18c7042c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="users" sheetId="16" r:id="R5a43b5b9682f4380"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="roles" sheetId="17" r:id="Rca966effe0e5409c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="permissions" sheetId="18" r:id="Re78090d3284d4dc7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="user_roles" sheetId="19" r:id="Rf44b3a5f6bd74232"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="role_permissions" sheetId="20" r:id="Rd0cfe4f1807a4705"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="teams" sheetId="21" r:id="R184593c99b904f85"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="team_members" sheetId="22" r:id="R47022647014a4c56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="locations" sheetId="23" r:id="Re35b0bc3df54495f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="location_import_batches" sheetId="24" r:id="Rf8c7b72d2a434f89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="location_import_rows" sheetId="25" r:id="R543bdfffb9f242c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="checkins" sheetId="26" r:id="R54c63a128d274cdd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="checkin_attachments" sheetId="27" r:id="R33d68626b5924809"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="safety_activities" sheetId="28" r:id="Rfea7c2f2c73d4ea5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assessment_templates" sheetId="29" r:id="R7547c556d3c24d9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assessment_questions" sheetId="30" r:id="R96b46e713cad46a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assessment_runs" sheetId="31" r:id="R0f7a39d1ccfd41d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assessment_answers" sheetId="32" r:id="R95a97ab8383041c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="safety_findings" sheetId="33" r:id="R531439026ff74c40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="corrective_actions" sheetId="34" r:id="R8de8abea3b0a4ce8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="health_checks" sheetId="35" r:id="R6745d588544b4f21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pretrip_checks" sheetId="36" r:id="R6fe628cd54b54cab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kyt_records" sheetId="37" r:id="R999ac06baf9946ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sos_events" sheetId="38" r:id="R229ccbb761664b9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="posts" sheetId="39" r:id="R1314105996a54471"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="comments" sheetId="40" r:id="R8249d0ad598841a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reactions" sheetId="41" r:id="Ra79b5f7bd7974db2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="awareness_questions" sheetId="42" r:id="R460d1cff3f2e4c5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="awareness_attempts" sheetId="43" r:id="R0ffc9706ac194e26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="awareness_answers" sheetId="44" r:id="R933ad1d2e83140b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="holidays" sheetId="45" r:id="Rbd912e6cf6df4342"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="point_rules" sheetId="46" r:id="R518b748217fe4e61"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="point_transactions" sheetId="47" r:id="R519cb722d28e4613"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="point_balances" sheetId="48" r:id="Rca96bc55e4f740f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rewards" sheetId="49" r:id="R33d47e6476cf46bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reward_redemptions" sheetId="50" r:id="Rcfd0daffcabf443d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reward_inventory_transactions" sheetId="51" r:id="R248a6c3c7ae74b04"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="notifications" sheetId="52" r:id="R6488c5e703eb4c7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="audit_logs" sheetId="53" r:id="Reb983dcff32e4a50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="plant_location_details" sheetId="54" r:id="R0bc1965f5acc4d67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="site_location_details" sheetId="55" r:id="R009ed9d020fc4384"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="office_location_details" sheetId="56" r:id="R21647d19a2614355"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Complete Index" sheetId="1" r:id="R2102f9e599804e51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database Setup" sheetId="2" r:id="R53aac150f01d4172"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="3" r:id="R2316b043c2ba4f42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table Summary" sheetId="4" r:id="Rdd98be3f274949c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Dictionary" sheetId="5" r:id="Rb543f80977854baf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="6" r:id="Ra097b6be8ae7430e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Source Mapping" sheetId="7" r:id="R96b0c969ef1a4647"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enums &amp; Status" sheetId="8" r:id="Rc2091f0de9dc450c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indexes &amp; Constraints" sheetId="9" r:id="R5bac2d0a23a24eae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MySQL DDL Examples" sheetId="10" r:id="R0f698e0a70b6490f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Flow" sheetId="11" r:id="R06d92451c95d4ae0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Privacy &amp; Audit" sheetId="12" r:id="R6b328004f97d4b20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SSO DB Integration" sheetId="13" r:id="Rb8d99a3d068845a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Location Source Mapping" sheetId="14" r:id="R5a8500a0e7e24967"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="organizations" sheetId="15" r:id="R1597424a6d184de8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="users" sheetId="16" r:id="R1672e690a0004f05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="roles" sheetId="17" r:id="R481aeca95b0c472e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="permissions" sheetId="18" r:id="Rb72dc0124bf3475e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="user_roles" sheetId="19" r:id="Rd8ed0a7eb3da4d5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="role_permissions" sheetId="20" r:id="R2fbf2f776970490a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="teams" sheetId="21" r:id="R0d553ef6efdc48b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="team_members" sheetId="22" r:id="Rb1417fce34da473b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="locations" sheetId="23" r:id="R3a97fb1157b2452b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="location_import_batches" sheetId="24" r:id="Re1a9628729e94c81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="location_import_rows" sheetId="25" r:id="R8fd1705fe424439f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="checkins" sheetId="26" r:id="R15459aeb5eaf47bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="checkin_attachments" sheetId="27" r:id="R89795da1854144c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="safety_activities" sheetId="28" r:id="R5157bc349e5c486e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assessment_templates" sheetId="29" r:id="R0f733f401dae4b67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assessment_questions" sheetId="30" r:id="R3f80590b2d23442a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assessment_runs" sheetId="31" r:id="Rcf85fa33146d4d29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assessment_answers" sheetId="32" r:id="R2b9cf17cbe064ef6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="safety_findings" sheetId="33" r:id="Rc38affc114fd4dfd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="corrective_actions" sheetId="34" r:id="R8e0b5f0254454eae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="health_checks" sheetId="35" r:id="R9eb132985c1a40a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pretrip_checks" sheetId="36" r:id="R9105369c1558403b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kyt_records" sheetId="37" r:id="R176775d1fd4a4c4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sos_events" sheetId="38" r:id="R3952ecaefe1d49c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="posts" sheetId="39" r:id="Rb79e90f0f54e4b0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="comments" sheetId="40" r:id="Rcb6ba49d941f415d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reactions" sheetId="41" r:id="R907fd7daa77d4836"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="awareness_questions" sheetId="42" r:id="Rd61760a843534292"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="awareness_attempts" sheetId="43" r:id="R264862b9c8124917"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="awareness_answers" sheetId="44" r:id="R6e68081cd3de4c89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="holidays" sheetId="45" r:id="R42b3982aaeac4375"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="point_rules" sheetId="46" r:id="R025503f674ca4d03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="point_transactions" sheetId="47" r:id="Raa8f1563c78b4376"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="point_balances" sheetId="48" r:id="Ra96a49fb336442e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rewards" sheetId="49" r:id="R448e89ab14324401"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reward_redemptions" sheetId="50" r:id="Rbf0cdf3c785f46ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reward_inventory_transactions" sheetId="51" r:id="R32ccecb68bcc4bf2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="notifications" sheetId="52" r:id="Rcb7754e11363436c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="audit_logs" sheetId="53" r:id="Raebcfe2e19a7451f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="plant_location_details" sheetId="54" r:id="R87765c57381a4967"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="site_location_details" sheetId="55" r:id="R158eb31eddec48b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="office_location_details" sheetId="56" r:id="Rcb34c184713a4729"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="safety_culture_events" sheetId="57" r:id="R815d781e0c1248df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="media_assets" sheetId="58" r:id="R0fe7ce778fcb466b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="export_jobs" sheetId="59" r:id="R836aaeb98ec54f20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="notification_preferences" sheetId="60" r:id="Rfb3b7db014784b5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assessment_attachments" sheetId="61" r:id="Re0d1cc21110048e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="corrective_action_comments" sheetId="62" r:id="R3ea69008f2a24447"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="archived_notifications" sheetId="63" r:id="R341d4b8d01464b0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="safety_settings" sheetId="64" r:id="Rd757cb2763c84b33"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2155,7 +2163,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>ไฟล์เดียวรวม Database Blueprint, Data Dictionary, Relationships, DDL และหน้าแยกครบ 42 tables</x:v>
+        <x:v>ไฟล์เดียวรวม Database Blueprint, Data Dictionary, Relationships, DDL และหน้าแยกครบ 50 tables</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -2237,7 +2245,7 @@
         <x:v>Table Summary</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>สรุป 42 tables</x:v>
+        <x:v>สรุป 50 tables</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
         <x:v>เปิดแท็บ Table Summary</x:v>
@@ -2255,7 +2263,7 @@
         <x:v>Column Dictionary</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>รายละเอียด 419 columns</x:v>
+        <x:v>รายละเอียด 497 columns</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
         <x:v>เปิดแท็บ Column Dictionary</x:v>
@@ -3182,6 +3190,150 @@
       <x:c r="F59"/>
       <x:c r="G59"/>
       <x:c r="H59"/>
+    </x:row>
+    <x:row r="60" ht="44" customHeight="1">
+      <x:c r="A60" s="22" t="str">
+        <x:v>Table Page</x:v>
+      </x:c>
+      <x:c r="B60" s="22" t="str">
+        <x:v>safety_culture_events</x:v>
+      </x:c>
+      <x:c r="C60" s="22" t="str">
+        <x:v>กิจกรรมและแคมเปญ Safety Culture ที่บันทึกในฐานจริง</x:v>
+      </x:c>
+      <x:c r="D60" s="22" t="str">
+        <x:v>เปิดแท็บ safety_culture_events</x:v>
+      </x:c>
+      <x:c r="E60" s="22"/>
+      <x:c r="F60" s="22"/>
+      <x:c r="G60" s="22"/>
+      <x:c r="H60" s="22"/>
+    </x:row>
+    <x:row r="61" ht="44" customHeight="1">
+      <x:c r="A61" s="22" t="str">
+        <x:v>Table Page</x:v>
+      </x:c>
+      <x:c r="B61" s="22" t="str">
+        <x:v>media_assets</x:v>
+      </x:c>
+      <x:c r="C61" s="22" t="str">
+        <x:v>Metadata ของไฟล์จริง พร้อม owner/link โดยไม่เก็บ base64 ในข้อมูลธุรกิจ</x:v>
+      </x:c>
+      <x:c r="D61" s="22" t="str">
+        <x:v>เปิดแท็บ media_assets</x:v>
+      </x:c>
+      <x:c r="E61" s="22"/>
+      <x:c r="F61" s="22"/>
+      <x:c r="G61" s="22"/>
+      <x:c r="H61" s="22"/>
+    </x:row>
+    <x:row r="62" ht="44" customHeight="1">
+      <x:c r="A62" s="22" t="str">
+        <x:v>Table Page</x:v>
+      </x:c>
+      <x:c r="B62" s="22" t="str">
+        <x:v>export_jobs</x:v>
+      </x:c>
+      <x:c r="C62" s="22" t="str">
+        <x:v>งาน export และผลลัพธ์ไฟล์จริงที่ตรวจสอบสถานะย้อนหลังได้</x:v>
+      </x:c>
+      <x:c r="D62" s="22" t="str">
+        <x:v>เปิดแท็บ export_jobs</x:v>
+      </x:c>
+      <x:c r="E62" s="22"/>
+      <x:c r="F62" s="22"/>
+      <x:c r="G62" s="22"/>
+      <x:c r="H62" s="22"/>
+    </x:row>
+    <x:row r="63" ht="44" customHeight="1">
+      <x:c r="A63" s="22" t="str">
+        <x:v>Table Page</x:v>
+      </x:c>
+      <x:c r="B63" s="22" t="str">
+        <x:v>notification_preferences</x:v>
+      </x:c>
+      <x:c r="C63" s="22" t="str">
+        <x:v>การตั้งค่าช่องทางแจ้งเตือนรายผู้ใช้</x:v>
+      </x:c>
+      <x:c r="D63" s="22" t="str">
+        <x:v>เปิดแท็บ notification_preferences</x:v>
+      </x:c>
+      <x:c r="E63" s="22"/>
+      <x:c r="F63" s="22"/>
+      <x:c r="G63" s="22"/>
+      <x:c r="H63" s="22"/>
+    </x:row>
+    <x:row r="64" ht="44" customHeight="1">
+      <x:c r="A64" s="22" t="str">
+        <x:v>Table Page</x:v>
+      </x:c>
+      <x:c r="B64" s="22" t="str">
+        <x:v>assessment_attachments</x:v>
+      </x:c>
+      <x:c r="C64" s="22" t="str">
+        <x:v>หลักฐานไฟล์ที่ผูกกับ assessment run ผ่าน media_assets</x:v>
+      </x:c>
+      <x:c r="D64" s="22" t="str">
+        <x:v>เปิดแท็บ assessment_attachments</x:v>
+      </x:c>
+      <x:c r="E64" s="22"/>
+      <x:c r="F64" s="22"/>
+      <x:c r="G64" s="22"/>
+      <x:c r="H64" s="22"/>
+    </x:row>
+    <x:row r="65" ht="44" customHeight="1">
+      <x:c r="A65" s="22" t="str">
+        <x:v>Table Page</x:v>
+      </x:c>
+      <x:c r="B65" s="22" t="str">
+        <x:v>corrective_action_comments</x:v>
+      </x:c>
+      <x:c r="C65" s="22" t="str">
+        <x:v>ความคิดเห็นและประวัติสนทนาของ corrective action</x:v>
+      </x:c>
+      <x:c r="D65" s="22" t="str">
+        <x:v>เปิดแท็บ corrective_action_comments</x:v>
+      </x:c>
+      <x:c r="E65" s="22"/>
+      <x:c r="F65" s="22"/>
+      <x:c r="G65" s="22"/>
+      <x:c r="H65" s="22"/>
+    </x:row>
+    <x:row r="66" ht="44" customHeight="1">
+      <x:c r="A66" s="22" t="str">
+        <x:v>Table Page</x:v>
+      </x:c>
+      <x:c r="B66" s="22" t="str">
+        <x:v>archived_notifications</x:v>
+      </x:c>
+      <x:c r="C66" s="22" t="str">
+        <x:v>สำเนาการแจ้งเตือนที่ผู้ใช้ archive แล้ว</x:v>
+      </x:c>
+      <x:c r="D66" s="22" t="str">
+        <x:v>เปิดแท็บ archived_notifications</x:v>
+      </x:c>
+      <x:c r="E66" s="22"/>
+      <x:c r="F66" s="22"/>
+      <x:c r="G66" s="22"/>
+      <x:c r="H66" s="22"/>
+    </x:row>
+    <x:row r="67" ht="44" customHeight="1">
+      <x:c r="A67" s="22" t="str">
+        <x:v>Table Page</x:v>
+      </x:c>
+      <x:c r="B67" s="22" t="str">
+        <x:v>safety_settings</x:v>
+      </x:c>
+      <x:c r="C67" s="22" t="str">
+        <x:v>ค่าตั้งค่าระบบ Safety ที่ Admin แก้ไขผ่าน API</x:v>
+      </x:c>
+      <x:c r="D67" s="22" t="str">
+        <x:v>เปิดแท็บ safety_settings</x:v>
+      </x:c>
+      <x:c r="E67" s="22"/>
+      <x:c r="F67" s="22"/>
+      <x:c r="G67" s="22"/>
+      <x:c r="H67" s="22"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -3190,7 +3342,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1d6d140fa554a89"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5be3c0797370479e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3421,7 +3573,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14273af9cf7c433c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd8b9df52d6c47c8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3686,6 +3838,26 @@
         <x:v>ไม่เขียนกลับ rmr_sso.Plant; แก้ไขและ soft-delete ได้เฉพาะ source=ADMIN</x:v>
       </x:c>
     </x:row>
+    <x:row r="15" ht="42" customHeight="1">
+      <x:c r="A15" s="22" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B15" s="22" t="str">
+        <x:v>Real API Persistence</x:v>
+      </x:c>
+      <x:c r="C15" s="22" t="str">
+        <x:v>หน้าเมนูที่เปิดเรียก /api/*</x:v>
+      </x:c>
+      <x:c r="D15" s="22" t="str">
+        <x:v>Validate session/permission → เขียน feature table จริง → เขียน audit_logs เมื่อเหมาะสม</x:v>
+      </x:c>
+      <x:c r="E15" s="22" t="str">
+        <x:v>safety_culture_events, media_assets, export_jobs, notification_preferences, assessment_attachments, corrective_action_comments, archived_notifications, safety_settings, audit_logs</x:v>
+      </x:c>
+      <x:c r="F15" s="22" t="str">
+        <x:v>audit_logs ห้ามเป็น primary storage; API fail ให้แสดง error/empty state ไม่เติม mock</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
@@ -3693,7 +3865,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10298d0cd7204278"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c98ba213ed34969"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3917,6 +4089,29 @@
         <x:v>หากเป็น external URL ต้องระวัง referrer และ access control</x:v>
       </x:c>
     </x:row>
+    <x:row r="12" ht="42" customHeight="1">
+      <x:c r="A12" s="22" t="str">
+        <x:v>Business records</x:v>
+      </x:c>
+      <x:c r="B12" s="22" t="str">
+        <x:v>INTERNAL</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="str">
+        <x:v>feature tables</x:v>
+      </x:c>
+      <x:c r="D12" s="22" t="str">
+        <x:v>ตรวจสิทธิ์ตาม owner/role</x:v>
+      </x:c>
+      <x:c r="E12" s="22" t="str">
+        <x:v>ใช้ตาม workflow ของระบบ</x:v>
+      </x:c>
+      <x:c r="F12" s="22" t="str">
+        <x:v>ตาม retention ของแต่ละ feature</x:v>
+      </x:c>
+      <x:c r="G12" s="22" t="str">
+        <x:v>audit_logs เก็บเฉพาะประวัติ ไม่ใช้แทนตารางธุรกิจ</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G1"/>
@@ -3924,7 +4119,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1dfe146ce2e64804"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90b7f7f9e114458d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4067,7 +4262,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20dde5896a8c44c5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb8c447c61a94c11"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4305,7 +4500,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb81973f36bc04bfe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb7fe8e42c124b28"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4946,8 +5141,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6de887ea7b814545"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4ebfda5a1b244f7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6708b5777dd4474d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8f8e75fa7c04e32"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6662,8 +6857,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a58c64cfb8a43fa"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8929a7507f08445d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re09a6f7a23c64e1a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d26c0ae5866407a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7114,8 +7309,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R158451db95bb4cd1"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fde65386d4b4089"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf985a83e35ea4c8a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa1e613e0c8e4c2f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7512,8 +7707,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re32107d068bb4b2c"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd726eac65bc748ae"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce4dcd6d9f144389"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cd22cf0f5414e6e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7921,8 +8116,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd619b8a93bea4838"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbcc5944ed4b43b5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b0b2c601cdd415b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4c9ee2655fd4592"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8316,7 +8511,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9de77506a79b430c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ed48ccfb640494b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8635,8 +8830,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb26575e818714fec"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0613b6df1164b39"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc6de8590048046e1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3179305077c04dbb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9122,8 +9317,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca36a08d87104958"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc10ae72c3ce64df1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7557e00fd724e64"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdba37ba4d99c4ea2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9504,8 +9699,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb3a59de8ee74588"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23d959002eea4215"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a85247cd74b4f91"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42ebbf96f2a14837"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10731,8 +10926,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdfdf8df48a07406e"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14e1d751274149b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde278406ccd449ee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1b2e9f6ce284d5d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11397,8 +11592,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0dca1f263ade4862"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3802d9c6abc45d9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2d9aa97e2d34b78"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9fba44680594c2b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12001,8 +12196,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1dc8db52e47c42c4"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9786612e143f462c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9cb41e4ec674d57"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca07a1d76e334f80"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12757,8 +12952,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b42f78334f346c3"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54d1839b66e248e6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc9fb485d0bf4585"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8dacc9c540534fbf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13240,8 +13435,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e5fca17c2c84710"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5028e35d0224137"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc6606b58a164396"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re54e7bcc53924760"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13964,8 +14159,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3957209916474f49"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb5c6c8bbd8f48ea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc270913052fa483a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03b90fa3fd2d4d3b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14538,8 +14733,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R809e503338af4dc5"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97c84aa340fa4a64"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a03f02c051b4287"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31229360939b4c20"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14661,7 +14856,7 @@
         <x:v>Shared</x:v>
       </x:c>
       <x:c r="B15" s="11" t="str">
-        <x:v>Notifications และ Audit Logs ใช้ข้ามทุก Phase</x:v>
+        <x:v>Notifications, Media, Export, Safety Settings และ Audit Logs ใช้ข้ามทุก Phase</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="42" customHeight="1">
@@ -14814,6 +15009,30 @@
       </x:c>
       <x:c r="B34" s="22" t="str">
         <x:v>โรงงานที่เพิ่มจากเว็บเก็บใน CPAC_Safety.locations ด้วย source=ADMIN, created_by=user.id และไม่ส่งกลับ rmr_sso.Plant</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="42" customHeight="1">
+      <x:c r="A35" s="22" t="str">
+        <x:v>Real API Storage</x:v>
+      </x:c>
+      <x:c r="B35" s="22" t="str">
+        <x:v>ข้อมูลธุรกิจของเมนูที่เปิดใช้งานเก็บในตารางจริง; audit_logs ใช้เป็น audit trail เท่านั้น</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="42" customHeight="1">
+      <x:c r="A36" s="22" t="str">
+        <x:v>Disabled Menus</x:v>
+      </x:c>
+      <x:c r="B36" s="22" t="str">
+        <x:v>Were OK และ Work Permit ปิดจาก menu config จึงไม่บังคับเชื่อม frontend API ในรอบนี้</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="42" customHeight="1">
+      <x:c r="A37" s="22" t="str">
+        <x:v>Media Rule</x:v>
+      </x:c>
+      <x:c r="B37" s="22" t="str">
+        <x:v>ไฟล์จริงเก็บใน storage/server upload directory และเก็บ metadata/owner link ใน media_assets</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -14823,7 +15042,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd4a3e2895864257"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra41845131b654f85"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15386,8 +15605,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e5ce36cb6784ba0"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15f6d9434a85407d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3ed05094f50479c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdff8e91e84b94cb4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15985,8 +16204,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23e81c2cfe554196"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8116698ac47d4ac4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8d34fc6ef604db7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41379b194db14b6e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16493,8 +16712,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R419261fa32ff478c"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R462090b45dd54ed4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69d3a51ad86246e2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6150e3df9a9423d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17096,8 +17315,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R270f3deedc1b4abd"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R158a2442c1e84b6c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f00304238a0416e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58f536a09bcc49a8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17643,8 +17862,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d7027f38d964ac8"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc67b0caa4ea24657"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc65d8c2db6c64619"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80689919da534b05"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18159,8 +18378,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc380dc6a89347f6"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60b3630d98104fd4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9c16fd84e2b4aee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc272e508f9ba4d76"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18675,8 +18894,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1ad2574fdf449ee"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a2f3414305b402c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R845efda18e43490a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R466d4e8bf5064ec5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19191,8 +19410,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0dd99f914e84b2b"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1bd7db9c39684785"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51fd328c026b423f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R404e9a84cb384eff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19707,8 +19926,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0ffd5df58e745f6"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R337bb0db07104595"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e0a13fa23034950"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R537dab1a573a4ec0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20248,8 +20467,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b04be8ae8ed461c"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc149d499c2c14c8b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f5835d4e3a74797"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a818be1356e4756"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21408,6 +21627,214 @@
         <x:v>23</x:v>
       </x:c>
     </x:row>
+    <x:row r="47" ht="42" customHeight="1">
+      <x:c r="A47" s="22" t="str">
+        <x:v>safety_culture_events</x:v>
+      </x:c>
+      <x:c r="B47" s="22" t="str">
+        <x:v>Safety Culture</x:v>
+      </x:c>
+      <x:c r="C47" s="22" t="str">
+        <x:v>กิจกรรมและแคมเปญ Safety Culture ที่บันทึกในฐานจริง</x:v>
+      </x:c>
+      <x:c r="D47" s="22" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="E47" s="22" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="F47" s="22" t="str">
+        <x:v>Phase 3</x:v>
+      </x:c>
+      <x:c r="G47" s="22" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H47" s="22" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="42" customHeight="1">
+      <x:c r="A48" s="22" t="str">
+        <x:v>media_assets</x:v>
+      </x:c>
+      <x:c r="B48" s="22" t="str">
+        <x:v>Shared</x:v>
+      </x:c>
+      <x:c r="C48" s="22" t="str">
+        <x:v>Metadata ของไฟล์จริง พร้อม owner/link โดยไม่เก็บ base64 ในข้อมูลธุรกิจ</x:v>
+      </x:c>
+      <x:c r="D48" s="22" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="E48" s="22" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="F48" s="22" t="str">
+        <x:v>Shared</x:v>
+      </x:c>
+      <x:c r="G48" s="22" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="H48" s="22" t="n">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="42" customHeight="1">
+      <x:c r="A49" s="22" t="str">
+        <x:v>export_jobs</x:v>
+      </x:c>
+      <x:c r="B49" s="22" t="str">
+        <x:v>Reports</x:v>
+      </x:c>
+      <x:c r="C49" s="22" t="str">
+        <x:v>งาน export และผลลัพธ์ไฟล์จริงที่ตรวจสอบสถานะย้อนหลังได้</x:v>
+      </x:c>
+      <x:c r="D49" s="22" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="E49" s="22" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="F49" s="22" t="str">
+        <x:v>Shared</x:v>
+      </x:c>
+      <x:c r="G49" s="22" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H49" s="22" t="n">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="42" customHeight="1">
+      <x:c r="A50" s="22" t="str">
+        <x:v>notification_preferences</x:v>
+      </x:c>
+      <x:c r="B50" s="22" t="str">
+        <x:v>Notifications</x:v>
+      </x:c>
+      <x:c r="C50" s="22" t="str">
+        <x:v>การตั้งค่าช่องทางแจ้งเตือนรายผู้ใช้</x:v>
+      </x:c>
+      <x:c r="D50" s="22" t="str">
+        <x:v>user_id</x:v>
+      </x:c>
+      <x:c r="E50" s="22" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="F50" s="22" t="str">
+        <x:v>Shared</x:v>
+      </x:c>
+      <x:c r="G50" s="22" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="H50" s="22" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="42" customHeight="1">
+      <x:c r="A51" s="22" t="str">
+        <x:v>assessment_attachments</x:v>
+      </x:c>
+      <x:c r="B51" s="22" t="str">
+        <x:v>Assessment</x:v>
+      </x:c>
+      <x:c r="C51" s="22" t="str">
+        <x:v>หลักฐานไฟล์ที่ผูกกับ assessment run ผ่าน media_assets</x:v>
+      </x:c>
+      <x:c r="D51" s="22" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="E51" s="22" t="str">
+        <x:v>users, media_assets, assessment_runs</x:v>
+      </x:c>
+      <x:c r="F51" s="22" t="str">
+        <x:v>Phase 2</x:v>
+      </x:c>
+      <x:c r="G51" s="22" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H51" s="22" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="42" customHeight="1">
+      <x:c r="A52" s="22" t="str">
+        <x:v>corrective_action_comments</x:v>
+      </x:c>
+      <x:c r="B52" s="22" t="str">
+        <x:v>Safety Effort</x:v>
+      </x:c>
+      <x:c r="C52" s="22" t="str">
+        <x:v>ความคิดเห็นและประวัติสนทนาของ corrective action</x:v>
+      </x:c>
+      <x:c r="D52" s="22" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="E52" s="22" t="str">
+        <x:v>corrective_actions, users</x:v>
+      </x:c>
+      <x:c r="F52" s="22" t="str">
+        <x:v>Phase 2</x:v>
+      </x:c>
+      <x:c r="G52" s="22" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H52" s="22" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="42" customHeight="1">
+      <x:c r="A53" s="22" t="str">
+        <x:v>archived_notifications</x:v>
+      </x:c>
+      <x:c r="B53" s="22" t="str">
+        <x:v>Notifications</x:v>
+      </x:c>
+      <x:c r="C53" s="22" t="str">
+        <x:v>สำเนาการแจ้งเตือนที่ผู้ใช้ archive แล้ว</x:v>
+      </x:c>
+      <x:c r="D53" s="22" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="E53" s="22" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="F53" s="22" t="str">
+        <x:v>Shared</x:v>
+      </x:c>
+      <x:c r="G53" s="22" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="H53" s="22" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="42" customHeight="1">
+      <x:c r="A54" s="22" t="str">
+        <x:v>safety_settings</x:v>
+      </x:c>
+      <x:c r="B54" s="22" t="str">
+        <x:v>Shared</x:v>
+      </x:c>
+      <x:c r="C54" s="22" t="str">
+        <x:v>ค่าตั้งค่าระบบ Safety ที่ Admin แก้ไขผ่าน API</x:v>
+      </x:c>
+      <x:c r="D54" s="22" t="str">
+        <x:v>setting_key</x:v>
+      </x:c>
+      <x:c r="E54" s="22" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="F54" s="22" t="str">
+        <x:v>Shared</x:v>
+      </x:c>
+      <x:c r="G54" s="22" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H54" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
@@ -21415,7 +21842,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R713d720f256644f2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e124e8346ea4528"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21897,8 +22324,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcbb318f02ddd4b73"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4f9956db7ac40af"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb75be8a1bac04cf6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3412a6707f7447ec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22279,8 +22706,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd08c9e439dd46fc"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb5bb979e1dc406e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3743d040c6f24997"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f2ebefc02ca44f6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22727,8 +23154,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72920cce9af44644"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4027ae7f48174374"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4fa324afd9343b1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R21f4d40270394862"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23208,8 +23635,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd23ce684ec44f6a"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd35868e55e0544bf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29e782bfc13a4e20"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R507663226da949b5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23687,8 +24114,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0bb61b5964f4ffa"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfce23cd165314fab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12f91cf115ea4645"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36732318ab5a4562"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24081,8 +24508,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe23a1f3ef4f438b"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c62c067010e47f6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc42b69e5564e421b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c0e167119b44122"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24539,8 +24966,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8e4924d6b324c33"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84928e69cf914f3a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R869fc419c129458d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22620c472c4f4481"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25206,8 +25633,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a8e521cb7c54583"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86698b229c544275"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R911a5ea1f29b4cea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbaca042ba6b4a7c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25532,8 +25959,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9cb34ef5aa94d5c"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R295bca638b3a47a5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R631c9ccbef834419"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a089e9381ac4c94"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26075,8 +26502,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7bd27b75f7714eb3"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref1cf4e4f986403e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2af967e203546a1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b8cc74b9c7444a1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -41249,6 +41676,2566 @@
       </x:c>
       <x:c r="N423" s="11"/>
     </x:row>
+    <x:row r="424" ht="42" customHeight="1">
+      <x:c r="A424" s="22" t="str">
+        <x:v>safety_culture_events</x:v>
+      </x:c>
+      <x:c r="B424" s="22" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="C424" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="D424" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E424" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F424" s="22" t="str">
+        <x:v>AUTO_INCREMENT</x:v>
+      </x:c>
+      <x:c r="G424" s="22" t="str">
+        <x:v>PK</x:v>
+      </x:c>
+      <x:c r="H424" s="22"/>
+      <x:c r="I424" s="22" t="str">
+        <x:v>PRIMARY</x:v>
+      </x:c>
+      <x:c r="J424" s="22" t="str">
+        <x:v>รหัสภายในของรายการ</x:v>
+      </x:c>
+      <x:c r="K424" s="22"/>
+      <x:c r="L424" s="22"/>
+      <x:c r="M424" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N424" s="22"/>
+    </x:row>
+    <x:row r="425" ht="42" customHeight="1">
+      <x:c r="A425" s="22" t="str">
+        <x:v>safety_culture_events</x:v>
+      </x:c>
+      <x:c r="B425" s="22" t="str">
+        <x:v>title</x:v>
+      </x:c>
+      <x:c r="C425" s="22" t="str">
+        <x:v>VARCHAR(255)</x:v>
+      </x:c>
+      <x:c r="D425" s="22" t="n">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="E425" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F425" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G425" s="22"/>
+      <x:c r="H425" s="22"/>
+      <x:c r="I425" s="22"/>
+      <x:c r="J425" s="22" t="str">
+        <x:v>ชื่อหรือหัวข้อ</x:v>
+      </x:c>
+      <x:c r="K425" s="22"/>
+      <x:c r="L425" s="22"/>
+      <x:c r="M425" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N425" s="22"/>
+    </x:row>
+    <x:row r="426" ht="42" customHeight="1">
+      <x:c r="A426" s="22" t="str">
+        <x:v>safety_culture_events</x:v>
+      </x:c>
+      <x:c r="B426" s="22" t="str">
+        <x:v>description</x:v>
+      </x:c>
+      <x:c r="C426" s="22" t="str">
+        <x:v>TEXT</x:v>
+      </x:c>
+      <x:c r="D426" s="22" t="n">
+        <x:v>65535</x:v>
+      </x:c>
+      <x:c r="E426" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F426" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G426" s="22"/>
+      <x:c r="H426" s="22"/>
+      <x:c r="I426" s="22"/>
+      <x:c r="J426" s="22" t="str">
+        <x:v>รายละเอียด</x:v>
+      </x:c>
+      <x:c r="K426" s="22"/>
+      <x:c r="L426" s="22"/>
+      <x:c r="M426" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N426" s="22"/>
+    </x:row>
+    <x:row r="427" ht="42" customHeight="1">
+      <x:c r="A427" s="22" t="str">
+        <x:v>safety_culture_events</x:v>
+      </x:c>
+      <x:c r="B427" s="22" t="str">
+        <x:v>event_start_at</x:v>
+      </x:c>
+      <x:c r="C427" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="D427" s="22"/>
+      <x:c r="E427" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F427" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G427" s="22"/>
+      <x:c r="H427" s="22"/>
+      <x:c r="I427" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="J427" s="22" t="str">
+        <x:v>event start at</x:v>
+      </x:c>
+      <x:c r="K427" s="22"/>
+      <x:c r="L427" s="22"/>
+      <x:c r="M427" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N427" s="22"/>
+    </x:row>
+    <x:row r="428" ht="42" customHeight="1">
+      <x:c r="A428" s="22" t="str">
+        <x:v>safety_culture_events</x:v>
+      </x:c>
+      <x:c r="B428" s="22" t="str">
+        <x:v>event_end_at</x:v>
+      </x:c>
+      <x:c r="C428" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="D428" s="22"/>
+      <x:c r="E428" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F428" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G428" s="22"/>
+      <x:c r="H428" s="22"/>
+      <x:c r="I428" s="22"/>
+      <x:c r="J428" s="22" t="str">
+        <x:v>event end at</x:v>
+      </x:c>
+      <x:c r="K428" s="22"/>
+      <x:c r="L428" s="22"/>
+      <x:c r="M428" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N428" s="22"/>
+    </x:row>
+    <x:row r="429" ht="42" customHeight="1">
+      <x:c r="A429" s="22" t="str">
+        <x:v>safety_culture_events</x:v>
+      </x:c>
+      <x:c r="B429" s="22" t="str">
+        <x:v>location_text</x:v>
+      </x:c>
+      <x:c r="C429" s="22" t="str">
+        <x:v>VARCHAR(255)</x:v>
+      </x:c>
+      <x:c r="D429" s="22" t="n">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="E429" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F429" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G429" s="22"/>
+      <x:c r="H429" s="22"/>
+      <x:c r="I429" s="22"/>
+      <x:c r="J429" s="22" t="str">
+        <x:v>location text</x:v>
+      </x:c>
+      <x:c r="K429" s="22"/>
+      <x:c r="L429" s="22"/>
+      <x:c r="M429" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N429" s="22"/>
+    </x:row>
+    <x:row r="430" ht="42" customHeight="1">
+      <x:c r="A430" s="22" t="str">
+        <x:v>safety_culture_events</x:v>
+      </x:c>
+      <x:c r="B430" s="22" t="str">
+        <x:v>status</x:v>
+      </x:c>
+      <x:c r="C430" s="22" t="str">
+        <x:v>VARCHAR(40)</x:v>
+      </x:c>
+      <x:c r="D430" s="22" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E430" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F430" s="22" t="str">
+        <x:v>DRAFT</x:v>
+      </x:c>
+      <x:c r="G430" s="22"/>
+      <x:c r="H430" s="22"/>
+      <x:c r="I430" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="J430" s="22" t="str">
+        <x:v>สถานะรายการ</x:v>
+      </x:c>
+      <x:c r="K430" s="22"/>
+      <x:c r="L430" s="22"/>
+      <x:c r="M430" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N430" s="22"/>
+    </x:row>
+    <x:row r="431" ht="42" customHeight="1">
+      <x:c r="A431" s="22" t="str">
+        <x:v>safety_culture_events</x:v>
+      </x:c>
+      <x:c r="B431" s="22" t="str">
+        <x:v>metadata</x:v>
+      </x:c>
+      <x:c r="C431" s="22" t="str">
+        <x:v>JSON</x:v>
+      </x:c>
+      <x:c r="D431" s="22"/>
+      <x:c r="E431" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F431" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G431" s="22"/>
+      <x:c r="H431" s="22"/>
+      <x:c r="I431" s="22"/>
+      <x:c r="J431" s="22" t="str">
+        <x:v>ข้อมูลประกอบแบบ JSON</x:v>
+      </x:c>
+      <x:c r="K431" s="22"/>
+      <x:c r="L431" s="22" t="str">
+        <x:v>valid JSON</x:v>
+      </x:c>
+      <x:c r="M431" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N431" s="22"/>
+    </x:row>
+    <x:row r="432" ht="42" customHeight="1">
+      <x:c r="A432" s="22" t="str">
+        <x:v>safety_culture_events</x:v>
+      </x:c>
+      <x:c r="B432" s="22" t="str">
+        <x:v>created_by</x:v>
+      </x:c>
+      <x:c r="C432" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="D432" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E432" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F432" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G432" s="22" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="H432" s="22" t="str">
+        <x:v>users.id</x:v>
+      </x:c>
+      <x:c r="I432" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="J432" s="22" t="str">
+        <x:v>ผู้สร้างรายการ</x:v>
+      </x:c>
+      <x:c r="K432" s="22"/>
+      <x:c r="L432" s="22"/>
+      <x:c r="M432" s="22" t="str">
+        <x:v>IDENTIFIER</x:v>
+      </x:c>
+      <x:c r="N432" s="22"/>
+    </x:row>
+    <x:row r="433" ht="42" customHeight="1">
+      <x:c r="A433" s="22" t="str">
+        <x:v>safety_culture_events</x:v>
+      </x:c>
+      <x:c r="B433" s="22" t="str">
+        <x:v>created_at</x:v>
+      </x:c>
+      <x:c r="C433" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="D433" s="22"/>
+      <x:c r="E433" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F433" s="22" t="str">
+        <x:v>CURRENT_TIMESTAMP(3)</x:v>
+      </x:c>
+      <x:c r="G433" s="22"/>
+      <x:c r="H433" s="22"/>
+      <x:c r="I433" s="22"/>
+      <x:c r="J433" s="22" t="str">
+        <x:v>วันที่และเวลาที่สร้างรายการ</x:v>
+      </x:c>
+      <x:c r="K433" s="22"/>
+      <x:c r="L433" s="22"/>
+      <x:c r="M433" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N433" s="22"/>
+    </x:row>
+    <x:row r="434" ht="42" customHeight="1">
+      <x:c r="A434" s="22" t="str">
+        <x:v>safety_culture_events</x:v>
+      </x:c>
+      <x:c r="B434" s="22" t="str">
+        <x:v>updated_at</x:v>
+      </x:c>
+      <x:c r="C434" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="D434" s="22"/>
+      <x:c r="E434" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F434" s="22" t="str">
+        <x:v>CURRENT_TIMESTAMP(3)</x:v>
+      </x:c>
+      <x:c r="G434" s="22"/>
+      <x:c r="H434" s="22"/>
+      <x:c r="I434" s="22"/>
+      <x:c r="J434" s="22" t="str">
+        <x:v>วันที่และเวลาที่แก้ไขล่าสุด</x:v>
+      </x:c>
+      <x:c r="K434" s="22"/>
+      <x:c r="L434" s="22"/>
+      <x:c r="M434" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N434" s="22"/>
+    </x:row>
+    <x:row r="435" ht="42" customHeight="1">
+      <x:c r="A435" s="22" t="str">
+        <x:v>safety_culture_events</x:v>
+      </x:c>
+      <x:c r="B435" s="22" t="str">
+        <x:v>deleted_at</x:v>
+      </x:c>
+      <x:c r="C435" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="D435" s="22"/>
+      <x:c r="E435" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F435" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G435" s="22"/>
+      <x:c r="H435" s="22"/>
+      <x:c r="I435" s="22"/>
+      <x:c r="J435" s="22" t="str">
+        <x:v>วันที่และเวลาที่ soft-delete</x:v>
+      </x:c>
+      <x:c r="K435" s="22"/>
+      <x:c r="L435" s="22"/>
+      <x:c r="M435" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N435" s="22"/>
+    </x:row>
+    <x:row r="436" ht="42" customHeight="1">
+      <x:c r="A436" s="22" t="str">
+        <x:v>media_assets</x:v>
+      </x:c>
+      <x:c r="B436" s="22" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="C436" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="D436" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E436" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F436" s="22" t="str">
+        <x:v>AUTO_INCREMENT</x:v>
+      </x:c>
+      <x:c r="G436" s="22" t="str">
+        <x:v>PK</x:v>
+      </x:c>
+      <x:c r="H436" s="22"/>
+      <x:c r="I436" s="22" t="str">
+        <x:v>PRIMARY</x:v>
+      </x:c>
+      <x:c r="J436" s="22" t="str">
+        <x:v>รหัสภายในของรายการ</x:v>
+      </x:c>
+      <x:c r="K436" s="22"/>
+      <x:c r="L436" s="22"/>
+      <x:c r="M436" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N436" s="22"/>
+    </x:row>
+    <x:row r="437" ht="42" customHeight="1">
+      <x:c r="A437" s="22" t="str">
+        <x:v>media_assets</x:v>
+      </x:c>
+      <x:c r="B437" s="22" t="str">
+        <x:v>file_name</x:v>
+      </x:c>
+      <x:c r="C437" s="22" t="str">
+        <x:v>VARCHAR(255)</x:v>
+      </x:c>
+      <x:c r="D437" s="22" t="n">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="E437" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F437" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G437" s="22"/>
+      <x:c r="H437" s="22"/>
+      <x:c r="I437" s="22"/>
+      <x:c r="J437" s="22" t="str">
+        <x:v>ชื่อไฟล์ในระบบ</x:v>
+      </x:c>
+      <x:c r="K437" s="22"/>
+      <x:c r="L437" s="22"/>
+      <x:c r="M437" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N437" s="22"/>
+    </x:row>
+    <x:row r="438" ht="42" customHeight="1">
+      <x:c r="A438" s="22" t="str">
+        <x:v>media_assets</x:v>
+      </x:c>
+      <x:c r="B438" s="22" t="str">
+        <x:v>original_name</x:v>
+      </x:c>
+      <x:c r="C438" s="22" t="str">
+        <x:v>VARCHAR(255)</x:v>
+      </x:c>
+      <x:c r="D438" s="22" t="n">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="E438" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F438" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G438" s="22"/>
+      <x:c r="H438" s="22"/>
+      <x:c r="I438" s="22"/>
+      <x:c r="J438" s="22" t="str">
+        <x:v>ชื่อไฟล์ต้นฉบับ</x:v>
+      </x:c>
+      <x:c r="K438" s="22"/>
+      <x:c r="L438" s="22"/>
+      <x:c r="M438" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N438" s="22"/>
+    </x:row>
+    <x:row r="439" ht="42" customHeight="1">
+      <x:c r="A439" s="22" t="str">
+        <x:v>media_assets</x:v>
+      </x:c>
+      <x:c r="B439" s="22" t="str">
+        <x:v>mime_type</x:v>
+      </x:c>
+      <x:c r="C439" s="22" t="str">
+        <x:v>VARCHAR(120)</x:v>
+      </x:c>
+      <x:c r="D439" s="22" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="E439" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F439" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G439" s="22"/>
+      <x:c r="H439" s="22"/>
+      <x:c r="I439" s="22"/>
+      <x:c r="J439" s="22" t="str">
+        <x:v>ชนิด MIME ของไฟล์</x:v>
+      </x:c>
+      <x:c r="K439" s="22"/>
+      <x:c r="L439" s="22"/>
+      <x:c r="M439" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N439" s="22"/>
+    </x:row>
+    <x:row r="440" ht="42" customHeight="1">
+      <x:c r="A440" s="22" t="str">
+        <x:v>media_assets</x:v>
+      </x:c>
+      <x:c r="B440" s="22" t="str">
+        <x:v>size_bytes</x:v>
+      </x:c>
+      <x:c r="C440" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="D440" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E440" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F440" s="22" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G440" s="22"/>
+      <x:c r="H440" s="22"/>
+      <x:c r="I440" s="22"/>
+      <x:c r="J440" s="22" t="str">
+        <x:v>ขนาดไฟล์เป็นไบต์</x:v>
+      </x:c>
+      <x:c r="K440" s="22"/>
+      <x:c r="L440" s="22"/>
+      <x:c r="M440" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N440" s="22"/>
+    </x:row>
+    <x:row r="441" ht="42" customHeight="1">
+      <x:c r="A441" s="22" t="str">
+        <x:v>media_assets</x:v>
+      </x:c>
+      <x:c r="B441" s="22" t="str">
+        <x:v>status</x:v>
+      </x:c>
+      <x:c r="C441" s="22" t="str">
+        <x:v>VARCHAR(40)</x:v>
+      </x:c>
+      <x:c r="D441" s="22" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E441" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F441" s="22" t="str">
+        <x:v>READY</x:v>
+      </x:c>
+      <x:c r="G441" s="22"/>
+      <x:c r="H441" s="22"/>
+      <x:c r="I441" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="J441" s="22" t="str">
+        <x:v>สถานะรายการ</x:v>
+      </x:c>
+      <x:c r="K441" s="22"/>
+      <x:c r="L441" s="22"/>
+      <x:c r="M441" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N441" s="22"/>
+    </x:row>
+    <x:row r="442" ht="42" customHeight="1">
+      <x:c r="A442" s="22" t="str">
+        <x:v>media_assets</x:v>
+      </x:c>
+      <x:c r="B442" s="22" t="str">
+        <x:v>module</x:v>
+      </x:c>
+      <x:c r="C442" s="22" t="str">
+        <x:v>VARCHAR(80)</x:v>
+      </x:c>
+      <x:c r="D442" s="22" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E442" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F442" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G442" s="22"/>
+      <x:c r="H442" s="22"/>
+      <x:c r="I442" s="22"/>
+      <x:c r="J442" s="22" t="str">
+        <x:v>module</x:v>
+      </x:c>
+      <x:c r="K442" s="22"/>
+      <x:c r="L442" s="22"/>
+      <x:c r="M442" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N442" s="22"/>
+    </x:row>
+    <x:row r="443" ht="42" customHeight="1">
+      <x:c r="A443" s="22" t="str">
+        <x:v>media_assets</x:v>
+      </x:c>
+      <x:c r="B443" s="22" t="str">
+        <x:v>owner_type</x:v>
+      </x:c>
+      <x:c r="C443" s="22" t="str">
+        <x:v>VARCHAR(80)</x:v>
+      </x:c>
+      <x:c r="D443" s="22" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E443" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F443" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G443" s="22"/>
+      <x:c r="H443" s="22"/>
+      <x:c r="I443" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="J443" s="22" t="str">
+        <x:v>ประเภทข้อมูลธุรกิจที่เป็นเจ้าของไฟล์</x:v>
+      </x:c>
+      <x:c r="K443" s="22"/>
+      <x:c r="L443" s="22"/>
+      <x:c r="M443" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N443" s="22"/>
+    </x:row>
+    <x:row r="444" ht="42" customHeight="1">
+      <x:c r="A444" s="22" t="str">
+        <x:v>media_assets</x:v>
+      </x:c>
+      <x:c r="B444" s="22" t="str">
+        <x:v>owner_id</x:v>
+      </x:c>
+      <x:c r="C444" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="D444" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E444" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F444" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G444" s="22"/>
+      <x:c r="H444" s="22"/>
+      <x:c r="I444" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="J444" s="22" t="str">
+        <x:v>รหัสข้อมูลธุรกิจที่เป็นเจ้าของไฟล์</x:v>
+      </x:c>
+      <x:c r="K444" s="22"/>
+      <x:c r="L444" s="22"/>
+      <x:c r="M444" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N444" s="22"/>
+    </x:row>
+    <x:row r="445" ht="42" customHeight="1">
+      <x:c r="A445" s="22" t="str">
+        <x:v>media_assets</x:v>
+      </x:c>
+      <x:c r="B445" s="22" t="str">
+        <x:v>link_type</x:v>
+      </x:c>
+      <x:c r="C445" s="22" t="str">
+        <x:v>VARCHAR(80)</x:v>
+      </x:c>
+      <x:c r="D445" s="22" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E445" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F445" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G445" s="22"/>
+      <x:c r="H445" s="22"/>
+      <x:c r="I445" s="22"/>
+      <x:c r="J445" s="22" t="str">
+        <x:v>ประเภทความสัมพันธ์ของไฟล์</x:v>
+      </x:c>
+      <x:c r="K445" s="22"/>
+      <x:c r="L445" s="22"/>
+      <x:c r="M445" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N445" s="22"/>
+    </x:row>
+    <x:row r="446" ht="42" customHeight="1">
+      <x:c r="A446" s="22" t="str">
+        <x:v>media_assets</x:v>
+      </x:c>
+      <x:c r="B446" s="22" t="str">
+        <x:v>upload_mode</x:v>
+      </x:c>
+      <x:c r="C446" s="22" t="str">
+        <x:v>VARCHAR(40)</x:v>
+      </x:c>
+      <x:c r="D446" s="22" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E446" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F446" s="22" t="str">
+        <x:v>server</x:v>
+      </x:c>
+      <x:c r="G446" s="22"/>
+      <x:c r="H446" s="22"/>
+      <x:c r="I446" s="22"/>
+      <x:c r="J446" s="22" t="str">
+        <x:v>upload mode</x:v>
+      </x:c>
+      <x:c r="K446" s="22"/>
+      <x:c r="L446" s="22"/>
+      <x:c r="M446" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N446" s="22"/>
+    </x:row>
+    <x:row r="447" ht="42" customHeight="1">
+      <x:c r="A447" s="22" t="str">
+        <x:v>media_assets</x:v>
+      </x:c>
+      <x:c r="B447" s="22" t="str">
+        <x:v>storage_path</x:v>
+      </x:c>
+      <x:c r="C447" s="22" t="str">
+        <x:v>VARCHAR(1000)</x:v>
+      </x:c>
+      <x:c r="D447" s="22" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="E447" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F447" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G447" s="22"/>
+      <x:c r="H447" s="22"/>
+      <x:c r="I447" s="22"/>
+      <x:c r="J447" s="22" t="str">
+        <x:v>ตำแหน่งไฟล์จริงใน storage/server</x:v>
+      </x:c>
+      <x:c r="K447" s="22"/>
+      <x:c r="L447" s="22"/>
+      <x:c r="M447" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N447" s="22" t="str">
+        <x:v>ไฟล์จริงอยู่นอก DB; DB เก็บ metadata เท่านั้น</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="448" ht="42" customHeight="1">
+      <x:c r="A448" s="22" t="str">
+        <x:v>media_assets</x:v>
+      </x:c>
+      <x:c r="B448" s="22" t="str">
+        <x:v>public_url</x:v>
+      </x:c>
+      <x:c r="C448" s="22" t="str">
+        <x:v>VARCHAR(1000)</x:v>
+      </x:c>
+      <x:c r="D448" s="22" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="E448" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F448" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G448" s="22"/>
+      <x:c r="H448" s="22"/>
+      <x:c r="I448" s="22"/>
+      <x:c r="J448" s="22" t="str">
+        <x:v>URL สำหรับเข้าถึงไฟล์ตามสิทธิ์</x:v>
+      </x:c>
+      <x:c r="K448" s="22"/>
+      <x:c r="L448" s="22"/>
+      <x:c r="M448" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N448" s="22"/>
+    </x:row>
+    <x:row r="449" ht="42" customHeight="1">
+      <x:c r="A449" s="22" t="str">
+        <x:v>media_assets</x:v>
+      </x:c>
+      <x:c r="B449" s="22" t="str">
+        <x:v>metadata</x:v>
+      </x:c>
+      <x:c r="C449" s="22" t="str">
+        <x:v>JSON</x:v>
+      </x:c>
+      <x:c r="D449" s="22"/>
+      <x:c r="E449" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F449" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G449" s="22"/>
+      <x:c r="H449" s="22"/>
+      <x:c r="I449" s="22"/>
+      <x:c r="J449" s="22" t="str">
+        <x:v>ข้อมูลประกอบแบบ JSON</x:v>
+      </x:c>
+      <x:c r="K449" s="22"/>
+      <x:c r="L449" s="22" t="str">
+        <x:v>valid JSON</x:v>
+      </x:c>
+      <x:c r="M449" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N449" s="22"/>
+    </x:row>
+    <x:row r="450" ht="42" customHeight="1">
+      <x:c r="A450" s="22" t="str">
+        <x:v>media_assets</x:v>
+      </x:c>
+      <x:c r="B450" s="22" t="str">
+        <x:v>created_by</x:v>
+      </x:c>
+      <x:c r="C450" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="D450" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E450" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F450" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G450" s="22" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="H450" s="22" t="str">
+        <x:v>users.id</x:v>
+      </x:c>
+      <x:c r="I450" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="J450" s="22" t="str">
+        <x:v>ผู้สร้างรายการ</x:v>
+      </x:c>
+      <x:c r="K450" s="22"/>
+      <x:c r="L450" s="22"/>
+      <x:c r="M450" s="22" t="str">
+        <x:v>IDENTIFIER</x:v>
+      </x:c>
+      <x:c r="N450" s="22"/>
+    </x:row>
+    <x:row r="451" ht="42" customHeight="1">
+      <x:c r="A451" s="22" t="str">
+        <x:v>media_assets</x:v>
+      </x:c>
+      <x:c r="B451" s="22" t="str">
+        <x:v>created_at</x:v>
+      </x:c>
+      <x:c r="C451" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="D451" s="22"/>
+      <x:c r="E451" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F451" s="22" t="str">
+        <x:v>CURRENT_TIMESTAMP(3)</x:v>
+      </x:c>
+      <x:c r="G451" s="22"/>
+      <x:c r="H451" s="22"/>
+      <x:c r="I451" s="22"/>
+      <x:c r="J451" s="22" t="str">
+        <x:v>วันที่และเวลาที่สร้างรายการ</x:v>
+      </x:c>
+      <x:c r="K451" s="22"/>
+      <x:c r="L451" s="22"/>
+      <x:c r="M451" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N451" s="22"/>
+    </x:row>
+    <x:row r="452" ht="42" customHeight="1">
+      <x:c r="A452" s="22" t="str">
+        <x:v>media_assets</x:v>
+      </x:c>
+      <x:c r="B452" s="22" t="str">
+        <x:v>updated_at</x:v>
+      </x:c>
+      <x:c r="C452" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="D452" s="22"/>
+      <x:c r="E452" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F452" s="22" t="str">
+        <x:v>CURRENT_TIMESTAMP(3)</x:v>
+      </x:c>
+      <x:c r="G452" s="22"/>
+      <x:c r="H452" s="22"/>
+      <x:c r="I452" s="22"/>
+      <x:c r="J452" s="22" t="str">
+        <x:v>วันที่และเวลาที่แก้ไขล่าสุด</x:v>
+      </x:c>
+      <x:c r="K452" s="22"/>
+      <x:c r="L452" s="22"/>
+      <x:c r="M452" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N452" s="22"/>
+    </x:row>
+    <x:row r="453" ht="42" customHeight="1">
+      <x:c r="A453" s="22" t="str">
+        <x:v>media_assets</x:v>
+      </x:c>
+      <x:c r="B453" s="22" t="str">
+        <x:v>deleted_at</x:v>
+      </x:c>
+      <x:c r="C453" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="D453" s="22"/>
+      <x:c r="E453" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F453" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G453" s="22"/>
+      <x:c r="H453" s="22"/>
+      <x:c r="I453" s="22"/>
+      <x:c r="J453" s="22" t="str">
+        <x:v>วันที่และเวลาที่ soft-delete</x:v>
+      </x:c>
+      <x:c r="K453" s="22"/>
+      <x:c r="L453" s="22"/>
+      <x:c r="M453" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N453" s="22"/>
+    </x:row>
+    <x:row r="454" ht="42" customHeight="1">
+      <x:c r="A454" s="22" t="str">
+        <x:v>export_jobs</x:v>
+      </x:c>
+      <x:c r="B454" s="22" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="C454" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="D454" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E454" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F454" s="22" t="str">
+        <x:v>AUTO_INCREMENT</x:v>
+      </x:c>
+      <x:c r="G454" s="22" t="str">
+        <x:v>PK</x:v>
+      </x:c>
+      <x:c r="H454" s="22"/>
+      <x:c r="I454" s="22" t="str">
+        <x:v>PRIMARY</x:v>
+      </x:c>
+      <x:c r="J454" s="22" t="str">
+        <x:v>รหัสภายในของรายการ</x:v>
+      </x:c>
+      <x:c r="K454" s="22"/>
+      <x:c r="L454" s="22"/>
+      <x:c r="M454" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N454" s="22"/>
+    </x:row>
+    <x:row r="455" ht="42" customHeight="1">
+      <x:c r="A455" s="22" t="str">
+        <x:v>export_jobs</x:v>
+      </x:c>
+      <x:c r="B455" s="22" t="str">
+        <x:v>job_type</x:v>
+      </x:c>
+      <x:c r="C455" s="22" t="str">
+        <x:v>VARCHAR(80)</x:v>
+      </x:c>
+      <x:c r="D455" s="22" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E455" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F455" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G455" s="22"/>
+      <x:c r="H455" s="22"/>
+      <x:c r="I455" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="J455" s="22" t="str">
+        <x:v>job type</x:v>
+      </x:c>
+      <x:c r="K455" s="22"/>
+      <x:c r="L455" s="22"/>
+      <x:c r="M455" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N455" s="22"/>
+    </x:row>
+    <x:row r="456" ht="42" customHeight="1">
+      <x:c r="A456" s="22" t="str">
+        <x:v>export_jobs</x:v>
+      </x:c>
+      <x:c r="B456" s="22" t="str">
+        <x:v>status</x:v>
+      </x:c>
+      <x:c r="C456" s="22" t="str">
+        <x:v>VARCHAR(40)</x:v>
+      </x:c>
+      <x:c r="D456" s="22" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E456" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F456" s="22" t="str">
+        <x:v>PENDING</x:v>
+      </x:c>
+      <x:c r="G456" s="22"/>
+      <x:c r="H456" s="22"/>
+      <x:c r="I456" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="J456" s="22" t="str">
+        <x:v>สถานะรายการ</x:v>
+      </x:c>
+      <x:c r="K456" s="22"/>
+      <x:c r="L456" s="22"/>
+      <x:c r="M456" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N456" s="22"/>
+    </x:row>
+    <x:row r="457" ht="42" customHeight="1">
+      <x:c r="A457" s="22" t="str">
+        <x:v>export_jobs</x:v>
+      </x:c>
+      <x:c r="B457" s="22" t="str">
+        <x:v>params</x:v>
+      </x:c>
+      <x:c r="C457" s="22" t="str">
+        <x:v>JSON</x:v>
+      </x:c>
+      <x:c r="D457" s="22"/>
+      <x:c r="E457" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F457" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G457" s="22"/>
+      <x:c r="H457" s="22"/>
+      <x:c r="I457" s="22"/>
+      <x:c r="J457" s="22" t="str">
+        <x:v>params</x:v>
+      </x:c>
+      <x:c r="K457" s="22"/>
+      <x:c r="L457" s="22" t="str">
+        <x:v>valid JSON</x:v>
+      </x:c>
+      <x:c r="M457" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N457" s="22"/>
+    </x:row>
+    <x:row r="458" ht="42" customHeight="1">
+      <x:c r="A458" s="22" t="str">
+        <x:v>export_jobs</x:v>
+      </x:c>
+      <x:c r="B458" s="22" t="str">
+        <x:v>result_json</x:v>
+      </x:c>
+      <x:c r="C458" s="22" t="str">
+        <x:v>JSON</x:v>
+      </x:c>
+      <x:c r="D458" s="22"/>
+      <x:c r="E458" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F458" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G458" s="22"/>
+      <x:c r="H458" s="22"/>
+      <x:c r="I458" s="22"/>
+      <x:c r="J458" s="22" t="str">
+        <x:v>result json</x:v>
+      </x:c>
+      <x:c r="K458" s="22"/>
+      <x:c r="L458" s="22" t="str">
+        <x:v>valid JSON</x:v>
+      </x:c>
+      <x:c r="M458" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N458" s="22"/>
+    </x:row>
+    <x:row r="459" ht="42" customHeight="1">
+      <x:c r="A459" s="22" t="str">
+        <x:v>export_jobs</x:v>
+      </x:c>
+      <x:c r="B459" s="22" t="str">
+        <x:v>file_name</x:v>
+      </x:c>
+      <x:c r="C459" s="22" t="str">
+        <x:v>VARCHAR(255)</x:v>
+      </x:c>
+      <x:c r="D459" s="22" t="n">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="E459" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F459" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G459" s="22"/>
+      <x:c r="H459" s="22"/>
+      <x:c r="I459" s="22"/>
+      <x:c r="J459" s="22" t="str">
+        <x:v>ชื่อไฟล์ในระบบ</x:v>
+      </x:c>
+      <x:c r="K459" s="22"/>
+      <x:c r="L459" s="22"/>
+      <x:c r="M459" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N459" s="22"/>
+    </x:row>
+    <x:row r="460" ht="42" customHeight="1">
+      <x:c r="A460" s="22" t="str">
+        <x:v>export_jobs</x:v>
+      </x:c>
+      <x:c r="B460" s="22" t="str">
+        <x:v>created_by</x:v>
+      </x:c>
+      <x:c r="C460" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="D460" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E460" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F460" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G460" s="22" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="H460" s="22" t="str">
+        <x:v>users.id</x:v>
+      </x:c>
+      <x:c r="I460" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="J460" s="22" t="str">
+        <x:v>ผู้สร้างรายการ</x:v>
+      </x:c>
+      <x:c r="K460" s="22"/>
+      <x:c r="L460" s="22"/>
+      <x:c r="M460" s="22" t="str">
+        <x:v>IDENTIFIER</x:v>
+      </x:c>
+      <x:c r="N460" s="22"/>
+    </x:row>
+    <x:row r="461" ht="42" customHeight="1">
+      <x:c r="A461" s="22" t="str">
+        <x:v>export_jobs</x:v>
+      </x:c>
+      <x:c r="B461" s="22" t="str">
+        <x:v>started_at</x:v>
+      </x:c>
+      <x:c r="C461" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="D461" s="22"/>
+      <x:c r="E461" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F461" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G461" s="22"/>
+      <x:c r="H461" s="22"/>
+      <x:c r="I461" s="22"/>
+      <x:c r="J461" s="22" t="str">
+        <x:v>started at</x:v>
+      </x:c>
+      <x:c r="K461" s="22"/>
+      <x:c r="L461" s="22"/>
+      <x:c r="M461" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N461" s="22"/>
+    </x:row>
+    <x:row r="462" ht="42" customHeight="1">
+      <x:c r="A462" s="22" t="str">
+        <x:v>export_jobs</x:v>
+      </x:c>
+      <x:c r="B462" s="22" t="str">
+        <x:v>completed_at</x:v>
+      </x:c>
+      <x:c r="C462" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="D462" s="22"/>
+      <x:c r="E462" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F462" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G462" s="22"/>
+      <x:c r="H462" s="22"/>
+      <x:c r="I462" s="22"/>
+      <x:c r="J462" s="22" t="str">
+        <x:v>completed at</x:v>
+      </x:c>
+      <x:c r="K462" s="22"/>
+      <x:c r="L462" s="22"/>
+      <x:c r="M462" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N462" s="22"/>
+    </x:row>
+    <x:row r="463" ht="42" customHeight="1">
+      <x:c r="A463" s="22" t="str">
+        <x:v>export_jobs</x:v>
+      </x:c>
+      <x:c r="B463" s="22" t="str">
+        <x:v>created_at</x:v>
+      </x:c>
+      <x:c r="C463" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="D463" s="22"/>
+      <x:c r="E463" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F463" s="22" t="str">
+        <x:v>CURRENT_TIMESTAMP(3)</x:v>
+      </x:c>
+      <x:c r="G463" s="22"/>
+      <x:c r="H463" s="22"/>
+      <x:c r="I463" s="22"/>
+      <x:c r="J463" s="22" t="str">
+        <x:v>วันที่และเวลาที่สร้างรายการ</x:v>
+      </x:c>
+      <x:c r="K463" s="22"/>
+      <x:c r="L463" s="22"/>
+      <x:c r="M463" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N463" s="22"/>
+    </x:row>
+    <x:row r="464" ht="42" customHeight="1">
+      <x:c r="A464" s="22" t="str">
+        <x:v>export_jobs</x:v>
+      </x:c>
+      <x:c r="B464" s="22" t="str">
+        <x:v>updated_at</x:v>
+      </x:c>
+      <x:c r="C464" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="D464" s="22"/>
+      <x:c r="E464" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F464" s="22" t="str">
+        <x:v>CURRENT_TIMESTAMP(3)</x:v>
+      </x:c>
+      <x:c r="G464" s="22"/>
+      <x:c r="H464" s="22"/>
+      <x:c r="I464" s="22"/>
+      <x:c r="J464" s="22" t="str">
+        <x:v>วันที่และเวลาที่แก้ไขล่าสุด</x:v>
+      </x:c>
+      <x:c r="K464" s="22"/>
+      <x:c r="L464" s="22"/>
+      <x:c r="M464" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N464" s="22"/>
+    </x:row>
+    <x:row r="465" ht="42" customHeight="1">
+      <x:c r="A465" s="22" t="str">
+        <x:v>notification_preferences</x:v>
+      </x:c>
+      <x:c r="B465" s="22" t="str">
+        <x:v>user_id</x:v>
+      </x:c>
+      <x:c r="C465" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="D465" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E465" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F465" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G465" s="22" t="str">
+        <x:v>PK</x:v>
+      </x:c>
+      <x:c r="H465" s="22" t="str">
+        <x:v>users.id</x:v>
+      </x:c>
+      <x:c r="I465" s="22" t="str">
+        <x:v>PRIMARY</x:v>
+      </x:c>
+      <x:c r="J465" s="22" t="str">
+        <x:v>ผู้ใช้งานเจ้าของรายการ</x:v>
+      </x:c>
+      <x:c r="K465" s="22"/>
+      <x:c r="L465" s="22"/>
+      <x:c r="M465" s="22" t="str">
+        <x:v>IDENTIFIER</x:v>
+      </x:c>
+      <x:c r="N465" s="22"/>
+    </x:row>
+    <x:row r="466" ht="42" customHeight="1">
+      <x:c r="A466" s="22" t="str">
+        <x:v>notification_preferences</x:v>
+      </x:c>
+      <x:c r="B466" s="22" t="str">
+        <x:v>email_enabled</x:v>
+      </x:c>
+      <x:c r="C466" s="22" t="str">
+        <x:v>TINYINT(1)</x:v>
+      </x:c>
+      <x:c r="D466" s="22" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E466" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F466" s="22" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G466" s="22"/>
+      <x:c r="H466" s="22"/>
+      <x:c r="I466" s="22"/>
+      <x:c r="J466" s="22" t="str">
+        <x:v>email enabled</x:v>
+      </x:c>
+      <x:c r="K466" s="22"/>
+      <x:c r="L466" s="22"/>
+      <x:c r="M466" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N466" s="22"/>
+    </x:row>
+    <x:row r="467" ht="42" customHeight="1">
+      <x:c r="A467" s="22" t="str">
+        <x:v>notification_preferences</x:v>
+      </x:c>
+      <x:c r="B467" s="22" t="str">
+        <x:v>in_app_enabled</x:v>
+      </x:c>
+      <x:c r="C467" s="22" t="str">
+        <x:v>TINYINT(1)</x:v>
+      </x:c>
+      <x:c r="D467" s="22" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E467" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F467" s="22" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G467" s="22"/>
+      <x:c r="H467" s="22"/>
+      <x:c r="I467" s="22"/>
+      <x:c r="J467" s="22" t="str">
+        <x:v>in app enabled</x:v>
+      </x:c>
+      <x:c r="K467" s="22"/>
+      <x:c r="L467" s="22"/>
+      <x:c r="M467" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N467" s="22"/>
+    </x:row>
+    <x:row r="468" ht="42" customHeight="1">
+      <x:c r="A468" s="22" t="str">
+        <x:v>notification_preferences</x:v>
+      </x:c>
+      <x:c r="B468" s="22" t="str">
+        <x:v>preferences_json</x:v>
+      </x:c>
+      <x:c r="C468" s="22" t="str">
+        <x:v>JSON</x:v>
+      </x:c>
+      <x:c r="D468" s="22"/>
+      <x:c r="E468" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F468" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G468" s="22"/>
+      <x:c r="H468" s="22"/>
+      <x:c r="I468" s="22"/>
+      <x:c r="J468" s="22" t="str">
+        <x:v>การตั้งค่าเพิ่มเติมแบบ JSON</x:v>
+      </x:c>
+      <x:c r="K468" s="22"/>
+      <x:c r="L468" s="22" t="str">
+        <x:v>valid JSON</x:v>
+      </x:c>
+      <x:c r="M468" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N468" s="22"/>
+    </x:row>
+    <x:row r="469" ht="42" customHeight="1">
+      <x:c r="A469" s="22" t="str">
+        <x:v>notification_preferences</x:v>
+      </x:c>
+      <x:c r="B469" s="22" t="str">
+        <x:v>created_at</x:v>
+      </x:c>
+      <x:c r="C469" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="D469" s="22"/>
+      <x:c r="E469" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F469" s="22" t="str">
+        <x:v>CURRENT_TIMESTAMP(3)</x:v>
+      </x:c>
+      <x:c r="G469" s="22"/>
+      <x:c r="H469" s="22"/>
+      <x:c r="I469" s="22"/>
+      <x:c r="J469" s="22" t="str">
+        <x:v>วันที่และเวลาที่สร้างรายการ</x:v>
+      </x:c>
+      <x:c r="K469" s="22"/>
+      <x:c r="L469" s="22"/>
+      <x:c r="M469" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N469" s="22"/>
+    </x:row>
+    <x:row r="470" ht="42" customHeight="1">
+      <x:c r="A470" s="22" t="str">
+        <x:v>notification_preferences</x:v>
+      </x:c>
+      <x:c r="B470" s="22" t="str">
+        <x:v>updated_at</x:v>
+      </x:c>
+      <x:c r="C470" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="D470" s="22"/>
+      <x:c r="E470" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F470" s="22" t="str">
+        <x:v>CURRENT_TIMESTAMP(3)</x:v>
+      </x:c>
+      <x:c r="G470" s="22"/>
+      <x:c r="H470" s="22"/>
+      <x:c r="I470" s="22"/>
+      <x:c r="J470" s="22" t="str">
+        <x:v>วันที่และเวลาที่แก้ไขล่าสุด</x:v>
+      </x:c>
+      <x:c r="K470" s="22"/>
+      <x:c r="L470" s="22"/>
+      <x:c r="M470" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N470" s="22"/>
+    </x:row>
+    <x:row r="471" ht="42" customHeight="1">
+      <x:c r="A471" s="22" t="str">
+        <x:v>assessment_attachments</x:v>
+      </x:c>
+      <x:c r="B471" s="22" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="C471" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="D471" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E471" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F471" s="22" t="str">
+        <x:v>AUTO_INCREMENT</x:v>
+      </x:c>
+      <x:c r="G471" s="22" t="str">
+        <x:v>PK</x:v>
+      </x:c>
+      <x:c r="H471" s="22"/>
+      <x:c r="I471" s="22" t="str">
+        <x:v>PRIMARY</x:v>
+      </x:c>
+      <x:c r="J471" s="22" t="str">
+        <x:v>รหัสภายในของรายการ</x:v>
+      </x:c>
+      <x:c r="K471" s="22"/>
+      <x:c r="L471" s="22"/>
+      <x:c r="M471" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N471" s="22"/>
+    </x:row>
+    <x:row r="472" ht="42" customHeight="1">
+      <x:c r="A472" s="22" t="str">
+        <x:v>assessment_attachments</x:v>
+      </x:c>
+      <x:c r="B472" s="22" t="str">
+        <x:v>assessment_run_id</x:v>
+      </x:c>
+      <x:c r="C472" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="D472" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E472" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F472" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G472" s="22" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="H472" s="22" t="str">
+        <x:v>assessment_runs.id</x:v>
+      </x:c>
+      <x:c r="I472" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="J472" s="22" t="str">
+        <x:v>Assessment run ที่แนบไฟล์</x:v>
+      </x:c>
+      <x:c r="K472" s="22"/>
+      <x:c r="L472" s="22"/>
+      <x:c r="M472" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N472" s="22"/>
+    </x:row>
+    <x:row r="473" ht="42" customHeight="1">
+      <x:c r="A473" s="22" t="str">
+        <x:v>assessment_attachments</x:v>
+      </x:c>
+      <x:c r="B473" s="22" t="str">
+        <x:v>media_asset_id</x:v>
+      </x:c>
+      <x:c r="C473" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="D473" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E473" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F473" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G473" s="22" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="H473" s="22" t="str">
+        <x:v>media_assets.id</x:v>
+      </x:c>
+      <x:c r="I473" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="J473" s="22" t="str">
+        <x:v>ไฟล์ metadata ที่อ้างอิง</x:v>
+      </x:c>
+      <x:c r="K473" s="22"/>
+      <x:c r="L473" s="22"/>
+      <x:c r="M473" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N473" s="22"/>
+    </x:row>
+    <x:row r="474" ht="42" customHeight="1">
+      <x:c r="A474" s="22" t="str">
+        <x:v>assessment_attachments</x:v>
+      </x:c>
+      <x:c r="B474" s="22" t="str">
+        <x:v>file_url</x:v>
+      </x:c>
+      <x:c r="C474" s="22" t="str">
+        <x:v>VARCHAR(1000)</x:v>
+      </x:c>
+      <x:c r="D474" s="22" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="E474" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F474" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G474" s="22"/>
+      <x:c r="H474" s="22"/>
+      <x:c r="I474" s="22"/>
+      <x:c r="J474" s="22" t="str">
+        <x:v>file url</x:v>
+      </x:c>
+      <x:c r="K474" s="22"/>
+      <x:c r="L474" s="22"/>
+      <x:c r="M474" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N474" s="22"/>
+    </x:row>
+    <x:row r="475" ht="42" customHeight="1">
+      <x:c r="A475" s="22" t="str">
+        <x:v>assessment_attachments</x:v>
+      </x:c>
+      <x:c r="B475" s="22" t="str">
+        <x:v>attachment_type</x:v>
+      </x:c>
+      <x:c r="C475" s="22" t="str">
+        <x:v>VARCHAR(80)</x:v>
+      </x:c>
+      <x:c r="D475" s="22" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E475" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F475" s="22" t="str">
+        <x:v>EVIDENCE</x:v>
+      </x:c>
+      <x:c r="G475" s="22"/>
+      <x:c r="H475" s="22"/>
+      <x:c r="I475" s="22"/>
+      <x:c r="J475" s="22" t="str">
+        <x:v>attachment type</x:v>
+      </x:c>
+      <x:c r="K475" s="22"/>
+      <x:c r="L475" s="22"/>
+      <x:c r="M475" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N475" s="22"/>
+    </x:row>
+    <x:row r="476" ht="42" customHeight="1">
+      <x:c r="A476" s="22" t="str">
+        <x:v>assessment_attachments</x:v>
+      </x:c>
+      <x:c r="B476" s="22" t="str">
+        <x:v>metadata</x:v>
+      </x:c>
+      <x:c r="C476" s="22" t="str">
+        <x:v>JSON</x:v>
+      </x:c>
+      <x:c r="D476" s="22"/>
+      <x:c r="E476" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F476" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G476" s="22"/>
+      <x:c r="H476" s="22"/>
+      <x:c r="I476" s="22"/>
+      <x:c r="J476" s="22" t="str">
+        <x:v>ข้อมูลประกอบแบบ JSON</x:v>
+      </x:c>
+      <x:c r="K476" s="22"/>
+      <x:c r="L476" s="22" t="str">
+        <x:v>valid JSON</x:v>
+      </x:c>
+      <x:c r="M476" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N476" s="22"/>
+    </x:row>
+    <x:row r="477" ht="42" customHeight="1">
+      <x:c r="A477" s="22" t="str">
+        <x:v>assessment_attachments</x:v>
+      </x:c>
+      <x:c r="B477" s="22" t="str">
+        <x:v>created_by</x:v>
+      </x:c>
+      <x:c r="C477" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="D477" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E477" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F477" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G477" s="22" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="H477" s="22" t="str">
+        <x:v>users.id</x:v>
+      </x:c>
+      <x:c r="I477" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="J477" s="22" t="str">
+        <x:v>ผู้สร้างรายการ</x:v>
+      </x:c>
+      <x:c r="K477" s="22"/>
+      <x:c r="L477" s="22"/>
+      <x:c r="M477" s="22" t="str">
+        <x:v>IDENTIFIER</x:v>
+      </x:c>
+      <x:c r="N477" s="22"/>
+    </x:row>
+    <x:row r="478" ht="42" customHeight="1">
+      <x:c r="A478" s="22" t="str">
+        <x:v>assessment_attachments</x:v>
+      </x:c>
+      <x:c r="B478" s="22" t="str">
+        <x:v>created_at</x:v>
+      </x:c>
+      <x:c r="C478" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="D478" s="22"/>
+      <x:c r="E478" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F478" s="22" t="str">
+        <x:v>CURRENT_TIMESTAMP(3)</x:v>
+      </x:c>
+      <x:c r="G478" s="22"/>
+      <x:c r="H478" s="22"/>
+      <x:c r="I478" s="22"/>
+      <x:c r="J478" s="22" t="str">
+        <x:v>วันที่และเวลาที่สร้างรายการ</x:v>
+      </x:c>
+      <x:c r="K478" s="22"/>
+      <x:c r="L478" s="22"/>
+      <x:c r="M478" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N478" s="22"/>
+    </x:row>
+    <x:row r="479" ht="42" customHeight="1">
+      <x:c r="A479" s="22" t="str">
+        <x:v>assessment_attachments</x:v>
+      </x:c>
+      <x:c r="B479" s="22" t="str">
+        <x:v>updated_at</x:v>
+      </x:c>
+      <x:c r="C479" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="D479" s="22"/>
+      <x:c r="E479" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F479" s="22" t="str">
+        <x:v>CURRENT_TIMESTAMP(3)</x:v>
+      </x:c>
+      <x:c r="G479" s="22"/>
+      <x:c r="H479" s="22"/>
+      <x:c r="I479" s="22"/>
+      <x:c r="J479" s="22" t="str">
+        <x:v>วันที่และเวลาที่แก้ไขล่าสุด</x:v>
+      </x:c>
+      <x:c r="K479" s="22"/>
+      <x:c r="L479" s="22"/>
+      <x:c r="M479" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N479" s="22"/>
+    </x:row>
+    <x:row r="480" ht="42" customHeight="1">
+      <x:c r="A480" s="22" t="str">
+        <x:v>corrective_action_comments</x:v>
+      </x:c>
+      <x:c r="B480" s="22" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="C480" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="D480" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E480" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F480" s="22" t="str">
+        <x:v>AUTO_INCREMENT</x:v>
+      </x:c>
+      <x:c r="G480" s="22" t="str">
+        <x:v>PK</x:v>
+      </x:c>
+      <x:c r="H480" s="22"/>
+      <x:c r="I480" s="22" t="str">
+        <x:v>PRIMARY</x:v>
+      </x:c>
+      <x:c r="J480" s="22" t="str">
+        <x:v>รหัสภายในของรายการ</x:v>
+      </x:c>
+      <x:c r="K480" s="22"/>
+      <x:c r="L480" s="22"/>
+      <x:c r="M480" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N480" s="22"/>
+    </x:row>
+    <x:row r="481" ht="42" customHeight="1">
+      <x:c r="A481" s="22" t="str">
+        <x:v>corrective_action_comments</x:v>
+      </x:c>
+      <x:c r="B481" s="22" t="str">
+        <x:v>corrective_action_id</x:v>
+      </x:c>
+      <x:c r="C481" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="D481" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E481" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F481" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G481" s="22" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="H481" s="22" t="str">
+        <x:v>corrective_actions.id</x:v>
+      </x:c>
+      <x:c r="I481" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="J481" s="22" t="str">
+        <x:v>Corrective action ที่แสดงความคิดเห็น</x:v>
+      </x:c>
+      <x:c r="K481" s="22"/>
+      <x:c r="L481" s="22"/>
+      <x:c r="M481" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N481" s="22"/>
+    </x:row>
+    <x:row r="482" ht="42" customHeight="1">
+      <x:c r="A482" s="22" t="str">
+        <x:v>corrective_action_comments</x:v>
+      </x:c>
+      <x:c r="B482" s="22" t="str">
+        <x:v>author_id</x:v>
+      </x:c>
+      <x:c r="C482" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="D482" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E482" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F482" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G482" s="22" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="H482" s="22" t="str">
+        <x:v>users.id</x:v>
+      </x:c>
+      <x:c r="I482" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="J482" s="22" t="str">
+        <x:v>ผู้เขียนความคิดเห็น</x:v>
+      </x:c>
+      <x:c r="K482" s="22"/>
+      <x:c r="L482" s="22"/>
+      <x:c r="M482" s="22" t="str">
+        <x:v>IDENTIFIER</x:v>
+      </x:c>
+      <x:c r="N482" s="22"/>
+    </x:row>
+    <x:row r="483" ht="42" customHeight="1">
+      <x:c r="A483" s="22" t="str">
+        <x:v>corrective_action_comments</x:v>
+      </x:c>
+      <x:c r="B483" s="22" t="str">
+        <x:v>content</x:v>
+      </x:c>
+      <x:c r="C483" s="22" t="str">
+        <x:v>TEXT</x:v>
+      </x:c>
+      <x:c r="D483" s="22" t="n">
+        <x:v>65535</x:v>
+      </x:c>
+      <x:c r="E483" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F483" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G483" s="22"/>
+      <x:c r="H483" s="22"/>
+      <x:c r="I483" s="22"/>
+      <x:c r="J483" s="22" t="str">
+        <x:v>ข้อความความคิดเห็น</x:v>
+      </x:c>
+      <x:c r="K483" s="22"/>
+      <x:c r="L483" s="22"/>
+      <x:c r="M483" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N483" s="22"/>
+    </x:row>
+    <x:row r="484" ht="42" customHeight="1">
+      <x:c r="A484" s="22" t="str">
+        <x:v>corrective_action_comments</x:v>
+      </x:c>
+      <x:c r="B484" s="22" t="str">
+        <x:v>metadata</x:v>
+      </x:c>
+      <x:c r="C484" s="22" t="str">
+        <x:v>JSON</x:v>
+      </x:c>
+      <x:c r="D484" s="22"/>
+      <x:c r="E484" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F484" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G484" s="22"/>
+      <x:c r="H484" s="22"/>
+      <x:c r="I484" s="22"/>
+      <x:c r="J484" s="22" t="str">
+        <x:v>ข้อมูลประกอบแบบ JSON</x:v>
+      </x:c>
+      <x:c r="K484" s="22"/>
+      <x:c r="L484" s="22" t="str">
+        <x:v>valid JSON</x:v>
+      </x:c>
+      <x:c r="M484" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N484" s="22"/>
+    </x:row>
+    <x:row r="485" ht="42" customHeight="1">
+      <x:c r="A485" s="22" t="str">
+        <x:v>corrective_action_comments</x:v>
+      </x:c>
+      <x:c r="B485" s="22" t="str">
+        <x:v>created_at</x:v>
+      </x:c>
+      <x:c r="C485" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="D485" s="22"/>
+      <x:c r="E485" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F485" s="22" t="str">
+        <x:v>CURRENT_TIMESTAMP(3)</x:v>
+      </x:c>
+      <x:c r="G485" s="22"/>
+      <x:c r="H485" s="22"/>
+      <x:c r="I485" s="22"/>
+      <x:c r="J485" s="22" t="str">
+        <x:v>วันที่และเวลาที่สร้างรายการ</x:v>
+      </x:c>
+      <x:c r="K485" s="22"/>
+      <x:c r="L485" s="22"/>
+      <x:c r="M485" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N485" s="22"/>
+    </x:row>
+    <x:row r="486" ht="42" customHeight="1">
+      <x:c r="A486" s="22" t="str">
+        <x:v>corrective_action_comments</x:v>
+      </x:c>
+      <x:c r="B486" s="22" t="str">
+        <x:v>updated_at</x:v>
+      </x:c>
+      <x:c r="C486" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="D486" s="22"/>
+      <x:c r="E486" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F486" s="22" t="str">
+        <x:v>CURRENT_TIMESTAMP(3)</x:v>
+      </x:c>
+      <x:c r="G486" s="22"/>
+      <x:c r="H486" s="22"/>
+      <x:c r="I486" s="22"/>
+      <x:c r="J486" s="22" t="str">
+        <x:v>วันที่และเวลาที่แก้ไขล่าสุด</x:v>
+      </x:c>
+      <x:c r="K486" s="22"/>
+      <x:c r="L486" s="22"/>
+      <x:c r="M486" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N486" s="22"/>
+    </x:row>
+    <x:row r="487" ht="42" customHeight="1">
+      <x:c r="A487" s="22" t="str">
+        <x:v>corrective_action_comments</x:v>
+      </x:c>
+      <x:c r="B487" s="22" t="str">
+        <x:v>deleted_at</x:v>
+      </x:c>
+      <x:c r="C487" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="D487" s="22"/>
+      <x:c r="E487" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F487" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G487" s="22"/>
+      <x:c r="H487" s="22"/>
+      <x:c r="I487" s="22"/>
+      <x:c r="J487" s="22" t="str">
+        <x:v>วันที่และเวลาที่ soft-delete</x:v>
+      </x:c>
+      <x:c r="K487" s="22"/>
+      <x:c r="L487" s="22"/>
+      <x:c r="M487" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N487" s="22"/>
+    </x:row>
+    <x:row r="488" ht="42" customHeight="1">
+      <x:c r="A488" s="22" t="str">
+        <x:v>archived_notifications</x:v>
+      </x:c>
+      <x:c r="B488" s="22" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="C488" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="D488" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E488" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F488" s="22" t="str">
+        <x:v>AUTO_INCREMENT</x:v>
+      </x:c>
+      <x:c r="G488" s="22" t="str">
+        <x:v>PK</x:v>
+      </x:c>
+      <x:c r="H488" s="22"/>
+      <x:c r="I488" s="22" t="str">
+        <x:v>PRIMARY</x:v>
+      </x:c>
+      <x:c r="J488" s="22" t="str">
+        <x:v>รหัสภายในของรายการ</x:v>
+      </x:c>
+      <x:c r="K488" s="22"/>
+      <x:c r="L488" s="22"/>
+      <x:c r="M488" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N488" s="22"/>
+    </x:row>
+    <x:row r="489" ht="42" customHeight="1">
+      <x:c r="A489" s="22" t="str">
+        <x:v>archived_notifications</x:v>
+      </x:c>
+      <x:c r="B489" s="22" t="str">
+        <x:v>notification_id</x:v>
+      </x:c>
+      <x:c r="C489" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="D489" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E489" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F489" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G489" s="22"/>
+      <x:c r="H489" s="22"/>
+      <x:c r="I489" s="22"/>
+      <x:c r="J489" s="22" t="str">
+        <x:v>Notification ต้นฉบับ</x:v>
+      </x:c>
+      <x:c r="K489" s="22"/>
+      <x:c r="L489" s="22"/>
+      <x:c r="M489" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N489" s="22"/>
+    </x:row>
+    <x:row r="490" ht="42" customHeight="1">
+      <x:c r="A490" s="22" t="str">
+        <x:v>archived_notifications</x:v>
+      </x:c>
+      <x:c r="B490" s="22" t="str">
+        <x:v>user_id</x:v>
+      </x:c>
+      <x:c r="C490" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="D490" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E490" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F490" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G490" s="22" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="H490" s="22" t="str">
+        <x:v>users.id</x:v>
+      </x:c>
+      <x:c r="I490" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="J490" s="22" t="str">
+        <x:v>ผู้ใช้งานเจ้าของรายการ</x:v>
+      </x:c>
+      <x:c r="K490" s="22"/>
+      <x:c r="L490" s="22"/>
+      <x:c r="M490" s="22" t="str">
+        <x:v>IDENTIFIER</x:v>
+      </x:c>
+      <x:c r="N490" s="22"/>
+    </x:row>
+    <x:row r="491" ht="42" customHeight="1">
+      <x:c r="A491" s="22" t="str">
+        <x:v>archived_notifications</x:v>
+      </x:c>
+      <x:c r="B491" s="22" t="str">
+        <x:v>notification_type</x:v>
+      </x:c>
+      <x:c r="C491" s="22" t="str">
+        <x:v>VARCHAR(80)</x:v>
+      </x:c>
+      <x:c r="D491" s="22" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E491" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F491" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G491" s="22"/>
+      <x:c r="H491" s="22"/>
+      <x:c r="I491" s="22"/>
+      <x:c r="J491" s="22" t="str">
+        <x:v>notification type</x:v>
+      </x:c>
+      <x:c r="K491" s="22"/>
+      <x:c r="L491" s="22"/>
+      <x:c r="M491" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N491" s="22"/>
+    </x:row>
+    <x:row r="492" ht="42" customHeight="1">
+      <x:c r="A492" s="22" t="str">
+        <x:v>archived_notifications</x:v>
+      </x:c>
+      <x:c r="B492" s="22" t="str">
+        <x:v>title</x:v>
+      </x:c>
+      <x:c r="C492" s="22" t="str">
+        <x:v>VARCHAR(255)</x:v>
+      </x:c>
+      <x:c r="D492" s="22" t="n">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="E492" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F492" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G492" s="22"/>
+      <x:c r="H492" s="22"/>
+      <x:c r="I492" s="22"/>
+      <x:c r="J492" s="22" t="str">
+        <x:v>ชื่อหรือหัวข้อ</x:v>
+      </x:c>
+      <x:c r="K492" s="22"/>
+      <x:c r="L492" s="22"/>
+      <x:c r="M492" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N492" s="22"/>
+    </x:row>
+    <x:row r="493" ht="42" customHeight="1">
+      <x:c r="A493" s="22" t="str">
+        <x:v>archived_notifications</x:v>
+      </x:c>
+      <x:c r="B493" s="22" t="str">
+        <x:v>body</x:v>
+      </x:c>
+      <x:c r="C493" s="22" t="str">
+        <x:v>TEXT</x:v>
+      </x:c>
+      <x:c r="D493" s="22" t="n">
+        <x:v>65535</x:v>
+      </x:c>
+      <x:c r="E493" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F493" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G493" s="22"/>
+      <x:c r="H493" s="22"/>
+      <x:c r="I493" s="22"/>
+      <x:c r="J493" s="22" t="str">
+        <x:v>body</x:v>
+      </x:c>
+      <x:c r="K493" s="22"/>
+      <x:c r="L493" s="22"/>
+      <x:c r="M493" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N493" s="22"/>
+    </x:row>
+    <x:row r="494" ht="42" customHeight="1">
+      <x:c r="A494" s="22" t="str">
+        <x:v>archived_notifications</x:v>
+      </x:c>
+      <x:c r="B494" s="22" t="str">
+        <x:v>read_at</x:v>
+      </x:c>
+      <x:c r="C494" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="D494" s="22"/>
+      <x:c r="E494" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F494" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G494" s="22"/>
+      <x:c r="H494" s="22"/>
+      <x:c r="I494" s="22"/>
+      <x:c r="J494" s="22" t="str">
+        <x:v>read at</x:v>
+      </x:c>
+      <x:c r="K494" s="22"/>
+      <x:c r="L494" s="22"/>
+      <x:c r="M494" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N494" s="22"/>
+    </x:row>
+    <x:row r="495" ht="42" customHeight="1">
+      <x:c r="A495" s="22" t="str">
+        <x:v>archived_notifications</x:v>
+      </x:c>
+      <x:c r="B495" s="22" t="str">
+        <x:v>original_created_at</x:v>
+      </x:c>
+      <x:c r="C495" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="D495" s="22"/>
+      <x:c r="E495" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F495" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G495" s="22"/>
+      <x:c r="H495" s="22"/>
+      <x:c r="I495" s="22"/>
+      <x:c r="J495" s="22" t="str">
+        <x:v>original created at</x:v>
+      </x:c>
+      <x:c r="K495" s="22"/>
+      <x:c r="L495" s="22"/>
+      <x:c r="M495" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N495" s="22"/>
+    </x:row>
+    <x:row r="496" ht="42" customHeight="1">
+      <x:c r="A496" s="22" t="str">
+        <x:v>archived_notifications</x:v>
+      </x:c>
+      <x:c r="B496" s="22" t="str">
+        <x:v>archived_at</x:v>
+      </x:c>
+      <x:c r="C496" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="D496" s="22"/>
+      <x:c r="E496" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F496" s="22" t="str">
+        <x:v>CURRENT_TIMESTAMP(3)</x:v>
+      </x:c>
+      <x:c r="G496" s="22"/>
+      <x:c r="H496" s="22"/>
+      <x:c r="I496" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="J496" s="22" t="str">
+        <x:v>วันที่และเวลาที่ archive</x:v>
+      </x:c>
+      <x:c r="K496" s="22"/>
+      <x:c r="L496" s="22"/>
+      <x:c r="M496" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N496" s="22"/>
+    </x:row>
+    <x:row r="497" ht="42" customHeight="1">
+      <x:c r="A497" s="22" t="str">
+        <x:v>safety_settings</x:v>
+      </x:c>
+      <x:c r="B497" s="22" t="str">
+        <x:v>setting_key</x:v>
+      </x:c>
+      <x:c r="C497" s="22" t="str">
+        <x:v>VARCHAR(120)</x:v>
+      </x:c>
+      <x:c r="D497" s="22" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="E497" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F497" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G497" s="22" t="str">
+        <x:v>PK</x:v>
+      </x:c>
+      <x:c r="H497" s="22"/>
+      <x:c r="I497" s="22" t="str">
+        <x:v>PRIMARY</x:v>
+      </x:c>
+      <x:c r="J497" s="22" t="str">
+        <x:v>คีย์ค่าตั้งค่าระบบ</x:v>
+      </x:c>
+      <x:c r="K497" s="22"/>
+      <x:c r="L497" s="22"/>
+      <x:c r="M497" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N497" s="22"/>
+    </x:row>
+    <x:row r="498" ht="42" customHeight="1">
+      <x:c r="A498" s="22" t="str">
+        <x:v>safety_settings</x:v>
+      </x:c>
+      <x:c r="B498" s="22" t="str">
+        <x:v>setting_value</x:v>
+      </x:c>
+      <x:c r="C498" s="22" t="str">
+        <x:v>JSON</x:v>
+      </x:c>
+      <x:c r="D498" s="22"/>
+      <x:c r="E498" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F498" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G498" s="22"/>
+      <x:c r="H498" s="22"/>
+      <x:c r="I498" s="22"/>
+      <x:c r="J498" s="22" t="str">
+        <x:v>ค่าตั้งค่าระบบแบบ JSON</x:v>
+      </x:c>
+      <x:c r="K498" s="22"/>
+      <x:c r="L498" s="22" t="str">
+        <x:v>valid JSON</x:v>
+      </x:c>
+      <x:c r="M498" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N498" s="22"/>
+    </x:row>
+    <x:row r="499" ht="42" customHeight="1">
+      <x:c r="A499" s="22" t="str">
+        <x:v>safety_settings</x:v>
+      </x:c>
+      <x:c r="B499" s="22" t="str">
+        <x:v>updated_by</x:v>
+      </x:c>
+      <x:c r="C499" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="D499" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E499" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="F499" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="G499" s="22" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="H499" s="22" t="str">
+        <x:v>users.id</x:v>
+      </x:c>
+      <x:c r="I499" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="J499" s="22" t="str">
+        <x:v>ผู้แก้ไขค่าล่าสุด</x:v>
+      </x:c>
+      <x:c r="K499" s="22"/>
+      <x:c r="L499" s="22"/>
+      <x:c r="M499" s="22" t="str">
+        <x:v>IDENTIFIER</x:v>
+      </x:c>
+      <x:c r="N499" s="22"/>
+    </x:row>
+    <x:row r="500" ht="42" customHeight="1">
+      <x:c r="A500" s="22" t="str">
+        <x:v>safety_settings</x:v>
+      </x:c>
+      <x:c r="B500" s="22" t="str">
+        <x:v>created_at</x:v>
+      </x:c>
+      <x:c r="C500" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="D500" s="22"/>
+      <x:c r="E500" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F500" s="22" t="str">
+        <x:v>CURRENT_TIMESTAMP(3)</x:v>
+      </x:c>
+      <x:c r="G500" s="22"/>
+      <x:c r="H500" s="22"/>
+      <x:c r="I500" s="22"/>
+      <x:c r="J500" s="22" t="str">
+        <x:v>วันที่และเวลาที่สร้างรายการ</x:v>
+      </x:c>
+      <x:c r="K500" s="22"/>
+      <x:c r="L500" s="22"/>
+      <x:c r="M500" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N500" s="22"/>
+    </x:row>
+    <x:row r="501" ht="42" customHeight="1">
+      <x:c r="A501" s="22" t="str">
+        <x:v>safety_settings</x:v>
+      </x:c>
+      <x:c r="B501" s="22" t="str">
+        <x:v>updated_at</x:v>
+      </x:c>
+      <x:c r="C501" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="D501" s="22"/>
+      <x:c r="E501" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="F501" s="22" t="str">
+        <x:v>CURRENT_TIMESTAMP(3)</x:v>
+      </x:c>
+      <x:c r="G501" s="22"/>
+      <x:c r="H501" s="22"/>
+      <x:c r="I501" s="22"/>
+      <x:c r="J501" s="22" t="str">
+        <x:v>วันที่และเวลาที่แก้ไขล่าสุด</x:v>
+      </x:c>
+      <x:c r="K501" s="22"/>
+      <x:c r="L501" s="22"/>
+      <x:c r="M501" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N501" s="22"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:N1"/>
@@ -41256,7 +44243,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43d6836bba644b98"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree8fbe49d72f4620"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -41831,8 +44818,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02538b5e01994605"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a6ead9354c44b97"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe912a8709d345d1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5507835ec377462a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -42320,8 +45307,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2dc4d7923fa48b1"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9847d01f6e94c81"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf371a7bb954b4905"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R71d51fbd5da243aa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -42805,8 +45792,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5151105170484dea"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdeb64a9f9ed94601"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb3e085d597249a0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc46c6374ce1d4720"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -42849,7 +45836,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>Shared | Shared | Critical | Audit trail ของการเข้าถึงและแก้ไขข้อมูลสำคัญ</x:v>
+        <x:v>Shared | Shared | Critical | Audit trail เท่านั้น ไม่ใช่ที่เก็บข้อมูลธุรกรรมของ feature</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -42864,6 +45851,21 @@
       <x:c r="L2" s="7"/>
       <x:c r="M2" s="7"/>
     </x:row>
+    <x:row r="3">
+      <x:c r="A3"/>
+      <x:c r="B3"/>
+      <x:c r="C3"/>
+      <x:c r="D3"/>
+      <x:c r="E3"/>
+      <x:c r="F3"/>
+      <x:c r="G3"/>
+      <x:c r="H3"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
+      <x:c r="M3"/>
+    </x:row>
     <x:row r="4">
       <x:c r="A4" s="15" t="str">
         <x:v>table_name</x:v>
@@ -42889,13 +45891,18 @@
       <x:c r="H4" s="11" t="str">
         <x:v>Critical</x:v>
       </x:c>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
+      <x:c r="M4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="15" t="str">
         <x:v>purpose_th</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>Audit trail ของการเข้าถึงและแก้ไขข้อมูลสำคัญ</x:v>
+        <x:v>Audit trail ของการเข้าถึงและแก้ไขข้อมูลสำคัญ; ห้ามใช้เป็น primary storage</x:v>
       </x:c>
       <x:c r="C5" s="15" t="str">
         <x:v>primary_key</x:v>
@@ -42909,8 +45916,28 @@
       <x:c r="F5" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="G5" s="15" t="str"/>
-      <x:c r="H5" s="11" t="str"/>
+      <x:c r="G5" s="15"/>
+      <x:c r="H5" s="11"/>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
+      <x:c r="M5"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6"/>
+      <x:c r="B6"/>
+      <x:c r="C6"/>
+      <x:c r="D6"/>
+      <x:c r="E6"/>
+      <x:c r="F6"/>
+      <x:c r="G6"/>
+      <x:c r="H6"/>
+      <x:c r="I6"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
+      <x:c r="M6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="16" t="str">
@@ -42929,6 +45956,21 @@
       <x:c r="L7" s="16"/>
       <x:c r="M7" s="16"/>
     </x:row>
+    <x:row r="8">
+      <x:c r="A8"/>
+      <x:c r="B8"/>
+      <x:c r="C8"/>
+      <x:c r="D8"/>
+      <x:c r="E8"/>
+      <x:c r="F8"/>
+      <x:c r="G8"/>
+      <x:c r="H8"/>
+      <x:c r="I8"/>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
+      <x:c r="M8"/>
+    </x:row>
     <x:row r="9" ht="30" customHeight="1">
       <x:c r="A9" s="14" t="str">
         <x:v>column_name</x:v>
@@ -43254,6 +46296,21 @@
         <x:v>NONE</x:v>
       </x:c>
       <x:c r="M18" s="11"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
+      <x:c r="I19"/>
+      <x:c r="J19"/>
+      <x:c r="K19"/>
+      <x:c r="L19"/>
+      <x:c r="M19"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="16" t="str">
@@ -43265,6 +46322,12 @@
       <x:c r="E20" s="16"/>
       <x:c r="F20" s="16"/>
       <x:c r="G20" s="16"/>
+      <x:c r="H20"/>
+      <x:c r="I20"/>
+      <x:c r="J20"/>
+      <x:c r="K20"/>
+      <x:c r="L20"/>
+      <x:c r="M20"/>
     </x:row>
     <x:row r="21" ht="30" customHeight="1">
       <x:c r="A21" s="14" t="str">
@@ -43288,6 +46351,12 @@
       <x:c r="G21" s="14" t="str">
         <x:v>description_th</x:v>
       </x:c>
+      <x:c r="H21"/>
+      <x:c r="I21"/>
+      <x:c r="J21"/>
+      <x:c r="K21"/>
+      <x:c r="L21"/>
+      <x:c r="M21"/>
     </x:row>
     <x:row r="22" ht="44" customHeight="1">
       <x:c r="A22" s="11" t="str">
@@ -43311,6 +46380,12 @@
       <x:c r="G22" s="11" t="str">
         <x:v>audit_logs.actor_user_id อ้างอิง users.id</x:v>
       </x:c>
+      <x:c r="H22"/>
+      <x:c r="I22"/>
+      <x:c r="J22"/>
+      <x:c r="K22"/>
+      <x:c r="L22"/>
+      <x:c r="M22"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -43321,8 +46396,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc35f2c960d254656"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0aae4c40a7fc4f0f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reff3f1cdaa2641b8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R803e5d724a154a1d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44421,8 +47496,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R960ed4cf0e26428e"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41effabf928f43b4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63bcaf7866e74b41"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6597bcc80c7848b0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45899,8 +48974,8 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R83f36250c33d47d1"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93f0f8215a9b41f3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a737ba2b2294f81"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9af204b998dc45a4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46913,9 +49988,2147 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10b6b88d9f34429d"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42ca65e9277f4ff1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4fb63bcf2024408"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2928e49a3184c36"/>
   </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="36" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="22" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="30" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="22" t="str">
+        <x:v>safety_culture_events</x:v>
+      </x:c>
+      <x:c r="B1" s="22"/>
+      <x:c r="C1" s="22"/>
+      <x:c r="D1" s="22"/>
+      <x:c r="E1" s="22"/>
+      <x:c r="F1" s="22"/>
+      <x:c r="G1" s="22"/>
+      <x:c r="H1" s="22"/>
+      <x:c r="I1" s="22"/>
+      <x:c r="J1" s="22"/>
+      <x:c r="K1" s="22"/>
+      <x:c r="L1" s="22"/>
+      <x:c r="M1" s="22"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="22" t="str">
+        <x:v>Safety Culture | Phase 3 | High | กิจกรรมและแคมเปญ Safety Culture ที่บันทึกในฐานจริง</x:v>
+      </x:c>
+      <x:c r="B2" s="22"/>
+      <x:c r="C2" s="22"/>
+      <x:c r="D2" s="22"/>
+      <x:c r="E2" s="22"/>
+      <x:c r="F2" s="22"/>
+      <x:c r="G2" s="22"/>
+      <x:c r="H2" s="22"/>
+      <x:c r="I2" s="22"/>
+      <x:c r="J2" s="22"/>
+      <x:c r="K2" s="22"/>
+      <x:c r="L2" s="22"/>
+      <x:c r="M2" s="22"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="22"/>
+      <x:c r="B3" s="22"/>
+      <x:c r="C3" s="22"/>
+      <x:c r="D3" s="22"/>
+      <x:c r="E3" s="22"/>
+      <x:c r="F3" s="22"/>
+      <x:c r="G3" s="22"/>
+      <x:c r="H3" s="22"/>
+      <x:c r="I3" s="22"/>
+      <x:c r="J3" s="22"/>
+      <x:c r="K3" s="22"/>
+      <x:c r="L3" s="22"/>
+      <x:c r="M3" s="22"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="22" t="str">
+        <x:v>table_name</x:v>
+      </x:c>
+      <x:c r="B4" s="22" t="str">
+        <x:v>safety_culture_events</x:v>
+      </x:c>
+      <x:c r="C4" s="22" t="str">
+        <x:v>module</x:v>
+      </x:c>
+      <x:c r="D4" s="22" t="str">
+        <x:v>Safety Culture</x:v>
+      </x:c>
+      <x:c r="E4" s="22" t="str">
+        <x:v>phase</x:v>
+      </x:c>
+      <x:c r="F4" s="22" t="str">
+        <x:v>Phase 3</x:v>
+      </x:c>
+      <x:c r="G4" s="22" t="str">
+        <x:v>priority</x:v>
+      </x:c>
+      <x:c r="H4" s="22" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I4" s="22"/>
+      <x:c r="J4" s="22"/>
+      <x:c r="K4" s="22"/>
+      <x:c r="L4" s="22"/>
+      <x:c r="M4" s="22"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="22" t="str">
+        <x:v>purpose_th</x:v>
+      </x:c>
+      <x:c r="B5" s="22" t="str">
+        <x:v>กิจกรรมและแคมเปญ Safety Culture ที่บันทึกในฐานจริง</x:v>
+      </x:c>
+      <x:c r="C5" s="22" t="str">
+        <x:v>primary_key</x:v>
+      </x:c>
+      <x:c r="D5" s="22" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="E5" s="22" t="str">
+        <x:v>column_count</x:v>
+      </x:c>
+      <x:c r="F5" s="22" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G5" s="22"/>
+      <x:c r="H5" s="22"/>
+      <x:c r="I5" s="22"/>
+      <x:c r="J5" s="22"/>
+      <x:c r="K5" s="22"/>
+      <x:c r="L5" s="22"/>
+      <x:c r="M5" s="22"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="22"/>
+      <x:c r="B6" s="22"/>
+      <x:c r="C6" s="22"/>
+      <x:c r="D6" s="22"/>
+      <x:c r="E6" s="22"/>
+      <x:c r="F6" s="22"/>
+      <x:c r="G6" s="22"/>
+      <x:c r="H6" s="22"/>
+      <x:c r="I6" s="22"/>
+      <x:c r="J6" s="22"/>
+      <x:c r="K6" s="22"/>
+      <x:c r="L6" s="22"/>
+      <x:c r="M6" s="22"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="22" t="str">
+        <x:v>Column Dictionary</x:v>
+      </x:c>
+      <x:c r="B7" s="22"/>
+      <x:c r="C7" s="22"/>
+      <x:c r="D7" s="22"/>
+      <x:c r="E7" s="22"/>
+      <x:c r="F7" s="22"/>
+      <x:c r="G7" s="22"/>
+      <x:c r="H7" s="22"/>
+      <x:c r="I7" s="22"/>
+      <x:c r="J7" s="22"/>
+      <x:c r="K7" s="22"/>
+      <x:c r="L7" s="22"/>
+      <x:c r="M7" s="22"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="22"/>
+      <x:c r="B8" s="22"/>
+      <x:c r="C8" s="22"/>
+      <x:c r="D8" s="22"/>
+      <x:c r="E8" s="22"/>
+      <x:c r="F8" s="22"/>
+      <x:c r="G8" s="22"/>
+      <x:c r="H8" s="22"/>
+      <x:c r="I8" s="22"/>
+      <x:c r="J8" s="22"/>
+      <x:c r="K8" s="22"/>
+      <x:c r="L8" s="22"/>
+      <x:c r="M8" s="22"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="22" t="str">
+        <x:v>column_name</x:v>
+      </x:c>
+      <x:c r="B9" s="22" t="str">
+        <x:v>data_type</x:v>
+      </x:c>
+      <x:c r="C9" s="22" t="str">
+        <x:v>length</x:v>
+      </x:c>
+      <x:c r="D9" s="22" t="str">
+        <x:v>nullable</x:v>
+      </x:c>
+      <x:c r="E9" s="22" t="str">
+        <x:v>default_value</x:v>
+      </x:c>
+      <x:c r="F9" s="22" t="str">
+        <x:v>key_type</x:v>
+      </x:c>
+      <x:c r="G9" s="22" t="str">
+        <x:v>references</x:v>
+      </x:c>
+      <x:c r="H9" s="22" t="str">
+        <x:v>index_type</x:v>
+      </x:c>
+      <x:c r="I9" s="22" t="str">
+        <x:v>description_th</x:v>
+      </x:c>
+      <x:c r="J9" s="22" t="str">
+        <x:v>example_value</x:v>
+      </x:c>
+      <x:c r="K9" s="22" t="str">
+        <x:v>validation_rule</x:v>
+      </x:c>
+      <x:c r="L9" s="22" t="str">
+        <x:v>personal_data_classification</x:v>
+      </x:c>
+      <x:c r="M9" s="22" t="str">
+        <x:v>notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="22" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="B10" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="C10" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D10" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E10" s="22" t="str">
+        <x:v>AUTO_INCREMENT</x:v>
+      </x:c>
+      <x:c r="F10" s="22" t="str">
+        <x:v>PK</x:v>
+      </x:c>
+      <x:c r="G10" s="22"/>
+      <x:c r="H10" s="22" t="str">
+        <x:v>PRIMARY</x:v>
+      </x:c>
+      <x:c r="I10" s="22" t="str">
+        <x:v>รหัสภายในของรายการ</x:v>
+      </x:c>
+      <x:c r="J10" s="22"/>
+      <x:c r="K10" s="22"/>
+      <x:c r="L10" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M10" s="22"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="22" t="str">
+        <x:v>title</x:v>
+      </x:c>
+      <x:c r="B11" s="22" t="str">
+        <x:v>VARCHAR(255)</x:v>
+      </x:c>
+      <x:c r="C11" s="22" t="n">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="D11" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E11" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F11" s="22"/>
+      <x:c r="G11" s="22"/>
+      <x:c r="H11" s="22"/>
+      <x:c r="I11" s="22" t="str">
+        <x:v>ชื่อหรือหัวข้อ</x:v>
+      </x:c>
+      <x:c r="J11" s="22"/>
+      <x:c r="K11" s="22"/>
+      <x:c r="L11" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M11" s="22"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="22" t="str">
+        <x:v>description</x:v>
+      </x:c>
+      <x:c r="B12" s="22" t="str">
+        <x:v>TEXT</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="n">
+        <x:v>65535</x:v>
+      </x:c>
+      <x:c r="D12" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E12" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F12" s="22"/>
+      <x:c r="G12" s="22"/>
+      <x:c r="H12" s="22"/>
+      <x:c r="I12" s="22" t="str">
+        <x:v>รายละเอียด</x:v>
+      </x:c>
+      <x:c r="J12" s="22"/>
+      <x:c r="K12" s="22"/>
+      <x:c r="L12" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M12" s="22"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="22" t="str">
+        <x:v>event_start_at</x:v>
+      </x:c>
+      <x:c r="B13" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="C13" s="22"/>
+      <x:c r="D13" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E13" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F13" s="22"/>
+      <x:c r="G13" s="22"/>
+      <x:c r="H13" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="I13" s="22" t="str">
+        <x:v>event start at</x:v>
+      </x:c>
+      <x:c r="J13" s="22"/>
+      <x:c r="K13" s="22"/>
+      <x:c r="L13" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M13" s="22"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="22" t="str">
+        <x:v>event_end_at</x:v>
+      </x:c>
+      <x:c r="B14" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="C14" s="22"/>
+      <x:c r="D14" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E14" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F14" s="22"/>
+      <x:c r="G14" s="22"/>
+      <x:c r="H14" s="22"/>
+      <x:c r="I14" s="22" t="str">
+        <x:v>event end at</x:v>
+      </x:c>
+      <x:c r="J14" s="22"/>
+      <x:c r="K14" s="22"/>
+      <x:c r="L14" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M14" s="22"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="22" t="str">
+        <x:v>location_text</x:v>
+      </x:c>
+      <x:c r="B15" s="22" t="str">
+        <x:v>VARCHAR(255)</x:v>
+      </x:c>
+      <x:c r="C15" s="22" t="n">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="D15" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E15" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F15" s="22"/>
+      <x:c r="G15" s="22"/>
+      <x:c r="H15" s="22"/>
+      <x:c r="I15" s="22" t="str">
+        <x:v>location text</x:v>
+      </x:c>
+      <x:c r="J15" s="22"/>
+      <x:c r="K15" s="22"/>
+      <x:c r="L15" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M15" s="22"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="22" t="str">
+        <x:v>status</x:v>
+      </x:c>
+      <x:c r="B16" s="22" t="str">
+        <x:v>VARCHAR(40)</x:v>
+      </x:c>
+      <x:c r="C16" s="22" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D16" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E16" s="22" t="str">
+        <x:v>DRAFT</x:v>
+      </x:c>
+      <x:c r="F16" s="22"/>
+      <x:c r="G16" s="22"/>
+      <x:c r="H16" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="I16" s="22" t="str">
+        <x:v>สถานะรายการ</x:v>
+      </x:c>
+      <x:c r="J16" s="22"/>
+      <x:c r="K16" s="22"/>
+      <x:c r="L16" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M16" s="22"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="22" t="str">
+        <x:v>metadata</x:v>
+      </x:c>
+      <x:c r="B17" s="22" t="str">
+        <x:v>JSON</x:v>
+      </x:c>
+      <x:c r="C17" s="22"/>
+      <x:c r="D17" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E17" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F17" s="22"/>
+      <x:c r="G17" s="22"/>
+      <x:c r="H17" s="22"/>
+      <x:c r="I17" s="22" t="str">
+        <x:v>ข้อมูลประกอบแบบ JSON</x:v>
+      </x:c>
+      <x:c r="J17" s="22"/>
+      <x:c r="K17" s="22" t="str">
+        <x:v>valid JSON</x:v>
+      </x:c>
+      <x:c r="L17" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M17" s="22"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="22" t="str">
+        <x:v>created_by</x:v>
+      </x:c>
+      <x:c r="B18" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="C18" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D18" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E18" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F18" s="22" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="G18" s="22" t="str">
+        <x:v>users.id</x:v>
+      </x:c>
+      <x:c r="H18" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="I18" s="22" t="str">
+        <x:v>ผู้สร้างรายการ</x:v>
+      </x:c>
+      <x:c r="J18" s="22"/>
+      <x:c r="K18" s="22"/>
+      <x:c r="L18" s="22" t="str">
+        <x:v>IDENTIFIER</x:v>
+      </x:c>
+      <x:c r="M18" s="22"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="22" t="str">
+        <x:v>created_at</x:v>
+      </x:c>
+      <x:c r="B19" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="C19" s="22"/>
+      <x:c r="D19" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E19" s="22" t="str">
+        <x:v>CURRENT_TIMESTAMP(3)</x:v>
+      </x:c>
+      <x:c r="F19" s="22"/>
+      <x:c r="G19" s="22"/>
+      <x:c r="H19" s="22"/>
+      <x:c r="I19" s="22" t="str">
+        <x:v>วันที่และเวลาที่สร้างรายการ</x:v>
+      </x:c>
+      <x:c r="J19" s="22"/>
+      <x:c r="K19" s="22"/>
+      <x:c r="L19" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M19" s="22"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="22" t="str">
+        <x:v>updated_at</x:v>
+      </x:c>
+      <x:c r="B20" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="C20" s="22"/>
+      <x:c r="D20" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E20" s="22" t="str">
+        <x:v>CURRENT_TIMESTAMP(3)</x:v>
+      </x:c>
+      <x:c r="F20" s="22"/>
+      <x:c r="G20" s="22"/>
+      <x:c r="H20" s="22"/>
+      <x:c r="I20" s="22" t="str">
+        <x:v>วันที่และเวลาที่แก้ไขล่าสุด</x:v>
+      </x:c>
+      <x:c r="J20" s="22"/>
+      <x:c r="K20" s="22"/>
+      <x:c r="L20" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M20" s="22"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="22" t="str">
+        <x:v>deleted_at</x:v>
+      </x:c>
+      <x:c r="B21" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="C21" s="22"/>
+      <x:c r="D21" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E21" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F21" s="22"/>
+      <x:c r="G21" s="22"/>
+      <x:c r="H21" s="22"/>
+      <x:c r="I21" s="22" t="str">
+        <x:v>วันที่และเวลาที่ soft-delete</x:v>
+      </x:c>
+      <x:c r="J21" s="22"/>
+      <x:c r="K21" s="22"/>
+      <x:c r="L21" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M21" s="22"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="22"/>
+      <x:c r="B22" s="22"/>
+      <x:c r="C22" s="22"/>
+      <x:c r="D22" s="22"/>
+      <x:c r="E22" s="22"/>
+      <x:c r="F22" s="22"/>
+      <x:c r="G22" s="22"/>
+      <x:c r="H22" s="22"/>
+      <x:c r="I22" s="22"/>
+      <x:c r="J22" s="22"/>
+      <x:c r="K22" s="22"/>
+      <x:c r="L22" s="22"/>
+      <x:c r="M22" s="22"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="22" t="str">
+        <x:v>Relationships ที่เกี่ยวข้อง</x:v>
+      </x:c>
+      <x:c r="B23" s="22"/>
+      <x:c r="C23" s="22"/>
+      <x:c r="D23" s="22"/>
+      <x:c r="E23" s="22"/>
+      <x:c r="F23" s="22"/>
+      <x:c r="G23" s="22"/>
+      <x:c r="H23" s="22"/>
+      <x:c r="I23" s="22"/>
+      <x:c r="J23" s="22"/>
+      <x:c r="K23" s="22"/>
+      <x:c r="L23" s="22"/>
+      <x:c r="M23" s="22"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="22" t="str">
+        <x:v>parent_table</x:v>
+      </x:c>
+      <x:c r="B24" s="22" t="str">
+        <x:v>child_table</x:v>
+      </x:c>
+      <x:c r="C24" s="22" t="str">
+        <x:v>foreign_key</x:v>
+      </x:c>
+      <x:c r="D24" s="22" t="str">
+        <x:v>cardinality</x:v>
+      </x:c>
+      <x:c r="E24" s="22" t="str">
+        <x:v>on_delete</x:v>
+      </x:c>
+      <x:c r="F24" s="22" t="str">
+        <x:v>on_update</x:v>
+      </x:c>
+      <x:c r="G24" s="22" t="str">
+        <x:v>description_th</x:v>
+      </x:c>
+      <x:c r="H24" s="22"/>
+      <x:c r="I24" s="22"/>
+      <x:c r="J24" s="22"/>
+      <x:c r="K24" s="22"/>
+      <x:c r="L24" s="22"/>
+      <x:c r="M24" s="22"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="22" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="B25" s="22" t="str">
+        <x:v>safety_culture_events</x:v>
+      </x:c>
+      <x:c r="C25" s="22" t="str">
+        <x:v>created_by</x:v>
+      </x:c>
+      <x:c r="D25" s="22" t="str">
+        <x:v>1 : Many</x:v>
+      </x:c>
+      <x:c r="E25" s="22" t="str">
+        <x:v>SET NULL</x:v>
+      </x:c>
+      <x:c r="F25" s="22" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G25" s="22" t="str">
+        <x:v>safety_culture_events.created_by อ้างอิง users.id</x:v>
+      </x:c>
+      <x:c r="H25" s="22"/>
+      <x:c r="I25" s="22"/>
+      <x:c r="J25" s="22"/>
+      <x:c r="K25" s="22"/>
+      <x:c r="L25" s="22"/>
+      <x:c r="M25" s="22"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="36" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="22" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="30" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="22" t="str">
+        <x:v>media_assets</x:v>
+      </x:c>
+      <x:c r="B1" s="22"/>
+      <x:c r="C1" s="22"/>
+      <x:c r="D1" s="22"/>
+      <x:c r="E1" s="22"/>
+      <x:c r="F1" s="22"/>
+      <x:c r="G1" s="22"/>
+      <x:c r="H1" s="22"/>
+      <x:c r="I1" s="22"/>
+      <x:c r="J1" s="22"/>
+      <x:c r="K1" s="22"/>
+      <x:c r="L1" s="22"/>
+      <x:c r="M1" s="22"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="22" t="str">
+        <x:v>Shared | Shared | Critical | Metadata ของไฟล์จริง พร้อม owner/link โดยไม่เก็บ base64 ในข้อมูลธุรกิจ</x:v>
+      </x:c>
+      <x:c r="B2" s="22"/>
+      <x:c r="C2" s="22"/>
+      <x:c r="D2" s="22"/>
+      <x:c r="E2" s="22"/>
+      <x:c r="F2" s="22"/>
+      <x:c r="G2" s="22"/>
+      <x:c r="H2" s="22"/>
+      <x:c r="I2" s="22"/>
+      <x:c r="J2" s="22"/>
+      <x:c r="K2" s="22"/>
+      <x:c r="L2" s="22"/>
+      <x:c r="M2" s="22"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="22"/>
+      <x:c r="B3" s="22"/>
+      <x:c r="C3" s="22"/>
+      <x:c r="D3" s="22"/>
+      <x:c r="E3" s="22"/>
+      <x:c r="F3" s="22"/>
+      <x:c r="G3" s="22"/>
+      <x:c r="H3" s="22"/>
+      <x:c r="I3" s="22"/>
+      <x:c r="J3" s="22"/>
+      <x:c r="K3" s="22"/>
+      <x:c r="L3" s="22"/>
+      <x:c r="M3" s="22"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="22" t="str">
+        <x:v>table_name</x:v>
+      </x:c>
+      <x:c r="B4" s="22" t="str">
+        <x:v>media_assets</x:v>
+      </x:c>
+      <x:c r="C4" s="22" t="str">
+        <x:v>module</x:v>
+      </x:c>
+      <x:c r="D4" s="22" t="str">
+        <x:v>Shared</x:v>
+      </x:c>
+      <x:c r="E4" s="22" t="str">
+        <x:v>phase</x:v>
+      </x:c>
+      <x:c r="F4" s="22" t="str">
+        <x:v>Shared</x:v>
+      </x:c>
+      <x:c r="G4" s="22" t="str">
+        <x:v>priority</x:v>
+      </x:c>
+      <x:c r="H4" s="22" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="I4" s="22"/>
+      <x:c r="J4" s="22"/>
+      <x:c r="K4" s="22"/>
+      <x:c r="L4" s="22"/>
+      <x:c r="M4" s="22"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="22" t="str">
+        <x:v>purpose_th</x:v>
+      </x:c>
+      <x:c r="B5" s="22" t="str">
+        <x:v>Metadata ของไฟล์จริง พร้อม owner/link โดยไม่เก็บ base64 ในข้อมูลธุรกิจ</x:v>
+      </x:c>
+      <x:c r="C5" s="22" t="str">
+        <x:v>primary_key</x:v>
+      </x:c>
+      <x:c r="D5" s="22" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="E5" s="22" t="str">
+        <x:v>column_count</x:v>
+      </x:c>
+      <x:c r="F5" s="22" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G5" s="22"/>
+      <x:c r="H5" s="22"/>
+      <x:c r="I5" s="22"/>
+      <x:c r="J5" s="22"/>
+      <x:c r="K5" s="22"/>
+      <x:c r="L5" s="22"/>
+      <x:c r="M5" s="22"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="22"/>
+      <x:c r="B6" s="22"/>
+      <x:c r="C6" s="22"/>
+      <x:c r="D6" s="22"/>
+      <x:c r="E6" s="22"/>
+      <x:c r="F6" s="22"/>
+      <x:c r="G6" s="22"/>
+      <x:c r="H6" s="22"/>
+      <x:c r="I6" s="22"/>
+      <x:c r="J6" s="22"/>
+      <x:c r="K6" s="22"/>
+      <x:c r="L6" s="22"/>
+      <x:c r="M6" s="22"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="22" t="str">
+        <x:v>Column Dictionary</x:v>
+      </x:c>
+      <x:c r="B7" s="22"/>
+      <x:c r="C7" s="22"/>
+      <x:c r="D7" s="22"/>
+      <x:c r="E7" s="22"/>
+      <x:c r="F7" s="22"/>
+      <x:c r="G7" s="22"/>
+      <x:c r="H7" s="22"/>
+      <x:c r="I7" s="22"/>
+      <x:c r="J7" s="22"/>
+      <x:c r="K7" s="22"/>
+      <x:c r="L7" s="22"/>
+      <x:c r="M7" s="22"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="22"/>
+      <x:c r="B8" s="22"/>
+      <x:c r="C8" s="22"/>
+      <x:c r="D8" s="22"/>
+      <x:c r="E8" s="22"/>
+      <x:c r="F8" s="22"/>
+      <x:c r="G8" s="22"/>
+      <x:c r="H8" s="22"/>
+      <x:c r="I8" s="22"/>
+      <x:c r="J8" s="22"/>
+      <x:c r="K8" s="22"/>
+      <x:c r="L8" s="22"/>
+      <x:c r="M8" s="22"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="22" t="str">
+        <x:v>column_name</x:v>
+      </x:c>
+      <x:c r="B9" s="22" t="str">
+        <x:v>data_type</x:v>
+      </x:c>
+      <x:c r="C9" s="22" t="str">
+        <x:v>length</x:v>
+      </x:c>
+      <x:c r="D9" s="22" t="str">
+        <x:v>nullable</x:v>
+      </x:c>
+      <x:c r="E9" s="22" t="str">
+        <x:v>default_value</x:v>
+      </x:c>
+      <x:c r="F9" s="22" t="str">
+        <x:v>key_type</x:v>
+      </x:c>
+      <x:c r="G9" s="22" t="str">
+        <x:v>references</x:v>
+      </x:c>
+      <x:c r="H9" s="22" t="str">
+        <x:v>index_type</x:v>
+      </x:c>
+      <x:c r="I9" s="22" t="str">
+        <x:v>description_th</x:v>
+      </x:c>
+      <x:c r="J9" s="22" t="str">
+        <x:v>example_value</x:v>
+      </x:c>
+      <x:c r="K9" s="22" t="str">
+        <x:v>validation_rule</x:v>
+      </x:c>
+      <x:c r="L9" s="22" t="str">
+        <x:v>personal_data_classification</x:v>
+      </x:c>
+      <x:c r="M9" s="22" t="str">
+        <x:v>notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="22" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="B10" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="C10" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D10" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E10" s="22" t="str">
+        <x:v>AUTO_INCREMENT</x:v>
+      </x:c>
+      <x:c r="F10" s="22" t="str">
+        <x:v>PK</x:v>
+      </x:c>
+      <x:c r="G10" s="22"/>
+      <x:c r="H10" s="22" t="str">
+        <x:v>PRIMARY</x:v>
+      </x:c>
+      <x:c r="I10" s="22" t="str">
+        <x:v>รหัสภายในของรายการ</x:v>
+      </x:c>
+      <x:c r="J10" s="22"/>
+      <x:c r="K10" s="22"/>
+      <x:c r="L10" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M10" s="22"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="22" t="str">
+        <x:v>file_name</x:v>
+      </x:c>
+      <x:c r="B11" s="22" t="str">
+        <x:v>VARCHAR(255)</x:v>
+      </x:c>
+      <x:c r="C11" s="22" t="n">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="D11" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E11" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F11" s="22"/>
+      <x:c r="G11" s="22"/>
+      <x:c r="H11" s="22"/>
+      <x:c r="I11" s="22" t="str">
+        <x:v>ชื่อไฟล์ในระบบ</x:v>
+      </x:c>
+      <x:c r="J11" s="22"/>
+      <x:c r="K11" s="22"/>
+      <x:c r="L11" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M11" s="22"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="22" t="str">
+        <x:v>original_name</x:v>
+      </x:c>
+      <x:c r="B12" s="22" t="str">
+        <x:v>VARCHAR(255)</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="n">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="D12" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E12" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F12" s="22"/>
+      <x:c r="G12" s="22"/>
+      <x:c r="H12" s="22"/>
+      <x:c r="I12" s="22" t="str">
+        <x:v>ชื่อไฟล์ต้นฉบับ</x:v>
+      </x:c>
+      <x:c r="J12" s="22"/>
+      <x:c r="K12" s="22"/>
+      <x:c r="L12" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M12" s="22"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="22" t="str">
+        <x:v>mime_type</x:v>
+      </x:c>
+      <x:c r="B13" s="22" t="str">
+        <x:v>VARCHAR(120)</x:v>
+      </x:c>
+      <x:c r="C13" s="22" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D13" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E13" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F13" s="22"/>
+      <x:c r="G13" s="22"/>
+      <x:c r="H13" s="22"/>
+      <x:c r="I13" s="22" t="str">
+        <x:v>ชนิด MIME ของไฟล์</x:v>
+      </x:c>
+      <x:c r="J13" s="22"/>
+      <x:c r="K13" s="22"/>
+      <x:c r="L13" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M13" s="22"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="22" t="str">
+        <x:v>size_bytes</x:v>
+      </x:c>
+      <x:c r="B14" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="C14" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D14" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E14" s="22" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F14" s="22"/>
+      <x:c r="G14" s="22"/>
+      <x:c r="H14" s="22"/>
+      <x:c r="I14" s="22" t="str">
+        <x:v>ขนาดไฟล์เป็นไบต์</x:v>
+      </x:c>
+      <x:c r="J14" s="22"/>
+      <x:c r="K14" s="22"/>
+      <x:c r="L14" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M14" s="22"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="22" t="str">
+        <x:v>status</x:v>
+      </x:c>
+      <x:c r="B15" s="22" t="str">
+        <x:v>VARCHAR(40)</x:v>
+      </x:c>
+      <x:c r="C15" s="22" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D15" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E15" s="22" t="str">
+        <x:v>READY</x:v>
+      </x:c>
+      <x:c r="F15" s="22"/>
+      <x:c r="G15" s="22"/>
+      <x:c r="H15" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="I15" s="22" t="str">
+        <x:v>สถานะรายการ</x:v>
+      </x:c>
+      <x:c r="J15" s="22"/>
+      <x:c r="K15" s="22"/>
+      <x:c r="L15" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M15" s="22"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="22" t="str">
+        <x:v>module</x:v>
+      </x:c>
+      <x:c r="B16" s="22" t="str">
+        <x:v>VARCHAR(80)</x:v>
+      </x:c>
+      <x:c r="C16" s="22" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D16" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E16" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F16" s="22"/>
+      <x:c r="G16" s="22"/>
+      <x:c r="H16" s="22"/>
+      <x:c r="I16" s="22" t="str">
+        <x:v>module</x:v>
+      </x:c>
+      <x:c r="J16" s="22"/>
+      <x:c r="K16" s="22"/>
+      <x:c r="L16" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M16" s="22"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="22" t="str">
+        <x:v>owner_type</x:v>
+      </x:c>
+      <x:c r="B17" s="22" t="str">
+        <x:v>VARCHAR(80)</x:v>
+      </x:c>
+      <x:c r="C17" s="22" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D17" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E17" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F17" s="22"/>
+      <x:c r="G17" s="22"/>
+      <x:c r="H17" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="I17" s="22" t="str">
+        <x:v>ประเภทข้อมูลธุรกิจที่เป็นเจ้าของไฟล์</x:v>
+      </x:c>
+      <x:c r="J17" s="22"/>
+      <x:c r="K17" s="22"/>
+      <x:c r="L17" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M17" s="22"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="22" t="str">
+        <x:v>owner_id</x:v>
+      </x:c>
+      <x:c r="B18" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="C18" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D18" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E18" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F18" s="22"/>
+      <x:c r="G18" s="22"/>
+      <x:c r="H18" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="I18" s="22" t="str">
+        <x:v>รหัสข้อมูลธุรกิจที่เป็นเจ้าของไฟล์</x:v>
+      </x:c>
+      <x:c r="J18" s="22"/>
+      <x:c r="K18" s="22"/>
+      <x:c r="L18" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M18" s="22"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="22" t="str">
+        <x:v>link_type</x:v>
+      </x:c>
+      <x:c r="B19" s="22" t="str">
+        <x:v>VARCHAR(80)</x:v>
+      </x:c>
+      <x:c r="C19" s="22" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D19" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E19" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F19" s="22"/>
+      <x:c r="G19" s="22"/>
+      <x:c r="H19" s="22"/>
+      <x:c r="I19" s="22" t="str">
+        <x:v>ประเภทความสัมพันธ์ของไฟล์</x:v>
+      </x:c>
+      <x:c r="J19" s="22"/>
+      <x:c r="K19" s="22"/>
+      <x:c r="L19" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M19" s="22"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="22" t="str">
+        <x:v>upload_mode</x:v>
+      </x:c>
+      <x:c r="B20" s="22" t="str">
+        <x:v>VARCHAR(40)</x:v>
+      </x:c>
+      <x:c r="C20" s="22" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D20" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E20" s="22" t="str">
+        <x:v>server</x:v>
+      </x:c>
+      <x:c r="F20" s="22"/>
+      <x:c r="G20" s="22"/>
+      <x:c r="H20" s="22"/>
+      <x:c r="I20" s="22" t="str">
+        <x:v>upload mode</x:v>
+      </x:c>
+      <x:c r="J20" s="22"/>
+      <x:c r="K20" s="22"/>
+      <x:c r="L20" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M20" s="22"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="22" t="str">
+        <x:v>storage_path</x:v>
+      </x:c>
+      <x:c r="B21" s="22" t="str">
+        <x:v>VARCHAR(1000)</x:v>
+      </x:c>
+      <x:c r="C21" s="22" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="D21" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E21" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F21" s="22"/>
+      <x:c r="G21" s="22"/>
+      <x:c r="H21" s="22"/>
+      <x:c r="I21" s="22" t="str">
+        <x:v>ตำแหน่งไฟล์จริงใน storage/server</x:v>
+      </x:c>
+      <x:c r="J21" s="22"/>
+      <x:c r="K21" s="22"/>
+      <x:c r="L21" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M21" s="22" t="str">
+        <x:v>ไฟล์จริงอยู่นอก DB; DB เก็บ metadata เท่านั้น</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="22" t="str">
+        <x:v>public_url</x:v>
+      </x:c>
+      <x:c r="B22" s="22" t="str">
+        <x:v>VARCHAR(1000)</x:v>
+      </x:c>
+      <x:c r="C22" s="22" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="D22" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E22" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F22" s="22"/>
+      <x:c r="G22" s="22"/>
+      <x:c r="H22" s="22"/>
+      <x:c r="I22" s="22" t="str">
+        <x:v>URL สำหรับเข้าถึงไฟล์ตามสิทธิ์</x:v>
+      </x:c>
+      <x:c r="J22" s="22"/>
+      <x:c r="K22" s="22"/>
+      <x:c r="L22" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M22" s="22"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="22" t="str">
+        <x:v>metadata</x:v>
+      </x:c>
+      <x:c r="B23" s="22" t="str">
+        <x:v>JSON</x:v>
+      </x:c>
+      <x:c r="C23" s="22"/>
+      <x:c r="D23" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E23" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F23" s="22"/>
+      <x:c r="G23" s="22"/>
+      <x:c r="H23" s="22"/>
+      <x:c r="I23" s="22" t="str">
+        <x:v>ข้อมูลประกอบแบบ JSON</x:v>
+      </x:c>
+      <x:c r="J23" s="22"/>
+      <x:c r="K23" s="22" t="str">
+        <x:v>valid JSON</x:v>
+      </x:c>
+      <x:c r="L23" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M23" s="22"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="22" t="str">
+        <x:v>created_by</x:v>
+      </x:c>
+      <x:c r="B24" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="C24" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D24" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E24" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F24" s="22" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="G24" s="22" t="str">
+        <x:v>users.id</x:v>
+      </x:c>
+      <x:c r="H24" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="I24" s="22" t="str">
+        <x:v>ผู้สร้างรายการ</x:v>
+      </x:c>
+      <x:c r="J24" s="22"/>
+      <x:c r="K24" s="22"/>
+      <x:c r="L24" s="22" t="str">
+        <x:v>IDENTIFIER</x:v>
+      </x:c>
+      <x:c r="M24" s="22"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="22" t="str">
+        <x:v>created_at</x:v>
+      </x:c>
+      <x:c r="B25" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="C25" s="22"/>
+      <x:c r="D25" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E25" s="22" t="str">
+        <x:v>CURRENT_TIMESTAMP(3)</x:v>
+      </x:c>
+      <x:c r="F25" s="22"/>
+      <x:c r="G25" s="22"/>
+      <x:c r="H25" s="22"/>
+      <x:c r="I25" s="22" t="str">
+        <x:v>วันที่และเวลาที่สร้างรายการ</x:v>
+      </x:c>
+      <x:c r="J25" s="22"/>
+      <x:c r="K25" s="22"/>
+      <x:c r="L25" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M25" s="22"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="22" t="str">
+        <x:v>updated_at</x:v>
+      </x:c>
+      <x:c r="B26" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="C26" s="22"/>
+      <x:c r="D26" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E26" s="22" t="str">
+        <x:v>CURRENT_TIMESTAMP(3)</x:v>
+      </x:c>
+      <x:c r="F26" s="22"/>
+      <x:c r="G26" s="22"/>
+      <x:c r="H26" s="22"/>
+      <x:c r="I26" s="22" t="str">
+        <x:v>วันที่และเวลาที่แก้ไขล่าสุด</x:v>
+      </x:c>
+      <x:c r="J26" s="22"/>
+      <x:c r="K26" s="22"/>
+      <x:c r="L26" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M26" s="22"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="22" t="str">
+        <x:v>deleted_at</x:v>
+      </x:c>
+      <x:c r="B27" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="C27" s="22"/>
+      <x:c r="D27" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E27" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F27" s="22"/>
+      <x:c r="G27" s="22"/>
+      <x:c r="H27" s="22"/>
+      <x:c r="I27" s="22" t="str">
+        <x:v>วันที่และเวลาที่ soft-delete</x:v>
+      </x:c>
+      <x:c r="J27" s="22"/>
+      <x:c r="K27" s="22"/>
+      <x:c r="L27" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M27" s="22"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="22"/>
+      <x:c r="B28" s="22"/>
+      <x:c r="C28" s="22"/>
+      <x:c r="D28" s="22"/>
+      <x:c r="E28" s="22"/>
+      <x:c r="F28" s="22"/>
+      <x:c r="G28" s="22"/>
+      <x:c r="H28" s="22"/>
+      <x:c r="I28" s="22"/>
+      <x:c r="J28" s="22"/>
+      <x:c r="K28" s="22"/>
+      <x:c r="L28" s="22"/>
+      <x:c r="M28" s="22"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="22" t="str">
+        <x:v>Relationships ที่เกี่ยวข้อง</x:v>
+      </x:c>
+      <x:c r="B29" s="22"/>
+      <x:c r="C29" s="22"/>
+      <x:c r="D29" s="22"/>
+      <x:c r="E29" s="22"/>
+      <x:c r="F29" s="22"/>
+      <x:c r="G29" s="22"/>
+      <x:c r="H29" s="22"/>
+      <x:c r="I29" s="22"/>
+      <x:c r="J29" s="22"/>
+      <x:c r="K29" s="22"/>
+      <x:c r="L29" s="22"/>
+      <x:c r="M29" s="22"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="22" t="str">
+        <x:v>parent_table</x:v>
+      </x:c>
+      <x:c r="B30" s="22" t="str">
+        <x:v>child_table</x:v>
+      </x:c>
+      <x:c r="C30" s="22" t="str">
+        <x:v>foreign_key</x:v>
+      </x:c>
+      <x:c r="D30" s="22" t="str">
+        <x:v>cardinality</x:v>
+      </x:c>
+      <x:c r="E30" s="22" t="str">
+        <x:v>on_delete</x:v>
+      </x:c>
+      <x:c r="F30" s="22" t="str">
+        <x:v>on_update</x:v>
+      </x:c>
+      <x:c r="G30" s="22" t="str">
+        <x:v>description_th</x:v>
+      </x:c>
+      <x:c r="H30" s="22"/>
+      <x:c r="I30" s="22"/>
+      <x:c r="J30" s="22"/>
+      <x:c r="K30" s="22"/>
+      <x:c r="L30" s="22"/>
+      <x:c r="M30" s="22"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="22" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="B31" s="22" t="str">
+        <x:v>media_assets</x:v>
+      </x:c>
+      <x:c r="C31" s="22" t="str">
+        <x:v>created_by</x:v>
+      </x:c>
+      <x:c r="D31" s="22" t="str">
+        <x:v>1 : Many</x:v>
+      </x:c>
+      <x:c r="E31" s="22" t="str">
+        <x:v>SET NULL</x:v>
+      </x:c>
+      <x:c r="F31" s="22" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G31" s="22" t="str">
+        <x:v>media_assets.created_by อ้างอิง users.id</x:v>
+      </x:c>
+      <x:c r="H31" s="22"/>
+      <x:c r="I31" s="22"/>
+      <x:c r="J31" s="22"/>
+      <x:c r="K31" s="22"/>
+      <x:c r="L31" s="22"/>
+      <x:c r="M31" s="22"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="36" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="22" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="30" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="22" t="str">
+        <x:v>export_jobs</x:v>
+      </x:c>
+      <x:c r="B1" s="22"/>
+      <x:c r="C1" s="22"/>
+      <x:c r="D1" s="22"/>
+      <x:c r="E1" s="22"/>
+      <x:c r="F1" s="22"/>
+      <x:c r="G1" s="22"/>
+      <x:c r="H1" s="22"/>
+      <x:c r="I1" s="22"/>
+      <x:c r="J1" s="22"/>
+      <x:c r="K1" s="22"/>
+      <x:c r="L1" s="22"/>
+      <x:c r="M1" s="22"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="22" t="str">
+        <x:v>Reports | Shared | High | งาน export และผลลัพธ์ไฟล์จริงที่ตรวจสอบสถานะย้อนหลังได้</x:v>
+      </x:c>
+      <x:c r="B2" s="22"/>
+      <x:c r="C2" s="22"/>
+      <x:c r="D2" s="22"/>
+      <x:c r="E2" s="22"/>
+      <x:c r="F2" s="22"/>
+      <x:c r="G2" s="22"/>
+      <x:c r="H2" s="22"/>
+      <x:c r="I2" s="22"/>
+      <x:c r="J2" s="22"/>
+      <x:c r="K2" s="22"/>
+      <x:c r="L2" s="22"/>
+      <x:c r="M2" s="22"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="22"/>
+      <x:c r="B3" s="22"/>
+      <x:c r="C3" s="22"/>
+      <x:c r="D3" s="22"/>
+      <x:c r="E3" s="22"/>
+      <x:c r="F3" s="22"/>
+      <x:c r="G3" s="22"/>
+      <x:c r="H3" s="22"/>
+      <x:c r="I3" s="22"/>
+      <x:c r="J3" s="22"/>
+      <x:c r="K3" s="22"/>
+      <x:c r="L3" s="22"/>
+      <x:c r="M3" s="22"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="22" t="str">
+        <x:v>table_name</x:v>
+      </x:c>
+      <x:c r="B4" s="22" t="str">
+        <x:v>export_jobs</x:v>
+      </x:c>
+      <x:c r="C4" s="22" t="str">
+        <x:v>module</x:v>
+      </x:c>
+      <x:c r="D4" s="22" t="str">
+        <x:v>Reports</x:v>
+      </x:c>
+      <x:c r="E4" s="22" t="str">
+        <x:v>phase</x:v>
+      </x:c>
+      <x:c r="F4" s="22" t="str">
+        <x:v>Shared</x:v>
+      </x:c>
+      <x:c r="G4" s="22" t="str">
+        <x:v>priority</x:v>
+      </x:c>
+      <x:c r="H4" s="22" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I4" s="22"/>
+      <x:c r="J4" s="22"/>
+      <x:c r="K4" s="22"/>
+      <x:c r="L4" s="22"/>
+      <x:c r="M4" s="22"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="22" t="str">
+        <x:v>purpose_th</x:v>
+      </x:c>
+      <x:c r="B5" s="22" t="str">
+        <x:v>งาน export และผลลัพธ์ไฟล์จริงที่ตรวจสอบสถานะย้อนหลังได้</x:v>
+      </x:c>
+      <x:c r="C5" s="22" t="str">
+        <x:v>primary_key</x:v>
+      </x:c>
+      <x:c r="D5" s="22" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="E5" s="22" t="str">
+        <x:v>column_count</x:v>
+      </x:c>
+      <x:c r="F5" s="22" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G5" s="22"/>
+      <x:c r="H5" s="22"/>
+      <x:c r="I5" s="22"/>
+      <x:c r="J5" s="22"/>
+      <x:c r="K5" s="22"/>
+      <x:c r="L5" s="22"/>
+      <x:c r="M5" s="22"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="22"/>
+      <x:c r="B6" s="22"/>
+      <x:c r="C6" s="22"/>
+      <x:c r="D6" s="22"/>
+      <x:c r="E6" s="22"/>
+      <x:c r="F6" s="22"/>
+      <x:c r="G6" s="22"/>
+      <x:c r="H6" s="22"/>
+      <x:c r="I6" s="22"/>
+      <x:c r="J6" s="22"/>
+      <x:c r="K6" s="22"/>
+      <x:c r="L6" s="22"/>
+      <x:c r="M6" s="22"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="22" t="str">
+        <x:v>Column Dictionary</x:v>
+      </x:c>
+      <x:c r="B7" s="22"/>
+      <x:c r="C7" s="22"/>
+      <x:c r="D7" s="22"/>
+      <x:c r="E7" s="22"/>
+      <x:c r="F7" s="22"/>
+      <x:c r="G7" s="22"/>
+      <x:c r="H7" s="22"/>
+      <x:c r="I7" s="22"/>
+      <x:c r="J7" s="22"/>
+      <x:c r="K7" s="22"/>
+      <x:c r="L7" s="22"/>
+      <x:c r="M7" s="22"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="22"/>
+      <x:c r="B8" s="22"/>
+      <x:c r="C8" s="22"/>
+      <x:c r="D8" s="22"/>
+      <x:c r="E8" s="22"/>
+      <x:c r="F8" s="22"/>
+      <x:c r="G8" s="22"/>
+      <x:c r="H8" s="22"/>
+      <x:c r="I8" s="22"/>
+      <x:c r="J8" s="22"/>
+      <x:c r="K8" s="22"/>
+      <x:c r="L8" s="22"/>
+      <x:c r="M8" s="22"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="22" t="str">
+        <x:v>column_name</x:v>
+      </x:c>
+      <x:c r="B9" s="22" t="str">
+        <x:v>data_type</x:v>
+      </x:c>
+      <x:c r="C9" s="22" t="str">
+        <x:v>length</x:v>
+      </x:c>
+      <x:c r="D9" s="22" t="str">
+        <x:v>nullable</x:v>
+      </x:c>
+      <x:c r="E9" s="22" t="str">
+        <x:v>default_value</x:v>
+      </x:c>
+      <x:c r="F9" s="22" t="str">
+        <x:v>key_type</x:v>
+      </x:c>
+      <x:c r="G9" s="22" t="str">
+        <x:v>references</x:v>
+      </x:c>
+      <x:c r="H9" s="22" t="str">
+        <x:v>index_type</x:v>
+      </x:c>
+      <x:c r="I9" s="22" t="str">
+        <x:v>description_th</x:v>
+      </x:c>
+      <x:c r="J9" s="22" t="str">
+        <x:v>example_value</x:v>
+      </x:c>
+      <x:c r="K9" s="22" t="str">
+        <x:v>validation_rule</x:v>
+      </x:c>
+      <x:c r="L9" s="22" t="str">
+        <x:v>personal_data_classification</x:v>
+      </x:c>
+      <x:c r="M9" s="22" t="str">
+        <x:v>notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="22" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="B10" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="C10" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D10" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E10" s="22" t="str">
+        <x:v>AUTO_INCREMENT</x:v>
+      </x:c>
+      <x:c r="F10" s="22" t="str">
+        <x:v>PK</x:v>
+      </x:c>
+      <x:c r="G10" s="22"/>
+      <x:c r="H10" s="22" t="str">
+        <x:v>PRIMARY</x:v>
+      </x:c>
+      <x:c r="I10" s="22" t="str">
+        <x:v>รหัสภายในของรายการ</x:v>
+      </x:c>
+      <x:c r="J10" s="22"/>
+      <x:c r="K10" s="22"/>
+      <x:c r="L10" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M10" s="22"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="22" t="str">
+        <x:v>job_type</x:v>
+      </x:c>
+      <x:c r="B11" s="22" t="str">
+        <x:v>VARCHAR(80)</x:v>
+      </x:c>
+      <x:c r="C11" s="22" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D11" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E11" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F11" s="22"/>
+      <x:c r="G11" s="22"/>
+      <x:c r="H11" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="I11" s="22" t="str">
+        <x:v>job type</x:v>
+      </x:c>
+      <x:c r="J11" s="22"/>
+      <x:c r="K11" s="22"/>
+      <x:c r="L11" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M11" s="22"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="22" t="str">
+        <x:v>status</x:v>
+      </x:c>
+      <x:c r="B12" s="22" t="str">
+        <x:v>VARCHAR(40)</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D12" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E12" s="22" t="str">
+        <x:v>PENDING</x:v>
+      </x:c>
+      <x:c r="F12" s="22"/>
+      <x:c r="G12" s="22"/>
+      <x:c r="H12" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="I12" s="22" t="str">
+        <x:v>สถานะรายการ</x:v>
+      </x:c>
+      <x:c r="J12" s="22"/>
+      <x:c r="K12" s="22"/>
+      <x:c r="L12" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M12" s="22"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="22" t="str">
+        <x:v>params</x:v>
+      </x:c>
+      <x:c r="B13" s="22" t="str">
+        <x:v>JSON</x:v>
+      </x:c>
+      <x:c r="C13" s="22"/>
+      <x:c r="D13" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E13" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F13" s="22"/>
+      <x:c r="G13" s="22"/>
+      <x:c r="H13" s="22"/>
+      <x:c r="I13" s="22" t="str">
+        <x:v>params</x:v>
+      </x:c>
+      <x:c r="J13" s="22"/>
+      <x:c r="K13" s="22" t="str">
+        <x:v>valid JSON</x:v>
+      </x:c>
+      <x:c r="L13" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M13" s="22"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="22" t="str">
+        <x:v>result_json</x:v>
+      </x:c>
+      <x:c r="B14" s="22" t="str">
+        <x:v>JSON</x:v>
+      </x:c>
+      <x:c r="C14" s="22"/>
+      <x:c r="D14" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E14" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F14" s="22"/>
+      <x:c r="G14" s="22"/>
+      <x:c r="H14" s="22"/>
+      <x:c r="I14" s="22" t="str">
+        <x:v>result json</x:v>
+      </x:c>
+      <x:c r="J14" s="22"/>
+      <x:c r="K14" s="22" t="str">
+        <x:v>valid JSON</x:v>
+      </x:c>
+      <x:c r="L14" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M14" s="22"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="22" t="str">
+        <x:v>file_name</x:v>
+      </x:c>
+      <x:c r="B15" s="22" t="str">
+        <x:v>VARCHAR(255)</x:v>
+      </x:c>
+      <x:c r="C15" s="22" t="n">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="D15" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E15" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F15" s="22"/>
+      <x:c r="G15" s="22"/>
+      <x:c r="H15" s="22"/>
+      <x:c r="I15" s="22" t="str">
+        <x:v>ชื่อไฟล์ในระบบ</x:v>
+      </x:c>
+      <x:c r="J15" s="22"/>
+      <x:c r="K15" s="22"/>
+      <x:c r="L15" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M15" s="22"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="22" t="str">
+        <x:v>created_by</x:v>
+      </x:c>
+      <x:c r="B16" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="C16" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D16" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E16" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F16" s="22" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="G16" s="22" t="str">
+        <x:v>users.id</x:v>
+      </x:c>
+      <x:c r="H16" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="I16" s="22" t="str">
+        <x:v>ผู้สร้างรายการ</x:v>
+      </x:c>
+      <x:c r="J16" s="22"/>
+      <x:c r="K16" s="22"/>
+      <x:c r="L16" s="22" t="str">
+        <x:v>IDENTIFIER</x:v>
+      </x:c>
+      <x:c r="M16" s="22"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="22" t="str">
+        <x:v>started_at</x:v>
+      </x:c>
+      <x:c r="B17" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="C17" s="22"/>
+      <x:c r="D17" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E17" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F17" s="22"/>
+      <x:c r="G17" s="22"/>
+      <x:c r="H17" s="22"/>
+      <x:c r="I17" s="22" t="str">
+        <x:v>started at</x:v>
+      </x:c>
+      <x:c r="J17" s="22"/>
+      <x:c r="K17" s="22"/>
+      <x:c r="L17" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M17" s="22"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="22" t="str">
+        <x:v>completed_at</x:v>
+      </x:c>
+      <x:c r="B18" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="C18" s="22"/>
+      <x:c r="D18" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E18" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F18" s="22"/>
+      <x:c r="G18" s="22"/>
+      <x:c r="H18" s="22"/>
+      <x:c r="I18" s="22" t="str">
+        <x:v>completed at</x:v>
+      </x:c>
+      <x:c r="J18" s="22"/>
+      <x:c r="K18" s="22"/>
+      <x:c r="L18" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M18" s="22"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="22" t="str">
+        <x:v>created_at</x:v>
+      </x:c>
+      <x:c r="B19" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="C19" s="22"/>
+      <x:c r="D19" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E19" s="22" t="str">
+        <x:v>CURRENT_TIMESTAMP(3)</x:v>
+      </x:c>
+      <x:c r="F19" s="22"/>
+      <x:c r="G19" s="22"/>
+      <x:c r="H19" s="22"/>
+      <x:c r="I19" s="22" t="str">
+        <x:v>วันที่และเวลาที่สร้างรายการ</x:v>
+      </x:c>
+      <x:c r="J19" s="22"/>
+      <x:c r="K19" s="22"/>
+      <x:c r="L19" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M19" s="22"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="22" t="str">
+        <x:v>updated_at</x:v>
+      </x:c>
+      <x:c r="B20" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="C20" s="22"/>
+      <x:c r="D20" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E20" s="22" t="str">
+        <x:v>CURRENT_TIMESTAMP(3)</x:v>
+      </x:c>
+      <x:c r="F20" s="22"/>
+      <x:c r="G20" s="22"/>
+      <x:c r="H20" s="22"/>
+      <x:c r="I20" s="22" t="str">
+        <x:v>วันที่และเวลาที่แก้ไขล่าสุด</x:v>
+      </x:c>
+      <x:c r="J20" s="22"/>
+      <x:c r="K20" s="22"/>
+      <x:c r="L20" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M20" s="22"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="22"/>
+      <x:c r="B21" s="22"/>
+      <x:c r="C21" s="22"/>
+      <x:c r="D21" s="22"/>
+      <x:c r="E21" s="22"/>
+      <x:c r="F21" s="22"/>
+      <x:c r="G21" s="22"/>
+      <x:c r="H21" s="22"/>
+      <x:c r="I21" s="22"/>
+      <x:c r="J21" s="22"/>
+      <x:c r="K21" s="22"/>
+      <x:c r="L21" s="22"/>
+      <x:c r="M21" s="22"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="22" t="str">
+        <x:v>Relationships ที่เกี่ยวข้อง</x:v>
+      </x:c>
+      <x:c r="B22" s="22"/>
+      <x:c r="C22" s="22"/>
+      <x:c r="D22" s="22"/>
+      <x:c r="E22" s="22"/>
+      <x:c r="F22" s="22"/>
+      <x:c r="G22" s="22"/>
+      <x:c r="H22" s="22"/>
+      <x:c r="I22" s="22"/>
+      <x:c r="J22" s="22"/>
+      <x:c r="K22" s="22"/>
+      <x:c r="L22" s="22"/>
+      <x:c r="M22" s="22"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="22" t="str">
+        <x:v>parent_table</x:v>
+      </x:c>
+      <x:c r="B23" s="22" t="str">
+        <x:v>child_table</x:v>
+      </x:c>
+      <x:c r="C23" s="22" t="str">
+        <x:v>foreign_key</x:v>
+      </x:c>
+      <x:c r="D23" s="22" t="str">
+        <x:v>cardinality</x:v>
+      </x:c>
+      <x:c r="E23" s="22" t="str">
+        <x:v>on_delete</x:v>
+      </x:c>
+      <x:c r="F23" s="22" t="str">
+        <x:v>on_update</x:v>
+      </x:c>
+      <x:c r="G23" s="22" t="str">
+        <x:v>description_th</x:v>
+      </x:c>
+      <x:c r="H23" s="22"/>
+      <x:c r="I23" s="22"/>
+      <x:c r="J23" s="22"/>
+      <x:c r="K23" s="22"/>
+      <x:c r="L23" s="22"/>
+      <x:c r="M23" s="22"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="22" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="B24" s="22" t="str">
+        <x:v>export_jobs</x:v>
+      </x:c>
+      <x:c r="C24" s="22" t="str">
+        <x:v>created_by</x:v>
+      </x:c>
+      <x:c r="D24" s="22" t="str">
+        <x:v>1 : Many</x:v>
+      </x:c>
+      <x:c r="E24" s="22" t="str">
+        <x:v>SET NULL</x:v>
+      </x:c>
+      <x:c r="F24" s="22" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G24" s="22" t="str">
+        <x:v>export_jobs.created_by อ้างอิง users.id</x:v>
+      </x:c>
+      <x:c r="H24" s="22"/>
+      <x:c r="I24" s="22"/>
+      <x:c r="J24" s="22"/>
+      <x:c r="K24" s="22"/>
+      <x:c r="L24" s="22"/>
+      <x:c r="M24" s="22"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
@@ -48311,6 +53524,259 @@
         <x:v>สำนักงานเป็นรายละเอียดหนึ่งต่อหนึ่งของ locations สำหรับเช็กอิน</x:v>
       </x:c>
     </x:row>
+    <x:row r="63" ht="42" customHeight="1">
+      <x:c r="A63" s="22" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="B63" s="22" t="str">
+        <x:v>archived_notifications</x:v>
+      </x:c>
+      <x:c r="C63" s="22" t="str">
+        <x:v>user_id</x:v>
+      </x:c>
+      <x:c r="D63" s="22" t="str">
+        <x:v>1 : Many</x:v>
+      </x:c>
+      <x:c r="E63" s="22" t="str">
+        <x:v>CASCADE</x:v>
+      </x:c>
+      <x:c r="F63" s="22" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G63" s="22" t="str">
+        <x:v>archived_notifications.user_id อ้างอิง users.id</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="42" customHeight="1">
+      <x:c r="A64" s="22" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="B64" s="22" t="str">
+        <x:v>assessment_attachments</x:v>
+      </x:c>
+      <x:c r="C64" s="22" t="str">
+        <x:v>created_by</x:v>
+      </x:c>
+      <x:c r="D64" s="22" t="str">
+        <x:v>1 : Many</x:v>
+      </x:c>
+      <x:c r="E64" s="22" t="str">
+        <x:v>SET NULL</x:v>
+      </x:c>
+      <x:c r="F64" s="22" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G64" s="22" t="str">
+        <x:v>assessment_attachments.created_by อ้างอิง users.id</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="42" customHeight="1">
+      <x:c r="A65" s="22" t="str">
+        <x:v>media_assets</x:v>
+      </x:c>
+      <x:c r="B65" s="22" t="str">
+        <x:v>assessment_attachments</x:v>
+      </x:c>
+      <x:c r="C65" s="22" t="str">
+        <x:v>media_asset_id</x:v>
+      </x:c>
+      <x:c r="D65" s="22" t="str">
+        <x:v>1 : Many</x:v>
+      </x:c>
+      <x:c r="E65" s="22" t="str">
+        <x:v>SET NULL</x:v>
+      </x:c>
+      <x:c r="F65" s="22" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G65" s="22" t="str">
+        <x:v>assessment_attachments.media_asset_id อ้างอิง media_assets.id</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="42" customHeight="1">
+      <x:c r="A66" s="22" t="str">
+        <x:v>assessment_runs</x:v>
+      </x:c>
+      <x:c r="B66" s="22" t="str">
+        <x:v>assessment_attachments</x:v>
+      </x:c>
+      <x:c r="C66" s="22" t="str">
+        <x:v>assessment_run_id</x:v>
+      </x:c>
+      <x:c r="D66" s="22" t="str">
+        <x:v>1 : Many</x:v>
+      </x:c>
+      <x:c r="E66" s="22" t="str">
+        <x:v>CASCADE</x:v>
+      </x:c>
+      <x:c r="F66" s="22" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G66" s="22" t="str">
+        <x:v>assessment_attachments.assessment_run_id อ้างอิง assessment_runs.id</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="42" customHeight="1">
+      <x:c r="A67" s="22" t="str">
+        <x:v>corrective_actions</x:v>
+      </x:c>
+      <x:c r="B67" s="22" t="str">
+        <x:v>corrective_action_comments</x:v>
+      </x:c>
+      <x:c r="C67" s="22" t="str">
+        <x:v>corrective_action_id</x:v>
+      </x:c>
+      <x:c r="D67" s="22" t="str">
+        <x:v>1 : Many</x:v>
+      </x:c>
+      <x:c r="E67" s="22" t="str">
+        <x:v>CASCADE</x:v>
+      </x:c>
+      <x:c r="F67" s="22" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G67" s="22" t="str">
+        <x:v>corrective_action_comments.corrective_action_id อ้างอิง corrective_actions.id</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="42" customHeight="1">
+      <x:c r="A68" s="22" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="B68" s="22" t="str">
+        <x:v>corrective_action_comments</x:v>
+      </x:c>
+      <x:c r="C68" s="22" t="str">
+        <x:v>author_id</x:v>
+      </x:c>
+      <x:c r="D68" s="22" t="str">
+        <x:v>1 : Many</x:v>
+      </x:c>
+      <x:c r="E68" s="22" t="str">
+        <x:v>SET NULL</x:v>
+      </x:c>
+      <x:c r="F68" s="22" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G68" s="22" t="str">
+        <x:v>corrective_action_comments.author_id อ้างอิง users.id</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="42" customHeight="1">
+      <x:c r="A69" s="22" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="B69" s="22" t="str">
+        <x:v>export_jobs</x:v>
+      </x:c>
+      <x:c r="C69" s="22" t="str">
+        <x:v>created_by</x:v>
+      </x:c>
+      <x:c r="D69" s="22" t="str">
+        <x:v>1 : Many</x:v>
+      </x:c>
+      <x:c r="E69" s="22" t="str">
+        <x:v>SET NULL</x:v>
+      </x:c>
+      <x:c r="F69" s="22" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G69" s="22" t="str">
+        <x:v>export_jobs.created_by อ้างอิง users.id</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="42" customHeight="1">
+      <x:c r="A70" s="22" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="B70" s="22" t="str">
+        <x:v>media_assets</x:v>
+      </x:c>
+      <x:c r="C70" s="22" t="str">
+        <x:v>created_by</x:v>
+      </x:c>
+      <x:c r="D70" s="22" t="str">
+        <x:v>1 : Many</x:v>
+      </x:c>
+      <x:c r="E70" s="22" t="str">
+        <x:v>SET NULL</x:v>
+      </x:c>
+      <x:c r="F70" s="22" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G70" s="22" t="str">
+        <x:v>media_assets.created_by อ้างอิง users.id</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="42" customHeight="1">
+      <x:c r="A71" s="22" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="B71" s="22" t="str">
+        <x:v>notification_preferences</x:v>
+      </x:c>
+      <x:c r="C71" s="22" t="str">
+        <x:v>user_id</x:v>
+      </x:c>
+      <x:c r="D71" s="22" t="str">
+        <x:v>1 : Many</x:v>
+      </x:c>
+      <x:c r="E71" s="22" t="str">
+        <x:v>CASCADE</x:v>
+      </x:c>
+      <x:c r="F71" s="22" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G71" s="22" t="str">
+        <x:v>notification_preferences.user_id อ้างอิง users.id</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="42" customHeight="1">
+      <x:c r="A72" s="22" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="B72" s="22" t="str">
+        <x:v>safety_culture_events</x:v>
+      </x:c>
+      <x:c r="C72" s="22" t="str">
+        <x:v>created_by</x:v>
+      </x:c>
+      <x:c r="D72" s="22" t="str">
+        <x:v>1 : Many</x:v>
+      </x:c>
+      <x:c r="E72" s="22" t="str">
+        <x:v>SET NULL</x:v>
+      </x:c>
+      <x:c r="F72" s="22" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G72" s="22" t="str">
+        <x:v>safety_culture_events.created_by อ้างอิง users.id</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="42" customHeight="1">
+      <x:c r="A73" s="22" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="B73" s="22" t="str">
+        <x:v>safety_settings</x:v>
+      </x:c>
+      <x:c r="C73" s="22" t="str">
+        <x:v>updated_by</x:v>
+      </x:c>
+      <x:c r="D73" s="22" t="str">
+        <x:v>1 : Many</x:v>
+      </x:c>
+      <x:c r="E73" s="22" t="str">
+        <x:v>SET NULL</x:v>
+      </x:c>
+      <x:c r="F73" s="22" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G73" s="22" t="str">
+        <x:v>safety_settings.updated_by อ้างอิง users.id</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G1"/>
@@ -48318,8 +53784,2755 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1739876bea14ea7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7fa0d6f8bb946a9"/>
   </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="36" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="22" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="30" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="22" t="str">
+        <x:v>notification_preferences</x:v>
+      </x:c>
+      <x:c r="B1" s="22"/>
+      <x:c r="C1" s="22"/>
+      <x:c r="D1" s="22"/>
+      <x:c r="E1" s="22"/>
+      <x:c r="F1" s="22"/>
+      <x:c r="G1" s="22"/>
+      <x:c r="H1" s="22"/>
+      <x:c r="I1" s="22"/>
+      <x:c r="J1" s="22"/>
+      <x:c r="K1" s="22"/>
+      <x:c r="L1" s="22"/>
+      <x:c r="M1" s="22"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="22" t="str">
+        <x:v>Notifications | Shared | Medium | การตั้งค่าช่องทางแจ้งเตือนรายผู้ใช้</x:v>
+      </x:c>
+      <x:c r="B2" s="22"/>
+      <x:c r="C2" s="22"/>
+      <x:c r="D2" s="22"/>
+      <x:c r="E2" s="22"/>
+      <x:c r="F2" s="22"/>
+      <x:c r="G2" s="22"/>
+      <x:c r="H2" s="22"/>
+      <x:c r="I2" s="22"/>
+      <x:c r="J2" s="22"/>
+      <x:c r="K2" s="22"/>
+      <x:c r="L2" s="22"/>
+      <x:c r="M2" s="22"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="22"/>
+      <x:c r="B3" s="22"/>
+      <x:c r="C3" s="22"/>
+      <x:c r="D3" s="22"/>
+      <x:c r="E3" s="22"/>
+      <x:c r="F3" s="22"/>
+      <x:c r="G3" s="22"/>
+      <x:c r="H3" s="22"/>
+      <x:c r="I3" s="22"/>
+      <x:c r="J3" s="22"/>
+      <x:c r="K3" s="22"/>
+      <x:c r="L3" s="22"/>
+      <x:c r="M3" s="22"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="22" t="str">
+        <x:v>table_name</x:v>
+      </x:c>
+      <x:c r="B4" s="22" t="str">
+        <x:v>notification_preferences</x:v>
+      </x:c>
+      <x:c r="C4" s="22" t="str">
+        <x:v>module</x:v>
+      </x:c>
+      <x:c r="D4" s="22" t="str">
+        <x:v>Notifications</x:v>
+      </x:c>
+      <x:c r="E4" s="22" t="str">
+        <x:v>phase</x:v>
+      </x:c>
+      <x:c r="F4" s="22" t="str">
+        <x:v>Shared</x:v>
+      </x:c>
+      <x:c r="G4" s="22" t="str">
+        <x:v>priority</x:v>
+      </x:c>
+      <x:c r="H4" s="22" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="I4" s="22"/>
+      <x:c r="J4" s="22"/>
+      <x:c r="K4" s="22"/>
+      <x:c r="L4" s="22"/>
+      <x:c r="M4" s="22"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="22" t="str">
+        <x:v>purpose_th</x:v>
+      </x:c>
+      <x:c r="B5" s="22" t="str">
+        <x:v>การตั้งค่าช่องทางแจ้งเตือนรายผู้ใช้</x:v>
+      </x:c>
+      <x:c r="C5" s="22" t="str">
+        <x:v>primary_key</x:v>
+      </x:c>
+      <x:c r="D5" s="22" t="str">
+        <x:v>user_id</x:v>
+      </x:c>
+      <x:c r="E5" s="22" t="str">
+        <x:v>column_count</x:v>
+      </x:c>
+      <x:c r="F5" s="22" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G5" s="22"/>
+      <x:c r="H5" s="22"/>
+      <x:c r="I5" s="22"/>
+      <x:c r="J5" s="22"/>
+      <x:c r="K5" s="22"/>
+      <x:c r="L5" s="22"/>
+      <x:c r="M5" s="22"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="22"/>
+      <x:c r="B6" s="22"/>
+      <x:c r="C6" s="22"/>
+      <x:c r="D6" s="22"/>
+      <x:c r="E6" s="22"/>
+      <x:c r="F6" s="22"/>
+      <x:c r="G6" s="22"/>
+      <x:c r="H6" s="22"/>
+      <x:c r="I6" s="22"/>
+      <x:c r="J6" s="22"/>
+      <x:c r="K6" s="22"/>
+      <x:c r="L6" s="22"/>
+      <x:c r="M6" s="22"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="22" t="str">
+        <x:v>Column Dictionary</x:v>
+      </x:c>
+      <x:c r="B7" s="22"/>
+      <x:c r="C7" s="22"/>
+      <x:c r="D7" s="22"/>
+      <x:c r="E7" s="22"/>
+      <x:c r="F7" s="22"/>
+      <x:c r="G7" s="22"/>
+      <x:c r="H7" s="22"/>
+      <x:c r="I7" s="22"/>
+      <x:c r="J7" s="22"/>
+      <x:c r="K7" s="22"/>
+      <x:c r="L7" s="22"/>
+      <x:c r="M7" s="22"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="22"/>
+      <x:c r="B8" s="22"/>
+      <x:c r="C8" s="22"/>
+      <x:c r="D8" s="22"/>
+      <x:c r="E8" s="22"/>
+      <x:c r="F8" s="22"/>
+      <x:c r="G8" s="22"/>
+      <x:c r="H8" s="22"/>
+      <x:c r="I8" s="22"/>
+      <x:c r="J8" s="22"/>
+      <x:c r="K8" s="22"/>
+      <x:c r="L8" s="22"/>
+      <x:c r="M8" s="22"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="22" t="str">
+        <x:v>column_name</x:v>
+      </x:c>
+      <x:c r="B9" s="22" t="str">
+        <x:v>data_type</x:v>
+      </x:c>
+      <x:c r="C9" s="22" t="str">
+        <x:v>length</x:v>
+      </x:c>
+      <x:c r="D9" s="22" t="str">
+        <x:v>nullable</x:v>
+      </x:c>
+      <x:c r="E9" s="22" t="str">
+        <x:v>default_value</x:v>
+      </x:c>
+      <x:c r="F9" s="22" t="str">
+        <x:v>key_type</x:v>
+      </x:c>
+      <x:c r="G9" s="22" t="str">
+        <x:v>references</x:v>
+      </x:c>
+      <x:c r="H9" s="22" t="str">
+        <x:v>index_type</x:v>
+      </x:c>
+      <x:c r="I9" s="22" t="str">
+        <x:v>description_th</x:v>
+      </x:c>
+      <x:c r="J9" s="22" t="str">
+        <x:v>example_value</x:v>
+      </x:c>
+      <x:c r="K9" s="22" t="str">
+        <x:v>validation_rule</x:v>
+      </x:c>
+      <x:c r="L9" s="22" t="str">
+        <x:v>personal_data_classification</x:v>
+      </x:c>
+      <x:c r="M9" s="22" t="str">
+        <x:v>notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="22" t="str">
+        <x:v>user_id</x:v>
+      </x:c>
+      <x:c r="B10" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="C10" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D10" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E10" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F10" s="22" t="str">
+        <x:v>PK</x:v>
+      </x:c>
+      <x:c r="G10" s="22" t="str">
+        <x:v>users.id</x:v>
+      </x:c>
+      <x:c r="H10" s="22" t="str">
+        <x:v>PRIMARY</x:v>
+      </x:c>
+      <x:c r="I10" s="22" t="str">
+        <x:v>ผู้ใช้งานเจ้าของรายการ</x:v>
+      </x:c>
+      <x:c r="J10" s="22"/>
+      <x:c r="K10" s="22"/>
+      <x:c r="L10" s="22" t="str">
+        <x:v>IDENTIFIER</x:v>
+      </x:c>
+      <x:c r="M10" s="22"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="22" t="str">
+        <x:v>email_enabled</x:v>
+      </x:c>
+      <x:c r="B11" s="22" t="str">
+        <x:v>TINYINT(1)</x:v>
+      </x:c>
+      <x:c r="C11" s="22" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D11" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E11" s="22" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F11" s="22"/>
+      <x:c r="G11" s="22"/>
+      <x:c r="H11" s="22"/>
+      <x:c r="I11" s="22" t="str">
+        <x:v>email enabled</x:v>
+      </x:c>
+      <x:c r="J11" s="22"/>
+      <x:c r="K11" s="22"/>
+      <x:c r="L11" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M11" s="22"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="22" t="str">
+        <x:v>in_app_enabled</x:v>
+      </x:c>
+      <x:c r="B12" s="22" t="str">
+        <x:v>TINYINT(1)</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D12" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E12" s="22" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F12" s="22"/>
+      <x:c r="G12" s="22"/>
+      <x:c r="H12" s="22"/>
+      <x:c r="I12" s="22" t="str">
+        <x:v>in app enabled</x:v>
+      </x:c>
+      <x:c r="J12" s="22"/>
+      <x:c r="K12" s="22"/>
+      <x:c r="L12" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M12" s="22"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="22" t="str">
+        <x:v>preferences_json</x:v>
+      </x:c>
+      <x:c r="B13" s="22" t="str">
+        <x:v>JSON</x:v>
+      </x:c>
+      <x:c r="C13" s="22"/>
+      <x:c r="D13" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E13" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F13" s="22"/>
+      <x:c r="G13" s="22"/>
+      <x:c r="H13" s="22"/>
+      <x:c r="I13" s="22" t="str">
+        <x:v>การตั้งค่าเพิ่มเติมแบบ JSON</x:v>
+      </x:c>
+      <x:c r="J13" s="22"/>
+      <x:c r="K13" s="22" t="str">
+        <x:v>valid JSON</x:v>
+      </x:c>
+      <x:c r="L13" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M13" s="22"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="22" t="str">
+        <x:v>created_at</x:v>
+      </x:c>
+      <x:c r="B14" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="C14" s="22"/>
+      <x:c r="D14" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E14" s="22" t="str">
+        <x:v>CURRENT_TIMESTAMP(3)</x:v>
+      </x:c>
+      <x:c r="F14" s="22"/>
+      <x:c r="G14" s="22"/>
+      <x:c r="H14" s="22"/>
+      <x:c r="I14" s="22" t="str">
+        <x:v>วันที่และเวลาที่สร้างรายการ</x:v>
+      </x:c>
+      <x:c r="J14" s="22"/>
+      <x:c r="K14" s="22"/>
+      <x:c r="L14" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M14" s="22"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="22" t="str">
+        <x:v>updated_at</x:v>
+      </x:c>
+      <x:c r="B15" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="C15" s="22"/>
+      <x:c r="D15" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E15" s="22" t="str">
+        <x:v>CURRENT_TIMESTAMP(3)</x:v>
+      </x:c>
+      <x:c r="F15" s="22"/>
+      <x:c r="G15" s="22"/>
+      <x:c r="H15" s="22"/>
+      <x:c r="I15" s="22" t="str">
+        <x:v>วันที่และเวลาที่แก้ไขล่าสุด</x:v>
+      </x:c>
+      <x:c r="J15" s="22"/>
+      <x:c r="K15" s="22"/>
+      <x:c r="L15" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M15" s="22"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="22"/>
+      <x:c r="B16" s="22"/>
+      <x:c r="C16" s="22"/>
+      <x:c r="D16" s="22"/>
+      <x:c r="E16" s="22"/>
+      <x:c r="F16" s="22"/>
+      <x:c r="G16" s="22"/>
+      <x:c r="H16" s="22"/>
+      <x:c r="I16" s="22"/>
+      <x:c r="J16" s="22"/>
+      <x:c r="K16" s="22"/>
+      <x:c r="L16" s="22"/>
+      <x:c r="M16" s="22"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="22" t="str">
+        <x:v>Relationships ที่เกี่ยวข้อง</x:v>
+      </x:c>
+      <x:c r="B17" s="22"/>
+      <x:c r="C17" s="22"/>
+      <x:c r="D17" s="22"/>
+      <x:c r="E17" s="22"/>
+      <x:c r="F17" s="22"/>
+      <x:c r="G17" s="22"/>
+      <x:c r="H17" s="22"/>
+      <x:c r="I17" s="22"/>
+      <x:c r="J17" s="22"/>
+      <x:c r="K17" s="22"/>
+      <x:c r="L17" s="22"/>
+      <x:c r="M17" s="22"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="22" t="str">
+        <x:v>parent_table</x:v>
+      </x:c>
+      <x:c r="B18" s="22" t="str">
+        <x:v>child_table</x:v>
+      </x:c>
+      <x:c r="C18" s="22" t="str">
+        <x:v>foreign_key</x:v>
+      </x:c>
+      <x:c r="D18" s="22" t="str">
+        <x:v>cardinality</x:v>
+      </x:c>
+      <x:c r="E18" s="22" t="str">
+        <x:v>on_delete</x:v>
+      </x:c>
+      <x:c r="F18" s="22" t="str">
+        <x:v>on_update</x:v>
+      </x:c>
+      <x:c r="G18" s="22" t="str">
+        <x:v>description_th</x:v>
+      </x:c>
+      <x:c r="H18" s="22"/>
+      <x:c r="I18" s="22"/>
+      <x:c r="J18" s="22"/>
+      <x:c r="K18" s="22"/>
+      <x:c r="L18" s="22"/>
+      <x:c r="M18" s="22"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="22" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="B19" s="22" t="str">
+        <x:v>notification_preferences</x:v>
+      </x:c>
+      <x:c r="C19" s="22" t="str">
+        <x:v>user_id</x:v>
+      </x:c>
+      <x:c r="D19" s="22" t="str">
+        <x:v>1 : Many</x:v>
+      </x:c>
+      <x:c r="E19" s="22" t="str">
+        <x:v>CASCADE</x:v>
+      </x:c>
+      <x:c r="F19" s="22" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G19" s="22" t="str">
+        <x:v>notification_preferences.user_id อ้างอิง users.id</x:v>
+      </x:c>
+      <x:c r="H19" s="22"/>
+      <x:c r="I19" s="22"/>
+      <x:c r="J19" s="22"/>
+      <x:c r="K19" s="22"/>
+      <x:c r="L19" s="22"/>
+      <x:c r="M19" s="22"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="36" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="22" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="30" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="22" t="str">
+        <x:v>assessment_attachments</x:v>
+      </x:c>
+      <x:c r="B1" s="22"/>
+      <x:c r="C1" s="22"/>
+      <x:c r="D1" s="22"/>
+      <x:c r="E1" s="22"/>
+      <x:c r="F1" s="22"/>
+      <x:c r="G1" s="22"/>
+      <x:c r="H1" s="22"/>
+      <x:c r="I1" s="22"/>
+      <x:c r="J1" s="22"/>
+      <x:c r="K1" s="22"/>
+      <x:c r="L1" s="22"/>
+      <x:c r="M1" s="22"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="22" t="str">
+        <x:v>Assessment | Phase 2 | High | หลักฐานไฟล์ที่ผูกกับ assessment run ผ่าน media_assets</x:v>
+      </x:c>
+      <x:c r="B2" s="22"/>
+      <x:c r="C2" s="22"/>
+      <x:c r="D2" s="22"/>
+      <x:c r="E2" s="22"/>
+      <x:c r="F2" s="22"/>
+      <x:c r="G2" s="22"/>
+      <x:c r="H2" s="22"/>
+      <x:c r="I2" s="22"/>
+      <x:c r="J2" s="22"/>
+      <x:c r="K2" s="22"/>
+      <x:c r="L2" s="22"/>
+      <x:c r="M2" s="22"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="22"/>
+      <x:c r="B3" s="22"/>
+      <x:c r="C3" s="22"/>
+      <x:c r="D3" s="22"/>
+      <x:c r="E3" s="22"/>
+      <x:c r="F3" s="22"/>
+      <x:c r="G3" s="22"/>
+      <x:c r="H3" s="22"/>
+      <x:c r="I3" s="22"/>
+      <x:c r="J3" s="22"/>
+      <x:c r="K3" s="22"/>
+      <x:c r="L3" s="22"/>
+      <x:c r="M3" s="22"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="22" t="str">
+        <x:v>table_name</x:v>
+      </x:c>
+      <x:c r="B4" s="22" t="str">
+        <x:v>assessment_attachments</x:v>
+      </x:c>
+      <x:c r="C4" s="22" t="str">
+        <x:v>module</x:v>
+      </x:c>
+      <x:c r="D4" s="22" t="str">
+        <x:v>Assessment</x:v>
+      </x:c>
+      <x:c r="E4" s="22" t="str">
+        <x:v>phase</x:v>
+      </x:c>
+      <x:c r="F4" s="22" t="str">
+        <x:v>Phase 2</x:v>
+      </x:c>
+      <x:c r="G4" s="22" t="str">
+        <x:v>priority</x:v>
+      </x:c>
+      <x:c r="H4" s="22" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I4" s="22"/>
+      <x:c r="J4" s="22"/>
+      <x:c r="K4" s="22"/>
+      <x:c r="L4" s="22"/>
+      <x:c r="M4" s="22"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="22" t="str">
+        <x:v>purpose_th</x:v>
+      </x:c>
+      <x:c r="B5" s="22" t="str">
+        <x:v>หลักฐานไฟล์ที่ผูกกับ assessment run ผ่าน media_assets</x:v>
+      </x:c>
+      <x:c r="C5" s="22" t="str">
+        <x:v>primary_key</x:v>
+      </x:c>
+      <x:c r="D5" s="22" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="E5" s="22" t="str">
+        <x:v>column_count</x:v>
+      </x:c>
+      <x:c r="F5" s="22" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G5" s="22"/>
+      <x:c r="H5" s="22"/>
+      <x:c r="I5" s="22"/>
+      <x:c r="J5" s="22"/>
+      <x:c r="K5" s="22"/>
+      <x:c r="L5" s="22"/>
+      <x:c r="M5" s="22"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="22"/>
+      <x:c r="B6" s="22"/>
+      <x:c r="C6" s="22"/>
+      <x:c r="D6" s="22"/>
+      <x:c r="E6" s="22"/>
+      <x:c r="F6" s="22"/>
+      <x:c r="G6" s="22"/>
+      <x:c r="H6" s="22"/>
+      <x:c r="I6" s="22"/>
+      <x:c r="J6" s="22"/>
+      <x:c r="K6" s="22"/>
+      <x:c r="L6" s="22"/>
+      <x:c r="M6" s="22"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="22" t="str">
+        <x:v>Column Dictionary</x:v>
+      </x:c>
+      <x:c r="B7" s="22"/>
+      <x:c r="C7" s="22"/>
+      <x:c r="D7" s="22"/>
+      <x:c r="E7" s="22"/>
+      <x:c r="F7" s="22"/>
+      <x:c r="G7" s="22"/>
+      <x:c r="H7" s="22"/>
+      <x:c r="I7" s="22"/>
+      <x:c r="J7" s="22"/>
+      <x:c r="K7" s="22"/>
+      <x:c r="L7" s="22"/>
+      <x:c r="M7" s="22"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="22"/>
+      <x:c r="B8" s="22"/>
+      <x:c r="C8" s="22"/>
+      <x:c r="D8" s="22"/>
+      <x:c r="E8" s="22"/>
+      <x:c r="F8" s="22"/>
+      <x:c r="G8" s="22"/>
+      <x:c r="H8" s="22"/>
+      <x:c r="I8" s="22"/>
+      <x:c r="J8" s="22"/>
+      <x:c r="K8" s="22"/>
+      <x:c r="L8" s="22"/>
+      <x:c r="M8" s="22"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="22" t="str">
+        <x:v>column_name</x:v>
+      </x:c>
+      <x:c r="B9" s="22" t="str">
+        <x:v>data_type</x:v>
+      </x:c>
+      <x:c r="C9" s="22" t="str">
+        <x:v>length</x:v>
+      </x:c>
+      <x:c r="D9" s="22" t="str">
+        <x:v>nullable</x:v>
+      </x:c>
+      <x:c r="E9" s="22" t="str">
+        <x:v>default_value</x:v>
+      </x:c>
+      <x:c r="F9" s="22" t="str">
+        <x:v>key_type</x:v>
+      </x:c>
+      <x:c r="G9" s="22" t="str">
+        <x:v>references</x:v>
+      </x:c>
+      <x:c r="H9" s="22" t="str">
+        <x:v>index_type</x:v>
+      </x:c>
+      <x:c r="I9" s="22" t="str">
+        <x:v>description_th</x:v>
+      </x:c>
+      <x:c r="J9" s="22" t="str">
+        <x:v>example_value</x:v>
+      </x:c>
+      <x:c r="K9" s="22" t="str">
+        <x:v>validation_rule</x:v>
+      </x:c>
+      <x:c r="L9" s="22" t="str">
+        <x:v>personal_data_classification</x:v>
+      </x:c>
+      <x:c r="M9" s="22" t="str">
+        <x:v>notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="22" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="B10" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="C10" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D10" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E10" s="22" t="str">
+        <x:v>AUTO_INCREMENT</x:v>
+      </x:c>
+      <x:c r="F10" s="22" t="str">
+        <x:v>PK</x:v>
+      </x:c>
+      <x:c r="G10" s="22"/>
+      <x:c r="H10" s="22" t="str">
+        <x:v>PRIMARY</x:v>
+      </x:c>
+      <x:c r="I10" s="22" t="str">
+        <x:v>รหัสภายในของรายการ</x:v>
+      </x:c>
+      <x:c r="J10" s="22"/>
+      <x:c r="K10" s="22"/>
+      <x:c r="L10" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M10" s="22"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="22" t="str">
+        <x:v>assessment_run_id</x:v>
+      </x:c>
+      <x:c r="B11" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="C11" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D11" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E11" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F11" s="22" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="G11" s="22" t="str">
+        <x:v>assessment_runs.id</x:v>
+      </x:c>
+      <x:c r="H11" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="I11" s="22" t="str">
+        <x:v>Assessment run ที่แนบไฟล์</x:v>
+      </x:c>
+      <x:c r="J11" s="22"/>
+      <x:c r="K11" s="22"/>
+      <x:c r="L11" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M11" s="22"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="22" t="str">
+        <x:v>media_asset_id</x:v>
+      </x:c>
+      <x:c r="B12" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D12" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E12" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F12" s="22" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="G12" s="22" t="str">
+        <x:v>media_assets.id</x:v>
+      </x:c>
+      <x:c r="H12" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="I12" s="22" t="str">
+        <x:v>ไฟล์ metadata ที่อ้างอิง</x:v>
+      </x:c>
+      <x:c r="J12" s="22"/>
+      <x:c r="K12" s="22"/>
+      <x:c r="L12" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M12" s="22"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="22" t="str">
+        <x:v>file_url</x:v>
+      </x:c>
+      <x:c r="B13" s="22" t="str">
+        <x:v>VARCHAR(1000)</x:v>
+      </x:c>
+      <x:c r="C13" s="22" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="D13" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E13" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F13" s="22"/>
+      <x:c r="G13" s="22"/>
+      <x:c r="H13" s="22"/>
+      <x:c r="I13" s="22" t="str">
+        <x:v>file url</x:v>
+      </x:c>
+      <x:c r="J13" s="22"/>
+      <x:c r="K13" s="22"/>
+      <x:c r="L13" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M13" s="22"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="22" t="str">
+        <x:v>attachment_type</x:v>
+      </x:c>
+      <x:c r="B14" s="22" t="str">
+        <x:v>VARCHAR(80)</x:v>
+      </x:c>
+      <x:c r="C14" s="22" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D14" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E14" s="22" t="str">
+        <x:v>EVIDENCE</x:v>
+      </x:c>
+      <x:c r="F14" s="22"/>
+      <x:c r="G14" s="22"/>
+      <x:c r="H14" s="22"/>
+      <x:c r="I14" s="22" t="str">
+        <x:v>attachment type</x:v>
+      </x:c>
+      <x:c r="J14" s="22"/>
+      <x:c r="K14" s="22"/>
+      <x:c r="L14" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M14" s="22"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="22" t="str">
+        <x:v>metadata</x:v>
+      </x:c>
+      <x:c r="B15" s="22" t="str">
+        <x:v>JSON</x:v>
+      </x:c>
+      <x:c r="C15" s="22"/>
+      <x:c r="D15" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E15" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F15" s="22"/>
+      <x:c r="G15" s="22"/>
+      <x:c r="H15" s="22"/>
+      <x:c r="I15" s="22" t="str">
+        <x:v>ข้อมูลประกอบแบบ JSON</x:v>
+      </x:c>
+      <x:c r="J15" s="22"/>
+      <x:c r="K15" s="22" t="str">
+        <x:v>valid JSON</x:v>
+      </x:c>
+      <x:c r="L15" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M15" s="22"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="22" t="str">
+        <x:v>created_by</x:v>
+      </x:c>
+      <x:c r="B16" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="C16" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D16" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E16" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F16" s="22" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="G16" s="22" t="str">
+        <x:v>users.id</x:v>
+      </x:c>
+      <x:c r="H16" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="I16" s="22" t="str">
+        <x:v>ผู้สร้างรายการ</x:v>
+      </x:c>
+      <x:c r="J16" s="22"/>
+      <x:c r="K16" s="22"/>
+      <x:c r="L16" s="22" t="str">
+        <x:v>IDENTIFIER</x:v>
+      </x:c>
+      <x:c r="M16" s="22"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="22" t="str">
+        <x:v>created_at</x:v>
+      </x:c>
+      <x:c r="B17" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="C17" s="22"/>
+      <x:c r="D17" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E17" s="22" t="str">
+        <x:v>CURRENT_TIMESTAMP(3)</x:v>
+      </x:c>
+      <x:c r="F17" s="22"/>
+      <x:c r="G17" s="22"/>
+      <x:c r="H17" s="22"/>
+      <x:c r="I17" s="22" t="str">
+        <x:v>วันที่และเวลาที่สร้างรายการ</x:v>
+      </x:c>
+      <x:c r="J17" s="22"/>
+      <x:c r="K17" s="22"/>
+      <x:c r="L17" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M17" s="22"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="22" t="str">
+        <x:v>updated_at</x:v>
+      </x:c>
+      <x:c r="B18" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="C18" s="22"/>
+      <x:c r="D18" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E18" s="22" t="str">
+        <x:v>CURRENT_TIMESTAMP(3)</x:v>
+      </x:c>
+      <x:c r="F18" s="22"/>
+      <x:c r="G18" s="22"/>
+      <x:c r="H18" s="22"/>
+      <x:c r="I18" s="22" t="str">
+        <x:v>วันที่และเวลาที่แก้ไขล่าสุด</x:v>
+      </x:c>
+      <x:c r="J18" s="22"/>
+      <x:c r="K18" s="22"/>
+      <x:c r="L18" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M18" s="22"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="22"/>
+      <x:c r="B19" s="22"/>
+      <x:c r="C19" s="22"/>
+      <x:c r="D19" s="22"/>
+      <x:c r="E19" s="22"/>
+      <x:c r="F19" s="22"/>
+      <x:c r="G19" s="22"/>
+      <x:c r="H19" s="22"/>
+      <x:c r="I19" s="22"/>
+      <x:c r="J19" s="22"/>
+      <x:c r="K19" s="22"/>
+      <x:c r="L19" s="22"/>
+      <x:c r="M19" s="22"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="22" t="str">
+        <x:v>Relationships ที่เกี่ยวข้อง</x:v>
+      </x:c>
+      <x:c r="B20" s="22"/>
+      <x:c r="C20" s="22"/>
+      <x:c r="D20" s="22"/>
+      <x:c r="E20" s="22"/>
+      <x:c r="F20" s="22"/>
+      <x:c r="G20" s="22"/>
+      <x:c r="H20" s="22"/>
+      <x:c r="I20" s="22"/>
+      <x:c r="J20" s="22"/>
+      <x:c r="K20" s="22"/>
+      <x:c r="L20" s="22"/>
+      <x:c r="M20" s="22"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="22" t="str">
+        <x:v>parent_table</x:v>
+      </x:c>
+      <x:c r="B21" s="22" t="str">
+        <x:v>child_table</x:v>
+      </x:c>
+      <x:c r="C21" s="22" t="str">
+        <x:v>foreign_key</x:v>
+      </x:c>
+      <x:c r="D21" s="22" t="str">
+        <x:v>cardinality</x:v>
+      </x:c>
+      <x:c r="E21" s="22" t="str">
+        <x:v>on_delete</x:v>
+      </x:c>
+      <x:c r="F21" s="22" t="str">
+        <x:v>on_update</x:v>
+      </x:c>
+      <x:c r="G21" s="22" t="str">
+        <x:v>description_th</x:v>
+      </x:c>
+      <x:c r="H21" s="22"/>
+      <x:c r="I21" s="22"/>
+      <x:c r="J21" s="22"/>
+      <x:c r="K21" s="22"/>
+      <x:c r="L21" s="22"/>
+      <x:c r="M21" s="22"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="22" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="B22" s="22" t="str">
+        <x:v>assessment_attachments</x:v>
+      </x:c>
+      <x:c r="C22" s="22" t="str">
+        <x:v>created_by</x:v>
+      </x:c>
+      <x:c r="D22" s="22" t="str">
+        <x:v>1 : Many</x:v>
+      </x:c>
+      <x:c r="E22" s="22" t="str">
+        <x:v>SET NULL</x:v>
+      </x:c>
+      <x:c r="F22" s="22" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G22" s="22" t="str">
+        <x:v>assessment_attachments.created_by อ้างอิง users.id</x:v>
+      </x:c>
+      <x:c r="H22" s="22"/>
+      <x:c r="I22" s="22"/>
+      <x:c r="J22" s="22"/>
+      <x:c r="K22" s="22"/>
+      <x:c r="L22" s="22"/>
+      <x:c r="M22" s="22"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="22" t="str">
+        <x:v>media_assets</x:v>
+      </x:c>
+      <x:c r="B23" s="22" t="str">
+        <x:v>assessment_attachments</x:v>
+      </x:c>
+      <x:c r="C23" s="22" t="str">
+        <x:v>media_asset_id</x:v>
+      </x:c>
+      <x:c r="D23" s="22" t="str">
+        <x:v>1 : Many</x:v>
+      </x:c>
+      <x:c r="E23" s="22" t="str">
+        <x:v>SET NULL</x:v>
+      </x:c>
+      <x:c r="F23" s="22" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G23" s="22" t="str">
+        <x:v>assessment_attachments.media_asset_id อ้างอิง media_assets.id</x:v>
+      </x:c>
+      <x:c r="H23" s="22"/>
+      <x:c r="I23" s="22"/>
+      <x:c r="J23" s="22"/>
+      <x:c r="K23" s="22"/>
+      <x:c r="L23" s="22"/>
+      <x:c r="M23" s="22"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="22" t="str">
+        <x:v>assessment_runs</x:v>
+      </x:c>
+      <x:c r="B24" s="22" t="str">
+        <x:v>assessment_attachments</x:v>
+      </x:c>
+      <x:c r="C24" s="22" t="str">
+        <x:v>assessment_run_id</x:v>
+      </x:c>
+      <x:c r="D24" s="22" t="str">
+        <x:v>1 : Many</x:v>
+      </x:c>
+      <x:c r="E24" s="22" t="str">
+        <x:v>CASCADE</x:v>
+      </x:c>
+      <x:c r="F24" s="22" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G24" s="22" t="str">
+        <x:v>assessment_attachments.assessment_run_id อ้างอิง assessment_runs.id</x:v>
+      </x:c>
+      <x:c r="H24" s="22"/>
+      <x:c r="I24" s="22"/>
+      <x:c r="J24" s="22"/>
+      <x:c r="K24" s="22"/>
+      <x:c r="L24" s="22"/>
+      <x:c r="M24" s="22"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="36" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="22" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="30" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="22" t="str">
+        <x:v>corrective_action_comments</x:v>
+      </x:c>
+      <x:c r="B1" s="22"/>
+      <x:c r="C1" s="22"/>
+      <x:c r="D1" s="22"/>
+      <x:c r="E1" s="22"/>
+      <x:c r="F1" s="22"/>
+      <x:c r="G1" s="22"/>
+      <x:c r="H1" s="22"/>
+      <x:c r="I1" s="22"/>
+      <x:c r="J1" s="22"/>
+      <x:c r="K1" s="22"/>
+      <x:c r="L1" s="22"/>
+      <x:c r="M1" s="22"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="22" t="str">
+        <x:v>Safety Effort | Phase 2 | High | ความคิดเห็นและประวัติสนทนาของ corrective action</x:v>
+      </x:c>
+      <x:c r="B2" s="22"/>
+      <x:c r="C2" s="22"/>
+      <x:c r="D2" s="22"/>
+      <x:c r="E2" s="22"/>
+      <x:c r="F2" s="22"/>
+      <x:c r="G2" s="22"/>
+      <x:c r="H2" s="22"/>
+      <x:c r="I2" s="22"/>
+      <x:c r="J2" s="22"/>
+      <x:c r="K2" s="22"/>
+      <x:c r="L2" s="22"/>
+      <x:c r="M2" s="22"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="22"/>
+      <x:c r="B3" s="22"/>
+      <x:c r="C3" s="22"/>
+      <x:c r="D3" s="22"/>
+      <x:c r="E3" s="22"/>
+      <x:c r="F3" s="22"/>
+      <x:c r="G3" s="22"/>
+      <x:c r="H3" s="22"/>
+      <x:c r="I3" s="22"/>
+      <x:c r="J3" s="22"/>
+      <x:c r="K3" s="22"/>
+      <x:c r="L3" s="22"/>
+      <x:c r="M3" s="22"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="22" t="str">
+        <x:v>table_name</x:v>
+      </x:c>
+      <x:c r="B4" s="22" t="str">
+        <x:v>corrective_action_comments</x:v>
+      </x:c>
+      <x:c r="C4" s="22" t="str">
+        <x:v>module</x:v>
+      </x:c>
+      <x:c r="D4" s="22" t="str">
+        <x:v>Safety Effort</x:v>
+      </x:c>
+      <x:c r="E4" s="22" t="str">
+        <x:v>phase</x:v>
+      </x:c>
+      <x:c r="F4" s="22" t="str">
+        <x:v>Phase 2</x:v>
+      </x:c>
+      <x:c r="G4" s="22" t="str">
+        <x:v>priority</x:v>
+      </x:c>
+      <x:c r="H4" s="22" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I4" s="22"/>
+      <x:c r="J4" s="22"/>
+      <x:c r="K4" s="22"/>
+      <x:c r="L4" s="22"/>
+      <x:c r="M4" s="22"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="22" t="str">
+        <x:v>purpose_th</x:v>
+      </x:c>
+      <x:c r="B5" s="22" t="str">
+        <x:v>ความคิดเห็นและประวัติสนทนาของ corrective action</x:v>
+      </x:c>
+      <x:c r="C5" s="22" t="str">
+        <x:v>primary_key</x:v>
+      </x:c>
+      <x:c r="D5" s="22" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="E5" s="22" t="str">
+        <x:v>column_count</x:v>
+      </x:c>
+      <x:c r="F5" s="22" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G5" s="22"/>
+      <x:c r="H5" s="22"/>
+      <x:c r="I5" s="22"/>
+      <x:c r="J5" s="22"/>
+      <x:c r="K5" s="22"/>
+      <x:c r="L5" s="22"/>
+      <x:c r="M5" s="22"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="22"/>
+      <x:c r="B6" s="22"/>
+      <x:c r="C6" s="22"/>
+      <x:c r="D6" s="22"/>
+      <x:c r="E6" s="22"/>
+      <x:c r="F6" s="22"/>
+      <x:c r="G6" s="22"/>
+      <x:c r="H6" s="22"/>
+      <x:c r="I6" s="22"/>
+      <x:c r="J6" s="22"/>
+      <x:c r="K6" s="22"/>
+      <x:c r="L6" s="22"/>
+      <x:c r="M6" s="22"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="22" t="str">
+        <x:v>Column Dictionary</x:v>
+      </x:c>
+      <x:c r="B7" s="22"/>
+      <x:c r="C7" s="22"/>
+      <x:c r="D7" s="22"/>
+      <x:c r="E7" s="22"/>
+      <x:c r="F7" s="22"/>
+      <x:c r="G7" s="22"/>
+      <x:c r="H7" s="22"/>
+      <x:c r="I7" s="22"/>
+      <x:c r="J7" s="22"/>
+      <x:c r="K7" s="22"/>
+      <x:c r="L7" s="22"/>
+      <x:c r="M7" s="22"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="22"/>
+      <x:c r="B8" s="22"/>
+      <x:c r="C8" s="22"/>
+      <x:c r="D8" s="22"/>
+      <x:c r="E8" s="22"/>
+      <x:c r="F8" s="22"/>
+      <x:c r="G8" s="22"/>
+      <x:c r="H8" s="22"/>
+      <x:c r="I8" s="22"/>
+      <x:c r="J8" s="22"/>
+      <x:c r="K8" s="22"/>
+      <x:c r="L8" s="22"/>
+      <x:c r="M8" s="22"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="22" t="str">
+        <x:v>column_name</x:v>
+      </x:c>
+      <x:c r="B9" s="22" t="str">
+        <x:v>data_type</x:v>
+      </x:c>
+      <x:c r="C9" s="22" t="str">
+        <x:v>length</x:v>
+      </x:c>
+      <x:c r="D9" s="22" t="str">
+        <x:v>nullable</x:v>
+      </x:c>
+      <x:c r="E9" s="22" t="str">
+        <x:v>default_value</x:v>
+      </x:c>
+      <x:c r="F9" s="22" t="str">
+        <x:v>key_type</x:v>
+      </x:c>
+      <x:c r="G9" s="22" t="str">
+        <x:v>references</x:v>
+      </x:c>
+      <x:c r="H9" s="22" t="str">
+        <x:v>index_type</x:v>
+      </x:c>
+      <x:c r="I9" s="22" t="str">
+        <x:v>description_th</x:v>
+      </x:c>
+      <x:c r="J9" s="22" t="str">
+        <x:v>example_value</x:v>
+      </x:c>
+      <x:c r="K9" s="22" t="str">
+        <x:v>validation_rule</x:v>
+      </x:c>
+      <x:c r="L9" s="22" t="str">
+        <x:v>personal_data_classification</x:v>
+      </x:c>
+      <x:c r="M9" s="22" t="str">
+        <x:v>notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="22" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="B10" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="C10" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D10" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E10" s="22" t="str">
+        <x:v>AUTO_INCREMENT</x:v>
+      </x:c>
+      <x:c r="F10" s="22" t="str">
+        <x:v>PK</x:v>
+      </x:c>
+      <x:c r="G10" s="22"/>
+      <x:c r="H10" s="22" t="str">
+        <x:v>PRIMARY</x:v>
+      </x:c>
+      <x:c r="I10" s="22" t="str">
+        <x:v>รหัสภายในของรายการ</x:v>
+      </x:c>
+      <x:c r="J10" s="22"/>
+      <x:c r="K10" s="22"/>
+      <x:c r="L10" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M10" s="22"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="22" t="str">
+        <x:v>corrective_action_id</x:v>
+      </x:c>
+      <x:c r="B11" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="C11" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D11" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E11" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F11" s="22" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="G11" s="22" t="str">
+        <x:v>corrective_actions.id</x:v>
+      </x:c>
+      <x:c r="H11" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="I11" s="22" t="str">
+        <x:v>Corrective action ที่แสดงความคิดเห็น</x:v>
+      </x:c>
+      <x:c r="J11" s="22"/>
+      <x:c r="K11" s="22"/>
+      <x:c r="L11" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M11" s="22"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="22" t="str">
+        <x:v>author_id</x:v>
+      </x:c>
+      <x:c r="B12" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D12" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E12" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F12" s="22" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="G12" s="22" t="str">
+        <x:v>users.id</x:v>
+      </x:c>
+      <x:c r="H12" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="I12" s="22" t="str">
+        <x:v>ผู้เขียนความคิดเห็น</x:v>
+      </x:c>
+      <x:c r="J12" s="22"/>
+      <x:c r="K12" s="22"/>
+      <x:c r="L12" s="22" t="str">
+        <x:v>IDENTIFIER</x:v>
+      </x:c>
+      <x:c r="M12" s="22"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="22" t="str">
+        <x:v>content</x:v>
+      </x:c>
+      <x:c r="B13" s="22" t="str">
+        <x:v>TEXT</x:v>
+      </x:c>
+      <x:c r="C13" s="22" t="n">
+        <x:v>65535</x:v>
+      </x:c>
+      <x:c r="D13" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E13" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F13" s="22"/>
+      <x:c r="G13" s="22"/>
+      <x:c r="H13" s="22"/>
+      <x:c r="I13" s="22" t="str">
+        <x:v>ข้อความความคิดเห็น</x:v>
+      </x:c>
+      <x:c r="J13" s="22"/>
+      <x:c r="K13" s="22"/>
+      <x:c r="L13" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M13" s="22"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="22" t="str">
+        <x:v>metadata</x:v>
+      </x:c>
+      <x:c r="B14" s="22" t="str">
+        <x:v>JSON</x:v>
+      </x:c>
+      <x:c r="C14" s="22"/>
+      <x:c r="D14" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E14" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F14" s="22"/>
+      <x:c r="G14" s="22"/>
+      <x:c r="H14" s="22"/>
+      <x:c r="I14" s="22" t="str">
+        <x:v>ข้อมูลประกอบแบบ JSON</x:v>
+      </x:c>
+      <x:c r="J14" s="22"/>
+      <x:c r="K14" s="22" t="str">
+        <x:v>valid JSON</x:v>
+      </x:c>
+      <x:c r="L14" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M14" s="22"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="22" t="str">
+        <x:v>created_at</x:v>
+      </x:c>
+      <x:c r="B15" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="C15" s="22"/>
+      <x:c r="D15" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E15" s="22" t="str">
+        <x:v>CURRENT_TIMESTAMP(3)</x:v>
+      </x:c>
+      <x:c r="F15" s="22"/>
+      <x:c r="G15" s="22"/>
+      <x:c r="H15" s="22"/>
+      <x:c r="I15" s="22" t="str">
+        <x:v>วันที่และเวลาที่สร้างรายการ</x:v>
+      </x:c>
+      <x:c r="J15" s="22"/>
+      <x:c r="K15" s="22"/>
+      <x:c r="L15" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M15" s="22"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="22" t="str">
+        <x:v>updated_at</x:v>
+      </x:c>
+      <x:c r="B16" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="C16" s="22"/>
+      <x:c r="D16" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E16" s="22" t="str">
+        <x:v>CURRENT_TIMESTAMP(3)</x:v>
+      </x:c>
+      <x:c r="F16" s="22"/>
+      <x:c r="G16" s="22"/>
+      <x:c r="H16" s="22"/>
+      <x:c r="I16" s="22" t="str">
+        <x:v>วันที่และเวลาที่แก้ไขล่าสุด</x:v>
+      </x:c>
+      <x:c r="J16" s="22"/>
+      <x:c r="K16" s="22"/>
+      <x:c r="L16" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M16" s="22"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="22" t="str">
+        <x:v>deleted_at</x:v>
+      </x:c>
+      <x:c r="B17" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="C17" s="22"/>
+      <x:c r="D17" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E17" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F17" s="22"/>
+      <x:c r="G17" s="22"/>
+      <x:c r="H17" s="22"/>
+      <x:c r="I17" s="22" t="str">
+        <x:v>วันที่และเวลาที่ soft-delete</x:v>
+      </x:c>
+      <x:c r="J17" s="22"/>
+      <x:c r="K17" s="22"/>
+      <x:c r="L17" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M17" s="22"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="22"/>
+      <x:c r="B18" s="22"/>
+      <x:c r="C18" s="22"/>
+      <x:c r="D18" s="22"/>
+      <x:c r="E18" s="22"/>
+      <x:c r="F18" s="22"/>
+      <x:c r="G18" s="22"/>
+      <x:c r="H18" s="22"/>
+      <x:c r="I18" s="22"/>
+      <x:c r="J18" s="22"/>
+      <x:c r="K18" s="22"/>
+      <x:c r="L18" s="22"/>
+      <x:c r="M18" s="22"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="22" t="str">
+        <x:v>Relationships ที่เกี่ยวข้อง</x:v>
+      </x:c>
+      <x:c r="B19" s="22"/>
+      <x:c r="C19" s="22"/>
+      <x:c r="D19" s="22"/>
+      <x:c r="E19" s="22"/>
+      <x:c r="F19" s="22"/>
+      <x:c r="G19" s="22"/>
+      <x:c r="H19" s="22"/>
+      <x:c r="I19" s="22"/>
+      <x:c r="J19" s="22"/>
+      <x:c r="K19" s="22"/>
+      <x:c r="L19" s="22"/>
+      <x:c r="M19" s="22"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="22" t="str">
+        <x:v>parent_table</x:v>
+      </x:c>
+      <x:c r="B20" s="22" t="str">
+        <x:v>child_table</x:v>
+      </x:c>
+      <x:c r="C20" s="22" t="str">
+        <x:v>foreign_key</x:v>
+      </x:c>
+      <x:c r="D20" s="22" t="str">
+        <x:v>cardinality</x:v>
+      </x:c>
+      <x:c r="E20" s="22" t="str">
+        <x:v>on_delete</x:v>
+      </x:c>
+      <x:c r="F20" s="22" t="str">
+        <x:v>on_update</x:v>
+      </x:c>
+      <x:c r="G20" s="22" t="str">
+        <x:v>description_th</x:v>
+      </x:c>
+      <x:c r="H20" s="22"/>
+      <x:c r="I20" s="22"/>
+      <x:c r="J20" s="22"/>
+      <x:c r="K20" s="22"/>
+      <x:c r="L20" s="22"/>
+      <x:c r="M20" s="22"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="22" t="str">
+        <x:v>corrective_actions</x:v>
+      </x:c>
+      <x:c r="B21" s="22" t="str">
+        <x:v>corrective_action_comments</x:v>
+      </x:c>
+      <x:c r="C21" s="22" t="str">
+        <x:v>corrective_action_id</x:v>
+      </x:c>
+      <x:c r="D21" s="22" t="str">
+        <x:v>1 : Many</x:v>
+      </x:c>
+      <x:c r="E21" s="22" t="str">
+        <x:v>CASCADE</x:v>
+      </x:c>
+      <x:c r="F21" s="22" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G21" s="22" t="str">
+        <x:v>corrective_action_comments.corrective_action_id อ้างอิง corrective_actions.id</x:v>
+      </x:c>
+      <x:c r="H21" s="22"/>
+      <x:c r="I21" s="22"/>
+      <x:c r="J21" s="22"/>
+      <x:c r="K21" s="22"/>
+      <x:c r="L21" s="22"/>
+      <x:c r="M21" s="22"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="22" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="B22" s="22" t="str">
+        <x:v>corrective_action_comments</x:v>
+      </x:c>
+      <x:c r="C22" s="22" t="str">
+        <x:v>author_id</x:v>
+      </x:c>
+      <x:c r="D22" s="22" t="str">
+        <x:v>1 : Many</x:v>
+      </x:c>
+      <x:c r="E22" s="22" t="str">
+        <x:v>SET NULL</x:v>
+      </x:c>
+      <x:c r="F22" s="22" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G22" s="22" t="str">
+        <x:v>corrective_action_comments.author_id อ้างอิง users.id</x:v>
+      </x:c>
+      <x:c r="H22" s="22"/>
+      <x:c r="I22" s="22"/>
+      <x:c r="J22" s="22"/>
+      <x:c r="K22" s="22"/>
+      <x:c r="L22" s="22"/>
+      <x:c r="M22" s="22"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="36" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="22" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="30" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="22" t="str">
+        <x:v>archived_notifications</x:v>
+      </x:c>
+      <x:c r="B1" s="22"/>
+      <x:c r="C1" s="22"/>
+      <x:c r="D1" s="22"/>
+      <x:c r="E1" s="22"/>
+      <x:c r="F1" s="22"/>
+      <x:c r="G1" s="22"/>
+      <x:c r="H1" s="22"/>
+      <x:c r="I1" s="22"/>
+      <x:c r="J1" s="22"/>
+      <x:c r="K1" s="22"/>
+      <x:c r="L1" s="22"/>
+      <x:c r="M1" s="22"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="22" t="str">
+        <x:v>Notifications | Shared | Medium | สำเนาการแจ้งเตือนที่ผู้ใช้ archive แล้ว</x:v>
+      </x:c>
+      <x:c r="B2" s="22"/>
+      <x:c r="C2" s="22"/>
+      <x:c r="D2" s="22"/>
+      <x:c r="E2" s="22"/>
+      <x:c r="F2" s="22"/>
+      <x:c r="G2" s="22"/>
+      <x:c r="H2" s="22"/>
+      <x:c r="I2" s="22"/>
+      <x:c r="J2" s="22"/>
+      <x:c r="K2" s="22"/>
+      <x:c r="L2" s="22"/>
+      <x:c r="M2" s="22"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="22"/>
+      <x:c r="B3" s="22"/>
+      <x:c r="C3" s="22"/>
+      <x:c r="D3" s="22"/>
+      <x:c r="E3" s="22"/>
+      <x:c r="F3" s="22"/>
+      <x:c r="G3" s="22"/>
+      <x:c r="H3" s="22"/>
+      <x:c r="I3" s="22"/>
+      <x:c r="J3" s="22"/>
+      <x:c r="K3" s="22"/>
+      <x:c r="L3" s="22"/>
+      <x:c r="M3" s="22"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="22" t="str">
+        <x:v>table_name</x:v>
+      </x:c>
+      <x:c r="B4" s="22" t="str">
+        <x:v>archived_notifications</x:v>
+      </x:c>
+      <x:c r="C4" s="22" t="str">
+        <x:v>module</x:v>
+      </x:c>
+      <x:c r="D4" s="22" t="str">
+        <x:v>Notifications</x:v>
+      </x:c>
+      <x:c r="E4" s="22" t="str">
+        <x:v>phase</x:v>
+      </x:c>
+      <x:c r="F4" s="22" t="str">
+        <x:v>Shared</x:v>
+      </x:c>
+      <x:c r="G4" s="22" t="str">
+        <x:v>priority</x:v>
+      </x:c>
+      <x:c r="H4" s="22" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="I4" s="22"/>
+      <x:c r="J4" s="22"/>
+      <x:c r="K4" s="22"/>
+      <x:c r="L4" s="22"/>
+      <x:c r="M4" s="22"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="22" t="str">
+        <x:v>purpose_th</x:v>
+      </x:c>
+      <x:c r="B5" s="22" t="str">
+        <x:v>สำเนาการแจ้งเตือนที่ผู้ใช้ archive แล้ว</x:v>
+      </x:c>
+      <x:c r="C5" s="22" t="str">
+        <x:v>primary_key</x:v>
+      </x:c>
+      <x:c r="D5" s="22" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="E5" s="22" t="str">
+        <x:v>column_count</x:v>
+      </x:c>
+      <x:c r="F5" s="22" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G5" s="22"/>
+      <x:c r="H5" s="22"/>
+      <x:c r="I5" s="22"/>
+      <x:c r="J5" s="22"/>
+      <x:c r="K5" s="22"/>
+      <x:c r="L5" s="22"/>
+      <x:c r="M5" s="22"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="22"/>
+      <x:c r="B6" s="22"/>
+      <x:c r="C6" s="22"/>
+      <x:c r="D6" s="22"/>
+      <x:c r="E6" s="22"/>
+      <x:c r="F6" s="22"/>
+      <x:c r="G6" s="22"/>
+      <x:c r="H6" s="22"/>
+      <x:c r="I6" s="22"/>
+      <x:c r="J6" s="22"/>
+      <x:c r="K6" s="22"/>
+      <x:c r="L6" s="22"/>
+      <x:c r="M6" s="22"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="22" t="str">
+        <x:v>Column Dictionary</x:v>
+      </x:c>
+      <x:c r="B7" s="22"/>
+      <x:c r="C7" s="22"/>
+      <x:c r="D7" s="22"/>
+      <x:c r="E7" s="22"/>
+      <x:c r="F7" s="22"/>
+      <x:c r="G7" s="22"/>
+      <x:c r="H7" s="22"/>
+      <x:c r="I7" s="22"/>
+      <x:c r="J7" s="22"/>
+      <x:c r="K7" s="22"/>
+      <x:c r="L7" s="22"/>
+      <x:c r="M7" s="22"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="22"/>
+      <x:c r="B8" s="22"/>
+      <x:c r="C8" s="22"/>
+      <x:c r="D8" s="22"/>
+      <x:c r="E8" s="22"/>
+      <x:c r="F8" s="22"/>
+      <x:c r="G8" s="22"/>
+      <x:c r="H8" s="22"/>
+      <x:c r="I8" s="22"/>
+      <x:c r="J8" s="22"/>
+      <x:c r="K8" s="22"/>
+      <x:c r="L8" s="22"/>
+      <x:c r="M8" s="22"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="22" t="str">
+        <x:v>column_name</x:v>
+      </x:c>
+      <x:c r="B9" s="22" t="str">
+        <x:v>data_type</x:v>
+      </x:c>
+      <x:c r="C9" s="22" t="str">
+        <x:v>length</x:v>
+      </x:c>
+      <x:c r="D9" s="22" t="str">
+        <x:v>nullable</x:v>
+      </x:c>
+      <x:c r="E9" s="22" t="str">
+        <x:v>default_value</x:v>
+      </x:c>
+      <x:c r="F9" s="22" t="str">
+        <x:v>key_type</x:v>
+      </x:c>
+      <x:c r="G9" s="22" t="str">
+        <x:v>references</x:v>
+      </x:c>
+      <x:c r="H9" s="22" t="str">
+        <x:v>index_type</x:v>
+      </x:c>
+      <x:c r="I9" s="22" t="str">
+        <x:v>description_th</x:v>
+      </x:c>
+      <x:c r="J9" s="22" t="str">
+        <x:v>example_value</x:v>
+      </x:c>
+      <x:c r="K9" s="22" t="str">
+        <x:v>validation_rule</x:v>
+      </x:c>
+      <x:c r="L9" s="22" t="str">
+        <x:v>personal_data_classification</x:v>
+      </x:c>
+      <x:c r="M9" s="22" t="str">
+        <x:v>notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="22" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="B10" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="C10" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D10" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E10" s="22" t="str">
+        <x:v>AUTO_INCREMENT</x:v>
+      </x:c>
+      <x:c r="F10" s="22" t="str">
+        <x:v>PK</x:v>
+      </x:c>
+      <x:c r="G10" s="22"/>
+      <x:c r="H10" s="22" t="str">
+        <x:v>PRIMARY</x:v>
+      </x:c>
+      <x:c r="I10" s="22" t="str">
+        <x:v>รหัสภายในของรายการ</x:v>
+      </x:c>
+      <x:c r="J10" s="22"/>
+      <x:c r="K10" s="22"/>
+      <x:c r="L10" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M10" s="22"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="22" t="str">
+        <x:v>notification_id</x:v>
+      </x:c>
+      <x:c r="B11" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="C11" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D11" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E11" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F11" s="22"/>
+      <x:c r="G11" s="22"/>
+      <x:c r="H11" s="22"/>
+      <x:c r="I11" s="22" t="str">
+        <x:v>Notification ต้นฉบับ</x:v>
+      </x:c>
+      <x:c r="J11" s="22"/>
+      <x:c r="K11" s="22"/>
+      <x:c r="L11" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M11" s="22"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="22" t="str">
+        <x:v>user_id</x:v>
+      </x:c>
+      <x:c r="B12" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D12" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E12" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F12" s="22" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="G12" s="22" t="str">
+        <x:v>users.id</x:v>
+      </x:c>
+      <x:c r="H12" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="I12" s="22" t="str">
+        <x:v>ผู้ใช้งานเจ้าของรายการ</x:v>
+      </x:c>
+      <x:c r="J12" s="22"/>
+      <x:c r="K12" s="22"/>
+      <x:c r="L12" s="22" t="str">
+        <x:v>IDENTIFIER</x:v>
+      </x:c>
+      <x:c r="M12" s="22"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="22" t="str">
+        <x:v>notification_type</x:v>
+      </x:c>
+      <x:c r="B13" s="22" t="str">
+        <x:v>VARCHAR(80)</x:v>
+      </x:c>
+      <x:c r="C13" s="22" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D13" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E13" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F13" s="22"/>
+      <x:c r="G13" s="22"/>
+      <x:c r="H13" s="22"/>
+      <x:c r="I13" s="22" t="str">
+        <x:v>notification type</x:v>
+      </x:c>
+      <x:c r="J13" s="22"/>
+      <x:c r="K13" s="22"/>
+      <x:c r="L13" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M13" s="22"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="22" t="str">
+        <x:v>title</x:v>
+      </x:c>
+      <x:c r="B14" s="22" t="str">
+        <x:v>VARCHAR(255)</x:v>
+      </x:c>
+      <x:c r="C14" s="22" t="n">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="D14" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E14" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F14" s="22"/>
+      <x:c r="G14" s="22"/>
+      <x:c r="H14" s="22"/>
+      <x:c r="I14" s="22" t="str">
+        <x:v>ชื่อหรือหัวข้อ</x:v>
+      </x:c>
+      <x:c r="J14" s="22"/>
+      <x:c r="K14" s="22"/>
+      <x:c r="L14" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M14" s="22"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="22" t="str">
+        <x:v>body</x:v>
+      </x:c>
+      <x:c r="B15" s="22" t="str">
+        <x:v>TEXT</x:v>
+      </x:c>
+      <x:c r="C15" s="22" t="n">
+        <x:v>65535</x:v>
+      </x:c>
+      <x:c r="D15" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E15" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F15" s="22"/>
+      <x:c r="G15" s="22"/>
+      <x:c r="H15" s="22"/>
+      <x:c r="I15" s="22" t="str">
+        <x:v>body</x:v>
+      </x:c>
+      <x:c r="J15" s="22"/>
+      <x:c r="K15" s="22"/>
+      <x:c r="L15" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M15" s="22"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="22" t="str">
+        <x:v>read_at</x:v>
+      </x:c>
+      <x:c r="B16" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="C16" s="22"/>
+      <x:c r="D16" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E16" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F16" s="22"/>
+      <x:c r="G16" s="22"/>
+      <x:c r="H16" s="22"/>
+      <x:c r="I16" s="22" t="str">
+        <x:v>read at</x:v>
+      </x:c>
+      <x:c r="J16" s="22"/>
+      <x:c r="K16" s="22"/>
+      <x:c r="L16" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M16" s="22"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="22" t="str">
+        <x:v>original_created_at</x:v>
+      </x:c>
+      <x:c r="B17" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="C17" s="22"/>
+      <x:c r="D17" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E17" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F17" s="22"/>
+      <x:c r="G17" s="22"/>
+      <x:c r="H17" s="22"/>
+      <x:c r="I17" s="22" t="str">
+        <x:v>original created at</x:v>
+      </x:c>
+      <x:c r="J17" s="22"/>
+      <x:c r="K17" s="22"/>
+      <x:c r="L17" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M17" s="22"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="22" t="str">
+        <x:v>archived_at</x:v>
+      </x:c>
+      <x:c r="B18" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="C18" s="22"/>
+      <x:c r="D18" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E18" s="22" t="str">
+        <x:v>CURRENT_TIMESTAMP(3)</x:v>
+      </x:c>
+      <x:c r="F18" s="22"/>
+      <x:c r="G18" s="22"/>
+      <x:c r="H18" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="I18" s="22" t="str">
+        <x:v>วันที่และเวลาที่ archive</x:v>
+      </x:c>
+      <x:c r="J18" s="22"/>
+      <x:c r="K18" s="22"/>
+      <x:c r="L18" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M18" s="22"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="22"/>
+      <x:c r="B19" s="22"/>
+      <x:c r="C19" s="22"/>
+      <x:c r="D19" s="22"/>
+      <x:c r="E19" s="22"/>
+      <x:c r="F19" s="22"/>
+      <x:c r="G19" s="22"/>
+      <x:c r="H19" s="22"/>
+      <x:c r="I19" s="22"/>
+      <x:c r="J19" s="22"/>
+      <x:c r="K19" s="22"/>
+      <x:c r="L19" s="22"/>
+      <x:c r="M19" s="22"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="22" t="str">
+        <x:v>Relationships ที่เกี่ยวข้อง</x:v>
+      </x:c>
+      <x:c r="B20" s="22"/>
+      <x:c r="C20" s="22"/>
+      <x:c r="D20" s="22"/>
+      <x:c r="E20" s="22"/>
+      <x:c r="F20" s="22"/>
+      <x:c r="G20" s="22"/>
+      <x:c r="H20" s="22"/>
+      <x:c r="I20" s="22"/>
+      <x:c r="J20" s="22"/>
+      <x:c r="K20" s="22"/>
+      <x:c r="L20" s="22"/>
+      <x:c r="M20" s="22"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="22" t="str">
+        <x:v>parent_table</x:v>
+      </x:c>
+      <x:c r="B21" s="22" t="str">
+        <x:v>child_table</x:v>
+      </x:c>
+      <x:c r="C21" s="22" t="str">
+        <x:v>foreign_key</x:v>
+      </x:c>
+      <x:c r="D21" s="22" t="str">
+        <x:v>cardinality</x:v>
+      </x:c>
+      <x:c r="E21" s="22" t="str">
+        <x:v>on_delete</x:v>
+      </x:c>
+      <x:c r="F21" s="22" t="str">
+        <x:v>on_update</x:v>
+      </x:c>
+      <x:c r="G21" s="22" t="str">
+        <x:v>description_th</x:v>
+      </x:c>
+      <x:c r="H21" s="22"/>
+      <x:c r="I21" s="22"/>
+      <x:c r="J21" s="22"/>
+      <x:c r="K21" s="22"/>
+      <x:c r="L21" s="22"/>
+      <x:c r="M21" s="22"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="22" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="B22" s="22" t="str">
+        <x:v>archived_notifications</x:v>
+      </x:c>
+      <x:c r="C22" s="22" t="str">
+        <x:v>user_id</x:v>
+      </x:c>
+      <x:c r="D22" s="22" t="str">
+        <x:v>1 : Many</x:v>
+      </x:c>
+      <x:c r="E22" s="22" t="str">
+        <x:v>CASCADE</x:v>
+      </x:c>
+      <x:c r="F22" s="22" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G22" s="22" t="str">
+        <x:v>archived_notifications.user_id อ้างอิง users.id</x:v>
+      </x:c>
+      <x:c r="H22" s="22"/>
+      <x:c r="I22" s="22"/>
+      <x:c r="J22" s="22"/>
+      <x:c r="K22" s="22"/>
+      <x:c r="L22" s="22"/>
+      <x:c r="M22" s="22"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="36" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="22" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="30" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="22" t="str">
+        <x:v>safety_settings</x:v>
+      </x:c>
+      <x:c r="B1" s="22"/>
+      <x:c r="C1" s="22"/>
+      <x:c r="D1" s="22"/>
+      <x:c r="E1" s="22"/>
+      <x:c r="F1" s="22"/>
+      <x:c r="G1" s="22"/>
+      <x:c r="H1" s="22"/>
+      <x:c r="I1" s="22"/>
+      <x:c r="J1" s="22"/>
+      <x:c r="K1" s="22"/>
+      <x:c r="L1" s="22"/>
+      <x:c r="M1" s="22"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="22" t="str">
+        <x:v>Shared | Shared | High | ค่าตั้งค่าระบบ Safety ที่ Admin แก้ไขผ่าน API</x:v>
+      </x:c>
+      <x:c r="B2" s="22"/>
+      <x:c r="C2" s="22"/>
+      <x:c r="D2" s="22"/>
+      <x:c r="E2" s="22"/>
+      <x:c r="F2" s="22"/>
+      <x:c r="G2" s="22"/>
+      <x:c r="H2" s="22"/>
+      <x:c r="I2" s="22"/>
+      <x:c r="J2" s="22"/>
+      <x:c r="K2" s="22"/>
+      <x:c r="L2" s="22"/>
+      <x:c r="M2" s="22"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="22"/>
+      <x:c r="B3" s="22"/>
+      <x:c r="C3" s="22"/>
+      <x:c r="D3" s="22"/>
+      <x:c r="E3" s="22"/>
+      <x:c r="F3" s="22"/>
+      <x:c r="G3" s="22"/>
+      <x:c r="H3" s="22"/>
+      <x:c r="I3" s="22"/>
+      <x:c r="J3" s="22"/>
+      <x:c r="K3" s="22"/>
+      <x:c r="L3" s="22"/>
+      <x:c r="M3" s="22"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="22" t="str">
+        <x:v>table_name</x:v>
+      </x:c>
+      <x:c r="B4" s="22" t="str">
+        <x:v>safety_settings</x:v>
+      </x:c>
+      <x:c r="C4" s="22" t="str">
+        <x:v>module</x:v>
+      </x:c>
+      <x:c r="D4" s="22" t="str">
+        <x:v>Shared</x:v>
+      </x:c>
+      <x:c r="E4" s="22" t="str">
+        <x:v>phase</x:v>
+      </x:c>
+      <x:c r="F4" s="22" t="str">
+        <x:v>Shared</x:v>
+      </x:c>
+      <x:c r="G4" s="22" t="str">
+        <x:v>priority</x:v>
+      </x:c>
+      <x:c r="H4" s="22" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I4" s="22"/>
+      <x:c r="J4" s="22"/>
+      <x:c r="K4" s="22"/>
+      <x:c r="L4" s="22"/>
+      <x:c r="M4" s="22"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="22" t="str">
+        <x:v>purpose_th</x:v>
+      </x:c>
+      <x:c r="B5" s="22" t="str">
+        <x:v>ค่าตั้งค่าระบบ Safety ที่ Admin แก้ไขผ่าน API</x:v>
+      </x:c>
+      <x:c r="C5" s="22" t="str">
+        <x:v>primary_key</x:v>
+      </x:c>
+      <x:c r="D5" s="22" t="str">
+        <x:v>setting_key</x:v>
+      </x:c>
+      <x:c r="E5" s="22" t="str">
+        <x:v>column_count</x:v>
+      </x:c>
+      <x:c r="F5" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G5" s="22"/>
+      <x:c r="H5" s="22"/>
+      <x:c r="I5" s="22"/>
+      <x:c r="J5" s="22"/>
+      <x:c r="K5" s="22"/>
+      <x:c r="L5" s="22"/>
+      <x:c r="M5" s="22"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="22"/>
+      <x:c r="B6" s="22"/>
+      <x:c r="C6" s="22"/>
+      <x:c r="D6" s="22"/>
+      <x:c r="E6" s="22"/>
+      <x:c r="F6" s="22"/>
+      <x:c r="G6" s="22"/>
+      <x:c r="H6" s="22"/>
+      <x:c r="I6" s="22"/>
+      <x:c r="J6" s="22"/>
+      <x:c r="K6" s="22"/>
+      <x:c r="L6" s="22"/>
+      <x:c r="M6" s="22"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="22" t="str">
+        <x:v>Column Dictionary</x:v>
+      </x:c>
+      <x:c r="B7" s="22"/>
+      <x:c r="C7" s="22"/>
+      <x:c r="D7" s="22"/>
+      <x:c r="E7" s="22"/>
+      <x:c r="F7" s="22"/>
+      <x:c r="G7" s="22"/>
+      <x:c r="H7" s="22"/>
+      <x:c r="I7" s="22"/>
+      <x:c r="J7" s="22"/>
+      <x:c r="K7" s="22"/>
+      <x:c r="L7" s="22"/>
+      <x:c r="M7" s="22"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="22"/>
+      <x:c r="B8" s="22"/>
+      <x:c r="C8" s="22"/>
+      <x:c r="D8" s="22"/>
+      <x:c r="E8" s="22"/>
+      <x:c r="F8" s="22"/>
+      <x:c r="G8" s="22"/>
+      <x:c r="H8" s="22"/>
+      <x:c r="I8" s="22"/>
+      <x:c r="J8" s="22"/>
+      <x:c r="K8" s="22"/>
+      <x:c r="L8" s="22"/>
+      <x:c r="M8" s="22"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="22" t="str">
+        <x:v>column_name</x:v>
+      </x:c>
+      <x:c r="B9" s="22" t="str">
+        <x:v>data_type</x:v>
+      </x:c>
+      <x:c r="C9" s="22" t="str">
+        <x:v>length</x:v>
+      </x:c>
+      <x:c r="D9" s="22" t="str">
+        <x:v>nullable</x:v>
+      </x:c>
+      <x:c r="E9" s="22" t="str">
+        <x:v>default_value</x:v>
+      </x:c>
+      <x:c r="F9" s="22" t="str">
+        <x:v>key_type</x:v>
+      </x:c>
+      <x:c r="G9" s="22" t="str">
+        <x:v>references</x:v>
+      </x:c>
+      <x:c r="H9" s="22" t="str">
+        <x:v>index_type</x:v>
+      </x:c>
+      <x:c r="I9" s="22" t="str">
+        <x:v>description_th</x:v>
+      </x:c>
+      <x:c r="J9" s="22" t="str">
+        <x:v>example_value</x:v>
+      </x:c>
+      <x:c r="K9" s="22" t="str">
+        <x:v>validation_rule</x:v>
+      </x:c>
+      <x:c r="L9" s="22" t="str">
+        <x:v>personal_data_classification</x:v>
+      </x:c>
+      <x:c r="M9" s="22" t="str">
+        <x:v>notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="22" t="str">
+        <x:v>setting_key</x:v>
+      </x:c>
+      <x:c r="B10" s="22" t="str">
+        <x:v>VARCHAR(120)</x:v>
+      </x:c>
+      <x:c r="C10" s="22" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D10" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E10" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F10" s="22" t="str">
+        <x:v>PK</x:v>
+      </x:c>
+      <x:c r="G10" s="22"/>
+      <x:c r="H10" s="22" t="str">
+        <x:v>PRIMARY</x:v>
+      </x:c>
+      <x:c r="I10" s="22" t="str">
+        <x:v>คีย์ค่าตั้งค่าระบบ</x:v>
+      </x:c>
+      <x:c r="J10" s="22"/>
+      <x:c r="K10" s="22"/>
+      <x:c r="L10" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M10" s="22"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="22" t="str">
+        <x:v>setting_value</x:v>
+      </x:c>
+      <x:c r="B11" s="22" t="str">
+        <x:v>JSON</x:v>
+      </x:c>
+      <x:c r="C11" s="22"/>
+      <x:c r="D11" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E11" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F11" s="22"/>
+      <x:c r="G11" s="22"/>
+      <x:c r="H11" s="22"/>
+      <x:c r="I11" s="22" t="str">
+        <x:v>ค่าตั้งค่าระบบแบบ JSON</x:v>
+      </x:c>
+      <x:c r="J11" s="22"/>
+      <x:c r="K11" s="22" t="str">
+        <x:v>valid JSON</x:v>
+      </x:c>
+      <x:c r="L11" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M11" s="22"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="22" t="str">
+        <x:v>updated_by</x:v>
+      </x:c>
+      <x:c r="B12" s="22" t="str">
+        <x:v>BIGINT UNSIGNED</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D12" s="22" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E12" s="22" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="F12" s="22" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="G12" s="22" t="str">
+        <x:v>users.id</x:v>
+      </x:c>
+      <x:c r="H12" s="22" t="str">
+        <x:v>INDEX</x:v>
+      </x:c>
+      <x:c r="I12" s="22" t="str">
+        <x:v>ผู้แก้ไขค่าล่าสุด</x:v>
+      </x:c>
+      <x:c r="J12" s="22"/>
+      <x:c r="K12" s="22"/>
+      <x:c r="L12" s="22" t="str">
+        <x:v>IDENTIFIER</x:v>
+      </x:c>
+      <x:c r="M12" s="22"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="22" t="str">
+        <x:v>created_at</x:v>
+      </x:c>
+      <x:c r="B13" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="C13" s="22"/>
+      <x:c r="D13" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E13" s="22" t="str">
+        <x:v>CURRENT_TIMESTAMP(3)</x:v>
+      </x:c>
+      <x:c r="F13" s="22"/>
+      <x:c r="G13" s="22"/>
+      <x:c r="H13" s="22"/>
+      <x:c r="I13" s="22" t="str">
+        <x:v>วันที่และเวลาที่สร้างรายการ</x:v>
+      </x:c>
+      <x:c r="J13" s="22"/>
+      <x:c r="K13" s="22"/>
+      <x:c r="L13" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M13" s="22"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="22" t="str">
+        <x:v>updated_at</x:v>
+      </x:c>
+      <x:c r="B14" s="22" t="str">
+        <x:v>DATETIME(3)</x:v>
+      </x:c>
+      <x:c r="C14" s="22"/>
+      <x:c r="D14" s="22" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="E14" s="22" t="str">
+        <x:v>CURRENT_TIMESTAMP(3)</x:v>
+      </x:c>
+      <x:c r="F14" s="22"/>
+      <x:c r="G14" s="22"/>
+      <x:c r="H14" s="22"/>
+      <x:c r="I14" s="22" t="str">
+        <x:v>วันที่และเวลาที่แก้ไขล่าสุด</x:v>
+      </x:c>
+      <x:c r="J14" s="22"/>
+      <x:c r="K14" s="22"/>
+      <x:c r="L14" s="22" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M14" s="22"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="22"/>
+      <x:c r="B15" s="22"/>
+      <x:c r="C15" s="22"/>
+      <x:c r="D15" s="22"/>
+      <x:c r="E15" s="22"/>
+      <x:c r="F15" s="22"/>
+      <x:c r="G15" s="22"/>
+      <x:c r="H15" s="22"/>
+      <x:c r="I15" s="22"/>
+      <x:c r="J15" s="22"/>
+      <x:c r="K15" s="22"/>
+      <x:c r="L15" s="22"/>
+      <x:c r="M15" s="22"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="22" t="str">
+        <x:v>Relationships ที่เกี่ยวข้อง</x:v>
+      </x:c>
+      <x:c r="B16" s="22"/>
+      <x:c r="C16" s="22"/>
+      <x:c r="D16" s="22"/>
+      <x:c r="E16" s="22"/>
+      <x:c r="F16" s="22"/>
+      <x:c r="G16" s="22"/>
+      <x:c r="H16" s="22"/>
+      <x:c r="I16" s="22"/>
+      <x:c r="J16" s="22"/>
+      <x:c r="K16" s="22"/>
+      <x:c r="L16" s="22"/>
+      <x:c r="M16" s="22"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="22" t="str">
+        <x:v>parent_table</x:v>
+      </x:c>
+      <x:c r="B17" s="22" t="str">
+        <x:v>child_table</x:v>
+      </x:c>
+      <x:c r="C17" s="22" t="str">
+        <x:v>foreign_key</x:v>
+      </x:c>
+      <x:c r="D17" s="22" t="str">
+        <x:v>cardinality</x:v>
+      </x:c>
+      <x:c r="E17" s="22" t="str">
+        <x:v>on_delete</x:v>
+      </x:c>
+      <x:c r="F17" s="22" t="str">
+        <x:v>on_update</x:v>
+      </x:c>
+      <x:c r="G17" s="22" t="str">
+        <x:v>description_th</x:v>
+      </x:c>
+      <x:c r="H17" s="22"/>
+      <x:c r="I17" s="22"/>
+      <x:c r="J17" s="22"/>
+      <x:c r="K17" s="22"/>
+      <x:c r="L17" s="22"/>
+      <x:c r="M17" s="22"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="22" t="str">
+        <x:v>users</x:v>
+      </x:c>
+      <x:c r="B18" s="22" t="str">
+        <x:v>safety_settings</x:v>
+      </x:c>
+      <x:c r="C18" s="22" t="str">
+        <x:v>updated_by</x:v>
+      </x:c>
+      <x:c r="D18" s="22" t="str">
+        <x:v>1 : Many</x:v>
+      </x:c>
+      <x:c r="E18" s="22" t="str">
+        <x:v>SET NULL</x:v>
+      </x:c>
+      <x:c r="F18" s="22" t="str">
+        <x:v>NO ACTION</x:v>
+      </x:c>
+      <x:c r="G18" s="22" t="str">
+        <x:v>safety_settings.updated_by อ้างอิง users.id</x:v>
+      </x:c>
+      <x:c r="H18" s="22"/>
+      <x:c r="I18" s="22"/>
+      <x:c r="J18" s="22"/>
+      <x:c r="K18" s="22"/>
+      <x:c r="L18" s="22"/>
+      <x:c r="M18" s="22"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
@@ -48828,7 +57041,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R219b91f0d4b44ba7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra955f786d95b4d67"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49362,7 +57575,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R138a61422af34e1b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50ffdbd831cb4d75"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49675,7 +57888,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raee76af591ad4583"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a1133a1e25747b0"/>
   </x:tableParts>
 </x:worksheet>
 </file>